--- a/data/parts_report_past.xlsx
+++ b/data/parts_report_past.xlsx
@@ -5,8 +5,8 @@
     <x:workbookView/>
   </x:bookViews>
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Ra271e1bb9bb44563"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Filters" sheetId="2" r:id="R81e7f1c4d5ab417d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R857ed5e9b13449d5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Filters" sheetId="2" r:id="Rffdee3f5c0b84bde"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -1258,17 +1258,17 @@
       </x:c>
       <x:c r="C22" t="inlineStr" s="7">
         <x:is>
-          <x:t>10-10-10, Club Member, Parts Ordered, Trane Supply</x:t>
+          <x:t>Club Member, Need to order part (NTO)</x:t>
         </x:is>
       </x:c>
       <x:c r="D22" t="inlineStr" s="9">
         <x:is>
-          <x:t>586864800</x:t>
+          <x:t>587448096</x:t>
         </x:is>
       </x:c>
       <x:c r="E22" t="inlineStr" s="11">
         <x:is>
-          <x:t>586864800</x:t>
+          <x:t>587448096</x:t>
         </x:is>
       </x:c>
       <x:c r="F22" s="13">
@@ -1276,7 +1276,7 @@
       </x:c>
       <x:c r="G22" t="inlineStr" s="15">
         <x:is>
-          <x:t>PP David Escobar</x:t>
+          <x:t/>
         </x:is>
       </x:c>
       <x:c r="H22" t="inlineStr" s="17">
@@ -1286,19 +1286,19 @@
       </x:c>
       <x:c r="I22" t="inlineStr" s="19">
         <x:is>
-          <x:t>CS - HVAC - Service - 12</x:t>
+          <x:t>PLM - HVAC - Service - 12</x:t>
         </x:is>
       </x:c>
       <x:c r="J22" t="inlineStr" s="21">
         <x:is>
-          <x:t>Hope Gadea</x:t>
+          <x:t>Cassandra Sexton</x:t>
         </x:is>
       </x:c>
       <x:c r="K22" s="23">
-        <x:v>46100</x:v>
+        <x:v>46106</x:v>
       </x:c>
       <x:c r="L22" s="25">
-        <x:v>46100</x:v>
+        <x:v>46106</x:v>
       </x:c>
     </x:row>
     <x:row r="23">
@@ -1416,21 +1416,21 @@
         </x:is>
       </x:c>
       <x:c r="B25" t="n" s="5">
-        <x:v>0</x:v>
+        <x:v>689.97</x:v>
       </x:c>
       <x:c r="C25" t="inlineStr" s="7">
         <x:is>
-          <x:t>Club Member, LW- 2 YEAR LABOR, Parts Ordered, Trane Supply</x:t>
+          <x:t>2-YR Labor Warranty, 2-YR Labor Warranty, 2-YR Labor Warranty, Club Member, Gemaire, Parts Received </x:t>
         </x:is>
       </x:c>
       <x:c r="D25" t="inlineStr" s="9">
         <x:is>
-          <x:t>587077196</x:t>
+          <x:t>587253199</x:t>
         </x:is>
       </x:c>
       <x:c r="E25" t="inlineStr" s="11">
         <x:is>
-          <x:t>587077196</x:t>
+          <x:t>587253199</x:t>
         </x:is>
       </x:c>
       <x:c r="F25" s="13">
@@ -1438,7 +1438,7 @@
       </x:c>
       <x:c r="G25" t="inlineStr" s="15">
         <x:is>
-          <x:t>Tyler Gallatin</x:t>
+          <x:t>PP Barrington Wilson</x:t>
         </x:is>
       </x:c>
       <x:c r="H25" t="inlineStr" s="17">
@@ -1453,14 +1453,14 @@
       </x:c>
       <x:c r="J25" t="inlineStr" s="21">
         <x:is>
-          <x:t>Timberwalk Association Inc</x:t>
+          <x:t>Dane Lyons</x:t>
         </x:is>
       </x:c>
       <x:c r="K25" s="23">
-        <x:v>46102</x:v>
+        <x:v>46105</x:v>
       </x:c>
       <x:c r="L25" s="25">
-        <x:v>46102</x:v>
+        <x:v>46105</x:v>
       </x:c>
     </x:row>
     <x:row r="26">
@@ -1470,21 +1470,21 @@
         </x:is>
       </x:c>
       <x:c r="B26" t="n" s="5">
-        <x:v>689.97</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="C26" t="inlineStr" s="7">
         <x:is>
-          <x:t>2-YR Labor Warranty, 2-YR Labor Warranty, 2-YR Labor Warranty, Club Member, Gemaire, Parts Received </x:t>
+          <x:t>10-Year Labor, Carrier enterprise, Club Member, Parts Received , PLM</x:t>
         </x:is>
       </x:c>
       <x:c r="D26" t="inlineStr" s="9">
         <x:is>
-          <x:t>587253199</x:t>
+          <x:t>587167128</x:t>
         </x:is>
       </x:c>
       <x:c r="E26" t="inlineStr" s="11">
         <x:is>
-          <x:t>587253199</x:t>
+          <x:t>587167128</x:t>
         </x:is>
       </x:c>
       <x:c r="F26" s="13">
@@ -1492,7 +1492,7 @@
       </x:c>
       <x:c r="G26" t="inlineStr" s="15">
         <x:is>
-          <x:t>PP Barrington Wilson</x:t>
+          <x:t>Tyler Gallatin</x:t>
         </x:is>
       </x:c>
       <x:c r="H26" t="inlineStr" s="17">
@@ -1502,19 +1502,19 @@
       </x:c>
       <x:c r="I26" t="inlineStr" s="19">
         <x:is>
-          <x:t>CS - HVAC - Service - 12</x:t>
+          <x:t>PLM - HVAC - Service - 12</x:t>
         </x:is>
       </x:c>
       <x:c r="J26" t="inlineStr" s="21">
         <x:is>
-          <x:t>Dane Lyons</x:t>
+          <x:t>Marsha &amp; David Gordon</x:t>
         </x:is>
       </x:c>
       <x:c r="K26" s="23">
-        <x:v>46105</x:v>
+        <x:v>46104</x:v>
       </x:c>
       <x:c r="L26" s="25">
-        <x:v>46105</x:v>
+        <x:v>46104</x:v>
       </x:c>
     </x:row>
     <x:row r="27">
@@ -1524,21 +1524,21 @@
         </x:is>
       </x:c>
       <x:c r="B27" t="n" s="5">
-        <x:v>0</x:v>
+        <x:v>945.4</x:v>
       </x:c>
       <x:c r="C27" t="inlineStr" s="7">
         <x:is>
-          <x:t>10-Year Labor, Carrier enterprise, Club Member, Parts Received , PLM</x:t>
+          <x:t>Club Member, Need to order part (NTO), PLM</x:t>
         </x:is>
       </x:c>
       <x:c r="D27" t="inlineStr" s="9">
         <x:is>
-          <x:t>587167128</x:t>
+          <x:t>587403893</x:t>
         </x:is>
       </x:c>
       <x:c r="E27" t="inlineStr" s="11">
         <x:is>
-          <x:t>587167128</x:t>
+          <x:t>587403893</x:t>
         </x:is>
       </x:c>
       <x:c r="F27" s="13">
@@ -1546,7 +1546,7 @@
       </x:c>
       <x:c r="G27" t="inlineStr" s="15">
         <x:is>
-          <x:t>Tyler Gallatin</x:t>
+          <x:t>Rolin Moimeme</x:t>
         </x:is>
       </x:c>
       <x:c r="H27" t="inlineStr" s="17">
@@ -1561,14 +1561,14 @@
       </x:c>
       <x:c r="J27" t="inlineStr" s="21">
         <x:is>
-          <x:t>Marsha &amp; David Gordon</x:t>
+          <x:t>WALKER, CAMERON</x:t>
         </x:is>
       </x:c>
       <x:c r="K27" s="23">
-        <x:v>46104</x:v>
+        <x:v>46106</x:v>
       </x:c>
       <x:c r="L27" s="25">
-        <x:v>46104</x:v>
+        <x:v>46106</x:v>
       </x:c>
     </x:row>
     <x:row r="28">
@@ -1578,21 +1578,21 @@
         </x:is>
       </x:c>
       <x:c r="B28" t="n" s="5">
-        <x:v>0</x:v>
+        <x:v>722.79</x:v>
       </x:c>
       <x:c r="C28" t="inlineStr" s="7">
         <x:is>
-          <x:t>10-Year Labor, 10-Year Labor, 10-Year Labor, 10-Year Labor, Goodman distribution , MULTI- 5, Parts Ordered, PLM, Potential Member</x:t>
+          <x:t>Baker Supply, Parts Ordered, PLM, Potential Member</x:t>
         </x:is>
       </x:c>
       <x:c r="D28" t="inlineStr" s="9">
         <x:is>
-          <x:t>587266021</x:t>
+          <x:t>459781920</x:t>
         </x:is>
       </x:c>
       <x:c r="E28" t="inlineStr" s="11">
         <x:is>
-          <x:t>587266021</x:t>
+          <x:t>459781920</x:t>
         </x:is>
       </x:c>
       <x:c r="F28" s="13">
@@ -1600,7 +1600,7 @@
       </x:c>
       <x:c r="G28" t="inlineStr" s="15">
         <x:is>
-          <x:t>PP Cesar Levy</x:t>
+          <x:t>PLM-Quentin Stewart</x:t>
         </x:is>
       </x:c>
       <x:c r="H28" t="inlineStr" s="17">
@@ -1615,225 +1615,63 @@
       </x:c>
       <x:c r="J28" t="inlineStr" s="21">
         <x:is>
-          <x:t>Nevalee &amp; Paul Oneil</x:t>
+          <x:t>Gluck Carolyn</x:t>
         </x:is>
       </x:c>
       <x:c r="K28" s="23">
-        <x:v>46105</x:v>
+        <x:v>45726</x:v>
       </x:c>
       <x:c r="L28" s="25">
-        <x:v>46105</x:v>
+        <x:v>45726</x:v>
       </x:c>
     </x:row>
     <x:row r="29">
-      <x:c r="A29" t="inlineStr" s="3">
-        <x:is>
-          <x:t>HC - Return to Repair</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B29" t="n" s="5">
-        <x:v>292.95</x:v>
-      </x:c>
-      <x:c r="C29" t="inlineStr" s="7">
-        <x:is>
-          <x:t>Baker Supply, Club Member, Parts Ordered, PLM</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D29" t="inlineStr" s="9">
-        <x:is>
-          <x:t>586875916</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="E29" t="inlineStr" s="11">
-        <x:is>
-          <x:t>586875916</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="F29" s="13">
-        <x:v>46106</x:v>
-      </x:c>
-      <x:c r="G29" t="inlineStr" s="15">
-        <x:is>
-          <x:t>PP Barrington Wilson</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="H29" t="inlineStr" s="17">
-        <x:is>
-          <x:t>Hold</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="I29" t="inlineStr" s="19">
-        <x:is>
-          <x:t>CS - HVAC - Service - 12</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="J29" t="inlineStr" s="21">
-        <x:is>
-          <x:t>Anna Tyulmenkova</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="K29" s="23">
-        <x:v>46100</x:v>
-      </x:c>
-      <x:c r="L29" s="25">
-        <x:v>46100</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="30">
-      <x:c r="A30" t="inlineStr" s="3">
-        <x:is>
-          <x:t>HC - Return to Repair</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B30" t="n" s="5">
-        <x:v>722.79</x:v>
-      </x:c>
-      <x:c r="C30" t="inlineStr" s="7">
-        <x:is>
-          <x:t>Baker Supply, Parts Ordered, PLM, Potential Member</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D30" t="inlineStr" s="9">
-        <x:is>
-          <x:t>459781920</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="E30" t="inlineStr" s="11">
-        <x:is>
-          <x:t>459781920</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="F30" s="13">
-        <x:v>46106</x:v>
-      </x:c>
-      <x:c r="G30" t="inlineStr" s="15">
-        <x:is>
-          <x:t>PLM-Quentin Stewart</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="H30" t="inlineStr" s="17">
-        <x:is>
-          <x:t>Hold</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="I30" t="inlineStr" s="19">
-        <x:is>
-          <x:t>PLM - HVAC - Service - 12</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="J30" t="inlineStr" s="21">
-        <x:is>
-          <x:t>Gluck Carolyn</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="K30" s="23">
-        <x:v>45726</x:v>
-      </x:c>
-      <x:c r="L30" s="25">
-        <x:v>45726</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="31">
-      <x:c r="A31" t="inlineStr" s="3">
-        <x:is>
-          <x:t>HC - Return to Repair</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B31" t="n" s="5">
-        <x:v>303.45</x:v>
-      </x:c>
-      <x:c r="C31" t="inlineStr" s="7">
-        <x:is>
-          <x:t>Carrier enterprise, Parts Ordered, Potential Member</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D31" t="inlineStr" s="9">
-        <x:is>
-          <x:t>581332764</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="E31" t="inlineStr" s="11">
-        <x:is>
-          <x:t>581332764</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="F31" s="13">
-        <x:v>46106</x:v>
-      </x:c>
-      <x:c r="G31" t="inlineStr" s="15">
-        <x:is>
-          <x:t>Justin Greene</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="H31" t="inlineStr" s="17">
-        <x:is>
-          <x:t>Hold</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="I31" t="inlineStr" s="19">
-        <x:is>
-          <x:t>CS - HVAC - Service - 12</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="J31" t="inlineStr" s="21">
-        <x:is>
-          <x:t>Chris Orsini</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="K31" s="23">
-        <x:v>46057</x:v>
-      </x:c>
-      <x:c r="L31" s="25">
-        <x:v>46057</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="32">
-      <x:c r="A32" t="n" s="4">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="B32" t="n" s="6">
-        <x:v>425.814</x:v>
-      </x:c>
-      <x:c r="C32" t="inlineStr" s="8">
+      <x:c r="A29" t="n" s="4">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="B29" t="n" s="6">
+        <x:v>486.05259259259259259259259259</x:v>
+      </x:c>
+      <x:c r="C29" t="inlineStr" s="8">
         <x:is>
           <x:t/>
         </x:is>
       </x:c>
-      <x:c r="D32" t="n" s="10">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="E32" t="inlineStr" s="12">
+      <x:c r="D29" t="n" s="10">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="E29" t="inlineStr" s="12">
         <x:is>
           <x:t/>
         </x:is>
       </x:c>
-      <x:c r="F32" s="14">
+      <x:c r="F29" s="14">
         <x:v/>
       </x:c>
-      <x:c r="G32" t="inlineStr" s="16">
+      <x:c r="G29" t="inlineStr" s="16">
         <x:is>
           <x:t/>
         </x:is>
       </x:c>
-      <x:c r="H32" t="inlineStr" s="18">
+      <x:c r="H29" t="inlineStr" s="18">
         <x:is>
           <x:t/>
         </x:is>
       </x:c>
-      <x:c r="I32" t="inlineStr" s="20">
+      <x:c r="I29" t="inlineStr" s="20">
         <x:is>
           <x:t/>
         </x:is>
       </x:c>
-      <x:c r="J32" t="inlineStr" s="22">
+      <x:c r="J29" t="inlineStr" s="22">
         <x:is>
           <x:t/>
         </x:is>
       </x:c>
-      <x:c r="K32" s="24">
+      <x:c r="K29" s="24">
         <x:v/>
       </x:c>
-      <x:c r="L32" s="26">
+      <x:c r="L29" s="26">
         <x:v/>
       </x:c>
     </x:row>

--- a/data/parts_report_past.xlsx
+++ b/data/parts_report_past.xlsx
@@ -5,8 +5,8 @@
     <x:workbookView/>
   </x:bookViews>
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R857ed5e9b13449d5"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Filters" sheetId="2" r:id="Rffdee3f5c0b84bde"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Re9ec0da196c2412e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Filters" sheetId="2" r:id="Rd31b711acc03497b"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -1626,52 +1626,592 @@
       </x:c>
     </x:row>
     <x:row r="29">
-      <x:c r="A29" t="n" s="4">
-        <x:v>27</x:v>
-      </x:c>
-      <x:c r="B29" t="n" s="6">
-        <x:v>486.05259259259259259259259259</x:v>
-      </x:c>
-      <x:c r="C29" t="inlineStr" s="8">
+      <x:c r="A29" t="inlineStr" s="3">
+        <x:is>
+          <x:t>HC - Return to Repair</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B29" t="n" s="5">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="C29" t="inlineStr" s="7">
+        <x:is>
+          <x:t>Carrier enterprise, Club Member, Parts Received </x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D29" t="inlineStr" s="9">
+        <x:is>
+          <x:t>586083412</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E29" t="inlineStr" s="11">
+        <x:is>
+          <x:t>586083412</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F29" s="13">
+        <x:v>46107</x:v>
+      </x:c>
+      <x:c r="G29" t="inlineStr" s="15">
+        <x:is>
+          <x:t>Michael Kertesz </x:t>
+        </x:is>
+      </x:c>
+      <x:c r="H29" t="inlineStr" s="17">
+        <x:is>
+          <x:t>Hold</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="I29" t="inlineStr" s="19">
+        <x:is>
+          <x:t>CS - HVAC - Service - 12</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="J29" t="inlineStr" s="21">
+        <x:is>
+          <x:t>Gregory  Tsesler</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="K29" s="23">
+        <x:v>46093</x:v>
+      </x:c>
+      <x:c r="L29" s="25">
+        <x:v>46093</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="30">
+      <x:c r="A30" t="inlineStr" s="3">
+        <x:is>
+          <x:t>HC - Return to Repair</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B30" t="n" s="5">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="C30" t="inlineStr" s="7">
+        <x:is>
+          <x:t>10-10-10, Club Member, Parts Ordered, Trane Supply</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D30" t="inlineStr" s="9">
+        <x:is>
+          <x:t>586864800</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E30" t="inlineStr" s="11">
+        <x:is>
+          <x:t>586864800</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F30" s="13">
+        <x:v>46107</x:v>
+      </x:c>
+      <x:c r="G30" t="inlineStr" s="15">
+        <x:is>
+          <x:t>PP David Escobar</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="H30" t="inlineStr" s="17">
+        <x:is>
+          <x:t>Hold</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="I30" t="inlineStr" s="19">
+        <x:is>
+          <x:t>CS - HVAC - Service - 12</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="J30" t="inlineStr" s="21">
+        <x:is>
+          <x:t>Hope Gadea</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="K30" s="23">
+        <x:v>46100</x:v>
+      </x:c>
+      <x:c r="L30" s="25">
+        <x:v>46100</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="31">
+      <x:c r="A31" t="inlineStr" s="3">
+        <x:is>
+          <x:t>HC - Return to Repair</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B31" t="n" s="5">
+        <x:v>294.96</x:v>
+      </x:c>
+      <x:c r="C31" t="inlineStr" s="7">
+        <x:is>
+          <x:t>10-10-10, 10-10-10, Club Member, Club Member (Additional System), MULTI- 2, Parts Ordered, Trane Supply</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D31" t="inlineStr" s="9">
+        <x:is>
+          <x:t>554624809</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E31" t="inlineStr" s="11">
+        <x:is>
+          <x:t>554624809</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F31" s="13">
+        <x:v>46107</x:v>
+      </x:c>
+      <x:c r="G31" t="inlineStr" s="15">
+        <x:is>
+          <x:t>PP Carlos Machado</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="H31" t="inlineStr" s="17">
+        <x:is>
+          <x:t>Hold</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="I31" t="inlineStr" s="19">
+        <x:is>
+          <x:t>CS - HVAC - Service - 12</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="J31" t="inlineStr" s="21">
+        <x:is>
+          <x:t>Michael &amp; Delle Lenzen</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="K31" s="23">
+        <x:v>45996</x:v>
+      </x:c>
+      <x:c r="L31" s="25">
+        <x:v>45996</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="32">
+      <x:c r="A32" t="inlineStr" s="3">
+        <x:is>
+          <x:t>HC - Return to Repair</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B32" t="n" s="5">
+        <x:v>344.21</x:v>
+      </x:c>
+      <x:c r="C32" t="inlineStr" s="7">
+        <x:is>
+          <x:t>10-10-10, Club Member, Parts Received </x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D32" t="inlineStr" s="9">
+        <x:is>
+          <x:t>587448160</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E32" t="inlineStr" s="11">
+        <x:is>
+          <x:t>587448160</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F32" s="13">
+        <x:v>46107</x:v>
+      </x:c>
+      <x:c r="G32" t="inlineStr" s="15">
+        <x:is>
+          <x:t>Rolin Moimeme</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="H32" t="inlineStr" s="17">
+        <x:is>
+          <x:t>Hold</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="I32" t="inlineStr" s="19">
+        <x:is>
+          <x:t>CS - HVAC - Service - 12</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="J32" t="inlineStr" s="21">
+        <x:is>
+          <x:t>Rene Ceusters</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="K32" s="23">
+        <x:v>46106</x:v>
+      </x:c>
+      <x:c r="L32" s="25">
+        <x:v>46106</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="33">
+      <x:c r="A33" t="inlineStr" s="3">
+        <x:is>
+          <x:t>HC - Return to Repair</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B33" t="n" s="5">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="C33" t="inlineStr" s="7">
+        <x:is>
+          <x:t>Club Member, LW- 2 YEAR LABOR, Parts Ordered, Trane Supply</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D33" t="inlineStr" s="9">
+        <x:is>
+          <x:t>587077196</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E33" t="inlineStr" s="11">
+        <x:is>
+          <x:t>587077196</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F33" s="13">
+        <x:v>46107</x:v>
+      </x:c>
+      <x:c r="G33" t="inlineStr" s="15">
+        <x:is>
+          <x:t>Tyler Gallatin</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="H33" t="inlineStr" s="17">
+        <x:is>
+          <x:t>Hold</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="I33" t="inlineStr" s="19">
+        <x:is>
+          <x:t>CS - HVAC - Service - 12</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="J33" t="inlineStr" s="21">
+        <x:is>
+          <x:t>Timberwalk Association Inc</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="K33" s="23">
+        <x:v>46102</x:v>
+      </x:c>
+      <x:c r="L33" s="25">
+        <x:v>46102</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="34">
+      <x:c r="A34" t="inlineStr" s="3">
+        <x:is>
+          <x:t>HC - Return to Repair</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B34" t="n" s="5">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="C34" t="inlineStr" s="7">
+        <x:is>
+          <x:t>5 YEAR WARRANTY, 5 YEAR WARRANTY, 5 YEAR WARRANTY, 5 YEAR WARRANTY, 5 YEAR WARRANTY, 5 YEAR WARRANTY, Club Member 3 sys, Gemaire, MULTI- 3, Parts Ordered</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D34" t="inlineStr" s="9">
+        <x:is>
+          <x:t>586595677</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E34" t="inlineStr" s="11">
+        <x:is>
+          <x:t>586595677</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F34" s="13">
+        <x:v>46107</x:v>
+      </x:c>
+      <x:c r="G34" t="inlineStr" s="15">
+        <x:is>
+          <x:t>PP Alejandro Espinosa</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="H34" t="inlineStr" s="17">
+        <x:is>
+          <x:t>Hold</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="I34" t="inlineStr" s="19">
+        <x:is>
+          <x:t>PLM - HVAC - Service - 12</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="J34" t="inlineStr" s="21">
+        <x:is>
+          <x:t>Bob Lauson</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="K34" s="23">
+        <x:v>46098</x:v>
+      </x:c>
+      <x:c r="L34" s="25">
+        <x:v>46098</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="35">
+      <x:c r="A35" t="inlineStr" s="3">
+        <x:is>
+          <x:t>HC - Return to Repair</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B35" t="n" s="5">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="C35" t="inlineStr" s="7">
+        <x:is>
+          <x:t>10-Year Labor, 10-Year Labor, 10-Year Labor, 10-Year Labor, Goodman distribution , MULTI- 5, Parts Ordered, PLM, Potential Member</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D35" t="inlineStr" s="9">
+        <x:is>
+          <x:t>587266021</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E35" t="inlineStr" s="11">
+        <x:is>
+          <x:t>587266021</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F35" s="13">
+        <x:v>46107</x:v>
+      </x:c>
+      <x:c r="G35" t="inlineStr" s="15">
+        <x:is>
+          <x:t>PP Cesar Levy</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="H35" t="inlineStr" s="17">
+        <x:is>
+          <x:t>Hold</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="I35" t="inlineStr" s="19">
+        <x:is>
+          <x:t>PLM - HVAC - Service - 12</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="J35" t="inlineStr" s="21">
+        <x:is>
+          <x:t>Nevalee &amp; Paul Oneil</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="K35" s="23">
+        <x:v>46105</x:v>
+      </x:c>
+      <x:c r="L35" s="25">
+        <x:v>46105</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="36">
+      <x:c r="A36" t="inlineStr" s="3">
+        <x:is>
+          <x:t>HC - Return to Repair</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B36" t="n" s="5">
+        <x:v>1340.1</x:v>
+      </x:c>
+      <x:c r="C36" t="inlineStr" s="7">
+        <x:is>
+          <x:t>Club Member, Club Member (Additional System), Gemaire, MULTI- 3, Parts Received , PLM</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D36" t="inlineStr" s="9">
+        <x:is>
+          <x:t>587281524</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E36" t="inlineStr" s="11">
+        <x:is>
+          <x:t>587281524</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F36" s="13">
+        <x:v>46107</x:v>
+      </x:c>
+      <x:c r="G36" t="inlineStr" s="15">
+        <x:is>
+          <x:t>PP Alejandro Espinosa</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="H36" t="inlineStr" s="17">
+        <x:is>
+          <x:t>Hold</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="I36" t="inlineStr" s="19">
+        <x:is>
+          <x:t>PLM - HVAC - Service - 12</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="J36" t="inlineStr" s="21">
+        <x:is>
+          <x:t>Robert Lake</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="K36" s="23">
+        <x:v>46105</x:v>
+      </x:c>
+      <x:c r="L36" s="25">
+        <x:v>46105</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="37">
+      <x:c r="A37" t="inlineStr" s="3">
+        <x:is>
+          <x:t>HC - Return to Repair</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B37" t="n" s="5">
+        <x:v>3247.45</x:v>
+      </x:c>
+      <x:c r="C37" t="inlineStr" s="7">
+        <x:is>
+          <x:t>10-Year Labor, Club Member, Club Member 2 sys , Gemaire, Parts Received , PLM</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D37" t="inlineStr" s="9">
+        <x:is>
+          <x:t>587314216</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E37" t="inlineStr" s="11">
+        <x:is>
+          <x:t>587314216</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F37" s="13">
+        <x:v>46107</x:v>
+      </x:c>
+      <x:c r="G37" t="inlineStr" s="15">
+        <x:is>
+          <x:t>Rolin Moimeme</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="H37" t="inlineStr" s="17">
+        <x:is>
+          <x:t>Hold</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="I37" t="inlineStr" s="19">
+        <x:is>
+          <x:t>CS - HVAC - Service - 12</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="J37" t="inlineStr" s="21">
+        <x:is>
+          <x:t>FRIEDMAN, SAMANTHA</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="K37" s="23">
+        <x:v>46105</x:v>
+      </x:c>
+      <x:c r="L37" s="25">
+        <x:v>46105</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="38">
+      <x:c r="A38" t="inlineStr" s="3">
+        <x:is>
+          <x:t>HC - Return to Repair</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B38" t="n" s="5">
+        <x:v>292.95</x:v>
+      </x:c>
+      <x:c r="C38" t="inlineStr" s="7">
+        <x:is>
+          <x:t>Baker Supply, Club Member, Parts Ordered, PLM</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D38" t="inlineStr" s="9">
+        <x:is>
+          <x:t>587301961</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E38" t="inlineStr" s="11">
+        <x:is>
+          <x:t>587301961</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F38" s="13">
+        <x:v>46107</x:v>
+      </x:c>
+      <x:c r="G38" t="inlineStr" s="15">
+        <x:is>
+          <x:t>Jesse Dague</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="H38" t="inlineStr" s="17">
+        <x:is>
+          <x:t>Hold</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="I38" t="inlineStr" s="19">
+        <x:is>
+          <x:t>CS - HVAC - Service - 12</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="J38" t="inlineStr" s="21">
+        <x:is>
+          <x:t>CHACON, LERA</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="K38" s="23">
+        <x:v>46105</x:v>
+      </x:c>
+      <x:c r="L38" s="25">
+        <x:v>46105</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="39">
+      <x:c r="A39" t="n" s="4">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="B39" t="n" s="6">
+        <x:v>503.8672972972972972972972973</x:v>
+      </x:c>
+      <x:c r="C39" t="inlineStr" s="8">
         <x:is>
           <x:t/>
         </x:is>
       </x:c>
-      <x:c r="D29" t="n" s="10">
-        <x:v>27</x:v>
-      </x:c>
-      <x:c r="E29" t="inlineStr" s="12">
+      <x:c r="D39" t="n" s="10">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="E39" t="inlineStr" s="12">
         <x:is>
           <x:t/>
         </x:is>
       </x:c>
-      <x:c r="F29" s="14">
+      <x:c r="F39" s="14">
         <x:v/>
       </x:c>
-      <x:c r="G29" t="inlineStr" s="16">
+      <x:c r="G39" t="inlineStr" s="16">
         <x:is>
           <x:t/>
         </x:is>
       </x:c>
-      <x:c r="H29" t="inlineStr" s="18">
+      <x:c r="H39" t="inlineStr" s="18">
         <x:is>
           <x:t/>
         </x:is>
       </x:c>
-      <x:c r="I29" t="inlineStr" s="20">
+      <x:c r="I39" t="inlineStr" s="20">
         <x:is>
           <x:t/>
         </x:is>
       </x:c>
-      <x:c r="J29" t="inlineStr" s="22">
+      <x:c r="J39" t="inlineStr" s="22">
         <x:is>
           <x:t/>
         </x:is>
       </x:c>
-      <x:c r="K29" s="24">
+      <x:c r="K39" s="24">
         <x:v/>
       </x:c>
-      <x:c r="L29" s="26">
+      <x:c r="L39" s="26">
         <x:v/>
       </x:c>
     </x:row>
@@ -1702,7 +2242,7 @@
       </x:c>
       <x:c r="B2" t="inlineStr" s="28">
         <x:is>
-          <x:t>03/25/25 - 03/25/26</x:t>
+          <x:t>03/26/25 - 03/26/26</x:t>
         </x:is>
       </x:c>
     </x:row>
@@ -1768,7 +2308,7 @@
     <x:mergeCell ref="A8:B8"/>
   </x:mergeCells>
   <x:hyperlinks>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A8" r:id="hyperlinkId1" location="/new/reports/459565681?DateType=3&amp;BusinessUnitId=2415185%2C2415187%2C15775258%2C2415186%2C2415190%2C182981963%2C182981958%2C182981961%2C182981957&amp;IncludeAdjustmentInvoices=false&amp;IsScheduling=True&amp;From=2025-03-25&amp;To=2026-03-25" display="View Report"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A8" r:id="hyperlinkId1" location="/new/reports/459565681?DateType=3&amp;BusinessUnitId=2415185%2C2415187%2C15775258%2C2415186%2C2415190%2C182981963%2C182981958%2C182981961%2C182981957&amp;IncludeAdjustmentInvoices=false&amp;IsScheduling=True&amp;From=2025-03-26&amp;To=2026-03-26" display="View Report"/>
   </x:hyperlinks>
 </x:worksheet>
 </file>
--- a/data/parts_report_past.xlsx
+++ b/data/parts_report_past.xlsx
@@ -5,8 +5,8 @@
     <x:workbookView/>
   </x:bookViews>
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Re9ec0da196c2412e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Filters" sheetId="2" r:id="Rd31b711acc03497b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R09a54d20f48c4ab0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Filters" sheetId="2" r:id="Rbbf377f01dbe4108"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -444,21 +444,21 @@
         </x:is>
       </x:c>
       <x:c r="B7" t="n" s="5">
-        <x:v>1241.16</x:v>
+        <x:v>339.51</x:v>
       </x:c>
       <x:c r="C7" t="inlineStr" s="7">
         <x:is>
-          <x:t>Club Member, Parts Received , York Supply </x:t>
+          <x:t>Club Member, Parts Received , PLM</x:t>
         </x:is>
       </x:c>
       <x:c r="D7" t="inlineStr" s="9">
         <x:is>
-          <x:t>583619842</x:t>
+          <x:t>586073723</x:t>
         </x:is>
       </x:c>
       <x:c r="E7" t="inlineStr" s="11">
         <x:is>
-          <x:t>583619842</x:t>
+          <x:t>586073723</x:t>
         </x:is>
       </x:c>
       <x:c r="F7" s="13">
@@ -466,7 +466,7 @@
       </x:c>
       <x:c r="G7" t="inlineStr" s="15">
         <x:is>
-          <x:t>Jesse Dague</x:t>
+          <x:t>PP Jacques Constant</x:t>
         </x:is>
       </x:c>
       <x:c r="H7" t="inlineStr" s="17">
@@ -476,19 +476,19 @@
       </x:c>
       <x:c r="I7" t="inlineStr" s="19">
         <x:is>
-          <x:t>CS - HVAC - Service - 12</x:t>
+          <x:t>PLM - HVAC - Service - 12</x:t>
         </x:is>
       </x:c>
       <x:c r="J7" t="inlineStr" s="21">
         <x:is>
-          <x:t>Cara Peckens</x:t>
+          <x:t>Catherin Miller </x:t>
         </x:is>
       </x:c>
       <x:c r="K7" s="23">
-        <x:v>46073</x:v>
+        <x:v>46093</x:v>
       </x:c>
       <x:c r="L7" s="25">
-        <x:v>46073</x:v>
+        <x:v>46093</x:v>
       </x:c>
     </x:row>
     <x:row r="8">
@@ -498,29 +498,29 @@
         </x:is>
       </x:c>
       <x:c r="B8" t="n" s="5">
-        <x:v>339.51</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="C8" t="inlineStr" s="7">
         <x:is>
-          <x:t>Club Member, Parts Received , PLM</x:t>
+          <x:t>10-Year Labor, 5 YEAR WARRANTY, 5 YEAR WARRANTY, 5 YEAR WARRANTY, Club Member, Goodman distribution , Parts Received </x:t>
         </x:is>
       </x:c>
       <x:c r="D8" t="inlineStr" s="9">
         <x:is>
-          <x:t>586073723</x:t>
+          <x:t>584259475</x:t>
         </x:is>
       </x:c>
       <x:c r="E8" t="inlineStr" s="11">
         <x:is>
-          <x:t>586073723</x:t>
+          <x:t>584259475</x:t>
         </x:is>
       </x:c>
       <x:c r="F8" s="13">
-        <x:v>46093</x:v>
+        <x:v>46094</x:v>
       </x:c>
       <x:c r="G8" t="inlineStr" s="15">
         <x:is>
-          <x:t>PP Jacques Constant</x:t>
+          <x:t>Bruce Coe</x:t>
         </x:is>
       </x:c>
       <x:c r="H8" t="inlineStr" s="17">
@@ -535,14 +535,14 @@
       </x:c>
       <x:c r="J8" t="inlineStr" s="21">
         <x:is>
-          <x:t>Catherin Miller </x:t>
+          <x:t>Barb Lois</x:t>
         </x:is>
       </x:c>
       <x:c r="K8" s="23">
-        <x:v>46093</x:v>
+        <x:v>46077</x:v>
       </x:c>
       <x:c r="L8" s="25">
-        <x:v>46093</x:v>
+        <x:v>46077</x:v>
       </x:c>
     </x:row>
     <x:row r="9">
@@ -552,29 +552,29 @@
         </x:is>
       </x:c>
       <x:c r="B9" t="n" s="5">
-        <x:v>0</x:v>
+        <x:v>1282.5</x:v>
       </x:c>
       <x:c r="C9" t="inlineStr" s="7">
         <x:is>
-          <x:t>10-Year Labor, 5 YEAR WARRANTY, 5 YEAR WARRANTY, 5 YEAR WARRANTY, Club Member, Goodman distribution , Parts Received </x:t>
+          <x:t>Club Member, Club Member (Additional System), Gemaire, Parts Received , PLM</x:t>
         </x:is>
       </x:c>
       <x:c r="D9" t="inlineStr" s="9">
         <x:is>
-          <x:t>584259475</x:t>
+          <x:t>586047631</x:t>
         </x:is>
       </x:c>
       <x:c r="E9" t="inlineStr" s="11">
         <x:is>
-          <x:t>584259475</x:t>
+          <x:t>586047631</x:t>
         </x:is>
       </x:c>
       <x:c r="F9" s="13">
-        <x:v>46094</x:v>
+        <x:v>46097</x:v>
       </x:c>
       <x:c r="G9" t="inlineStr" s="15">
         <x:is>
-          <x:t>Bruce Coe</x:t>
+          <x:t>PP Barrington Wilson</x:t>
         </x:is>
       </x:c>
       <x:c r="H9" t="inlineStr" s="17">
@@ -589,14 +589,14 @@
       </x:c>
       <x:c r="J9" t="inlineStr" s="21">
         <x:is>
-          <x:t>Barb Lois</x:t>
+          <x:t>MACLACHLAN, DAN</x:t>
         </x:is>
       </x:c>
       <x:c r="K9" s="23">
-        <x:v>46077</x:v>
+        <x:v>46092</x:v>
       </x:c>
       <x:c r="L9" s="25">
-        <x:v>46077</x:v>
+        <x:v>46092</x:v>
       </x:c>
     </x:row>
     <x:row r="10">
@@ -606,29 +606,29 @@
         </x:is>
       </x:c>
       <x:c r="B10" t="n" s="5">
-        <x:v>1282.5</x:v>
+        <x:v>292.95</x:v>
       </x:c>
       <x:c r="C10" t="inlineStr" s="7">
         <x:is>
-          <x:t>Club Member, Club Member (Additional System), Gemaire, Parts Received , PLM</x:t>
+          <x:t>Club Member, Gemaire, PSL Zone 4</x:t>
         </x:is>
       </x:c>
       <x:c r="D10" t="inlineStr" s="9">
         <x:is>
-          <x:t>586047631</x:t>
+          <x:t>586702574</x:t>
         </x:is>
       </x:c>
       <x:c r="E10" t="inlineStr" s="11">
         <x:is>
-          <x:t>586047631</x:t>
+          <x:t>586702574</x:t>
         </x:is>
       </x:c>
       <x:c r="F10" s="13">
-        <x:v>46097</x:v>
+        <x:v>46099</x:v>
       </x:c>
       <x:c r="G10" t="inlineStr" s="15">
         <x:is>
-          <x:t>PP Barrington Wilson</x:t>
+          <x:t>Jesse Dague</x:t>
         </x:is>
       </x:c>
       <x:c r="H10" t="inlineStr" s="17">
@@ -638,19 +638,19 @@
       </x:c>
       <x:c r="I10" t="inlineStr" s="19">
         <x:is>
-          <x:t>PLM - HVAC - Service - 12</x:t>
+          <x:t>CS - HVAC - Service - 12</x:t>
         </x:is>
       </x:c>
       <x:c r="J10" t="inlineStr" s="21">
         <x:is>
-          <x:t>MACLACHLAN, DAN</x:t>
+          <x:t>PAT WHELAN</x:t>
         </x:is>
       </x:c>
       <x:c r="K10" s="23">
-        <x:v>46092</x:v>
+        <x:v>46099</x:v>
       </x:c>
       <x:c r="L10" s="25">
-        <x:v>46092</x:v>
+        <x:v>46099</x:v>
       </x:c>
     </x:row>
     <x:row r="11">
@@ -660,29 +660,29 @@
         </x:is>
       </x:c>
       <x:c r="B11" t="n" s="5">
-        <x:v>292.95</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="C11" t="inlineStr" s="7">
         <x:is>
-          <x:t>Club Member, Gemaire, PSL Zone 4</x:t>
+          <x:t>5 YEAR WARRANTY, 5 YEAR WARRANTY, 5 YEAR WARRANTY, 5 YEAR WARRANTY, Club Member, Goodman distribution , Parts Received </x:t>
         </x:is>
       </x:c>
       <x:c r="D11" t="inlineStr" s="9">
         <x:is>
-          <x:t>586702574</x:t>
+          <x:t>586815067</x:t>
         </x:is>
       </x:c>
       <x:c r="E11" t="inlineStr" s="11">
         <x:is>
-          <x:t>586702574</x:t>
+          <x:t>586815067</x:t>
         </x:is>
       </x:c>
       <x:c r="F11" s="13">
-        <x:v>46099</x:v>
+        <x:v>46104</x:v>
       </x:c>
       <x:c r="G11" t="inlineStr" s="15">
         <x:is>
-          <x:t>Jesse Dague</x:t>
+          <x:t>Xavier Mateo</x:t>
         </x:is>
       </x:c>
       <x:c r="H11" t="inlineStr" s="17">
@@ -697,14 +697,14 @@
       </x:c>
       <x:c r="J11" t="inlineStr" s="21">
         <x:is>
-          <x:t>PAT WHELAN</x:t>
+          <x:t>Christine Semenza</x:t>
         </x:is>
       </x:c>
       <x:c r="K11" s="23">
-        <x:v>46099</x:v>
+        <x:v>46100</x:v>
       </x:c>
       <x:c r="L11" s="25">
-        <x:v>46099</x:v>
+        <x:v>46100</x:v>
       </x:c>
     </x:row>
     <x:row r="12">
@@ -718,17 +718,17 @@
       </x:c>
       <x:c r="C12" t="inlineStr" s="7">
         <x:is>
-          <x:t>5 YEAR WARRANTY, 5 YEAR WARRANTY, 5 YEAR WARRANTY, 5 YEAR WARRANTY, Club Member, Goodman distribution , Parts Received </x:t>
+          <x:t>Carrier enterprise, Club Member, Parts Received </x:t>
         </x:is>
       </x:c>
       <x:c r="D12" t="inlineStr" s="9">
         <x:is>
-          <x:t>586815067</x:t>
+          <x:t>586266511</x:t>
         </x:is>
       </x:c>
       <x:c r="E12" t="inlineStr" s="11">
         <x:is>
-          <x:t>586815067</x:t>
+          <x:t>586266511</x:t>
         </x:is>
       </x:c>
       <x:c r="F12" s="13">
@@ -736,7 +736,7 @@
       </x:c>
       <x:c r="G12" t="inlineStr" s="15">
         <x:is>
-          <x:t>Xavier Mateo</x:t>
+          <x:t/>
         </x:is>
       </x:c>
       <x:c r="H12" t="inlineStr" s="17">
@@ -751,14 +751,14 @@
       </x:c>
       <x:c r="J12" t="inlineStr" s="21">
         <x:is>
-          <x:t>Christine Semenza</x:t>
+          <x:t>Ruth Sapper</x:t>
         </x:is>
       </x:c>
       <x:c r="K12" s="23">
-        <x:v>46100</x:v>
+        <x:v>46094</x:v>
       </x:c>
       <x:c r="L12" s="25">
-        <x:v>46100</x:v>
+        <x:v>46094</x:v>
       </x:c>
     </x:row>
     <x:row r="13">
@@ -768,21 +768,21 @@
         </x:is>
       </x:c>
       <x:c r="B13" t="n" s="5">
-        <x:v>0</x:v>
+        <x:v>1100</x:v>
       </x:c>
       <x:c r="C13" t="inlineStr" s="7">
         <x:is>
-          <x:t>Carrier enterprise, Club Member, Parts Received </x:t>
+          <x:t>Club Member, Parts Received , PLM</x:t>
         </x:is>
       </x:c>
       <x:c r="D13" t="inlineStr" s="9">
         <x:is>
-          <x:t>586266511</x:t>
+          <x:t>587202433</x:t>
         </x:is>
       </x:c>
       <x:c r="E13" t="inlineStr" s="11">
         <x:is>
-          <x:t>586266511</x:t>
+          <x:t>587202433</x:t>
         </x:is>
       </x:c>
       <x:c r="F13" s="13">
@@ -790,7 +790,7 @@
       </x:c>
       <x:c r="G13" t="inlineStr" s="15">
         <x:is>
-          <x:t/>
+          <x:t>PP Braxton Patterson </x:t>
         </x:is>
       </x:c>
       <x:c r="H13" t="inlineStr" s="17">
@@ -800,19 +800,19 @@
       </x:c>
       <x:c r="I13" t="inlineStr" s="19">
         <x:is>
-          <x:t>CS - HVAC - Service - 12</x:t>
+          <x:t>PLM - HVAC - Service - 12</x:t>
         </x:is>
       </x:c>
       <x:c r="J13" t="inlineStr" s="21">
         <x:is>
-          <x:t>Ruth Sapper</x:t>
+          <x:t>CHRISTOPHER KENNEDY</x:t>
         </x:is>
       </x:c>
       <x:c r="K13" s="23">
-        <x:v>46094</x:v>
+        <x:v>46104</x:v>
       </x:c>
       <x:c r="L13" s="25">
-        <x:v>46094</x:v>
+        <x:v>46104</x:v>
       </x:c>
     </x:row>
     <x:row r="14">
@@ -822,29 +822,29 @@
         </x:is>
       </x:c>
       <x:c r="B14" t="n" s="5">
-        <x:v>1100</x:v>
+        <x:v>691.98</x:v>
       </x:c>
       <x:c r="C14" t="inlineStr" s="7">
         <x:is>
-          <x:t>Club Member, Parts Received , PLM</x:t>
+          <x:t>Club Member, Parts Received , Replacement Opportunity</x:t>
         </x:is>
       </x:c>
       <x:c r="D14" t="inlineStr" s="9">
         <x:is>
-          <x:t>587202433</x:t>
+          <x:t>587248489</x:t>
         </x:is>
       </x:c>
       <x:c r="E14" t="inlineStr" s="11">
         <x:is>
-          <x:t>587202433</x:t>
+          <x:t>587248489</x:t>
         </x:is>
       </x:c>
       <x:c r="F14" s="13">
-        <x:v>46104</x:v>
+        <x:v>46105</x:v>
       </x:c>
       <x:c r="G14" t="inlineStr" s="15">
         <x:is>
-          <x:t>PP Braxton Patterson </x:t>
+          <x:t>Justin Greene</x:t>
         </x:is>
       </x:c>
       <x:c r="H14" t="inlineStr" s="17">
@@ -854,19 +854,19 @@
       </x:c>
       <x:c r="I14" t="inlineStr" s="19">
         <x:is>
-          <x:t>PLM - HVAC - Service - 12</x:t>
+          <x:t>CS - HVAC - Service - 12</x:t>
         </x:is>
       </x:c>
       <x:c r="J14" t="inlineStr" s="21">
         <x:is>
-          <x:t>CHRISTOPHER KENNEDY</x:t>
+          <x:t>Baldwin Burey</x:t>
         </x:is>
       </x:c>
       <x:c r="K14" s="23">
-        <x:v>46104</x:v>
+        <x:v>46105</x:v>
       </x:c>
       <x:c r="L14" s="25">
-        <x:v>46104</x:v>
+        <x:v>46105</x:v>
       </x:c>
     </x:row>
     <x:row r="15">
@@ -876,21 +876,21 @@
         </x:is>
       </x:c>
       <x:c r="B15" t="n" s="5">
-        <x:v>691.98</x:v>
+        <x:v>1662.36</x:v>
       </x:c>
       <x:c r="C15" t="inlineStr" s="7">
         <x:is>
-          <x:t>Club Member, Parts Received , Replacement Opportunity</x:t>
+          <x:t>Club Member, Club Member (Additional System), MULTI- 2, Parts Received </x:t>
         </x:is>
       </x:c>
       <x:c r="D15" t="inlineStr" s="9">
         <x:is>
-          <x:t>587248489</x:t>
+          <x:t>587268927</x:t>
         </x:is>
       </x:c>
       <x:c r="E15" t="inlineStr" s="11">
         <x:is>
-          <x:t>587248489</x:t>
+          <x:t>587268927</x:t>
         </x:is>
       </x:c>
       <x:c r="F15" s="13">
@@ -898,7 +898,7 @@
       </x:c>
       <x:c r="G15" t="inlineStr" s="15">
         <x:is>
-          <x:t>Justin Greene</x:t>
+          <x:t>PP Demitri Semexant</x:t>
         </x:is>
       </x:c>
       <x:c r="H15" t="inlineStr" s="17">
@@ -913,7 +913,7 @@
       </x:c>
       <x:c r="J15" t="inlineStr" s="21">
         <x:is>
-          <x:t>Baldwin Burey</x:t>
+          <x:t>Susan  Paley</x:t>
         </x:is>
       </x:c>
       <x:c r="K15" s="23">
@@ -930,21 +930,21 @@
         </x:is>
       </x:c>
       <x:c r="B16" t="n" s="5">
-        <x:v>1662.36</x:v>
+        <x:v>1615.83</x:v>
       </x:c>
       <x:c r="C16" t="inlineStr" s="7">
         <x:is>
-          <x:t>Club Member, Club Member (Additional System), MULTI- 2, Parts Received </x:t>
+          <x:t>Club Member, Parts Received </x:t>
         </x:is>
       </x:c>
       <x:c r="D16" t="inlineStr" s="9">
         <x:is>
-          <x:t>587268927</x:t>
+          <x:t>587337488</x:t>
         </x:is>
       </x:c>
       <x:c r="E16" t="inlineStr" s="11">
         <x:is>
-          <x:t>587268927</x:t>
+          <x:t>587337488</x:t>
         </x:is>
       </x:c>
       <x:c r="F16" s="13">
@@ -967,7 +967,7 @@
       </x:c>
       <x:c r="J16" t="inlineStr" s="21">
         <x:is>
-          <x:t>Susan  Paley</x:t>
+          <x:t>Sabrina Rodriguez</x:t>
         </x:is>
       </x:c>
       <x:c r="K16" s="23">
@@ -984,21 +984,21 @@
         </x:is>
       </x:c>
       <x:c r="B17" t="n" s="5">
-        <x:v>1615.83</x:v>
+        <x:v>225</x:v>
       </x:c>
       <x:c r="C17" t="inlineStr" s="7">
         <x:is>
-          <x:t>Club Member, Parts Received </x:t>
+          <x:t>12-Year Labor, 12-Year Labor, 12-Year Labor, 12-Year Labor, 12-Year Labor, Carrier enterprise, Club Member 2 sys , MULTI- 2, Parts Received , PLM</x:t>
         </x:is>
       </x:c>
       <x:c r="D17" t="inlineStr" s="9">
         <x:is>
-          <x:t>587337488</x:t>
+          <x:t>586903562</x:t>
         </x:is>
       </x:c>
       <x:c r="E17" t="inlineStr" s="11">
         <x:is>
-          <x:t>587337488</x:t>
+          <x:t>586903562</x:t>
         </x:is>
       </x:c>
       <x:c r="F17" s="13">
@@ -1006,7 +1006,7 @@
       </x:c>
       <x:c r="G17" t="inlineStr" s="15">
         <x:is>
-          <x:t>PP Demitri Semexant</x:t>
+          <x:t>PP Braxton Patterson </x:t>
         </x:is>
       </x:c>
       <x:c r="H17" t="inlineStr" s="17">
@@ -1021,14 +1021,14 @@
       </x:c>
       <x:c r="J17" t="inlineStr" s="21">
         <x:is>
-          <x:t>Sabrina Rodriguez</x:t>
+          <x:t>Ruth  Hochberg</x:t>
         </x:is>
       </x:c>
       <x:c r="K17" s="23">
-        <x:v>46105</x:v>
+        <x:v>46100</x:v>
       </x:c>
       <x:c r="L17" s="25">
-        <x:v>46105</x:v>
+        <x:v>46100</x:v>
       </x:c>
     </x:row>
     <x:row r="18">
@@ -1038,21 +1038,21 @@
         </x:is>
       </x:c>
       <x:c r="B18" t="n" s="5">
-        <x:v>462.83</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="C18" t="inlineStr" s="7">
         <x:is>
-          <x:t>Baker Supply, Club Member, Parts Ordered, PLM, Potential Membership Renewal, Residential Maintenance Agreement</x:t>
+          <x:t>10-10-10, 10-10-10, Carrier enterprise, Club Member, Parts Received , PLM</x:t>
         </x:is>
       </x:c>
       <x:c r="D18" t="inlineStr" s="9">
         <x:is>
-          <x:t>555552166</x:t>
+          <x:t>586982846</x:t>
         </x:is>
       </x:c>
       <x:c r="E18" t="inlineStr" s="11">
         <x:is>
-          <x:t>555552166</x:t>
+          <x:t>586982846</x:t>
         </x:is>
       </x:c>
       <x:c r="F18" s="13">
@@ -1060,7 +1060,7 @@
       </x:c>
       <x:c r="G18" t="inlineStr" s="15">
         <x:is>
-          <x:t>PP Cesar Levy</x:t>
+          <x:t>Rickey McClam </x:t>
         </x:is>
       </x:c>
       <x:c r="H18" t="inlineStr" s="17">
@@ -1075,14 +1075,14 @@
       </x:c>
       <x:c r="J18" t="inlineStr" s="21">
         <x:is>
-          <x:t>Wanda Betancourt</x:t>
+          <x:t>Gwyn Bonasoro</x:t>
         </x:is>
       </x:c>
       <x:c r="K18" s="23">
-        <x:v>46007</x:v>
+        <x:v>46101</x:v>
       </x:c>
       <x:c r="L18" s="25">
-        <x:v>46007</x:v>
+        <x:v>46101</x:v>
       </x:c>
     </x:row>
     <x:row r="19">
@@ -1092,21 +1092,21 @@
         </x:is>
       </x:c>
       <x:c r="B19" t="n" s="5">
-        <x:v>225</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="C19" t="inlineStr" s="7">
         <x:is>
-          <x:t>12-Year Labor, 12-Year Labor, 12-Year Labor, 12-Year Labor, 12-Year Labor, Carrier enterprise, Club Member 2 sys , MULTI- 2, Parts Received , PLM</x:t>
+          <x:t>Carrier enterprise, Parts Received , PLM, Potential Member</x:t>
         </x:is>
       </x:c>
       <x:c r="D19" t="inlineStr" s="9">
         <x:is>
-          <x:t>586903562</x:t>
+          <x:t>586835264</x:t>
         </x:is>
       </x:c>
       <x:c r="E19" t="inlineStr" s="11">
         <x:is>
-          <x:t>586903562</x:t>
+          <x:t>586835264</x:t>
         </x:is>
       </x:c>
       <x:c r="F19" s="13">
@@ -1114,7 +1114,7 @@
       </x:c>
       <x:c r="G19" t="inlineStr" s="15">
         <x:is>
-          <x:t>PP Braxton Patterson </x:t>
+          <x:t>PP Michael Chenoy</x:t>
         </x:is>
       </x:c>
       <x:c r="H19" t="inlineStr" s="17">
@@ -1124,12 +1124,12 @@
       </x:c>
       <x:c r="I19" t="inlineStr" s="19">
         <x:is>
-          <x:t>CS - HVAC - Service - 12</x:t>
+          <x:t>PLM - HVAC - Service - 12</x:t>
         </x:is>
       </x:c>
       <x:c r="J19" t="inlineStr" s="21">
         <x:is>
-          <x:t>Ruth  Hochberg</x:t>
+          <x:t>WILSON, CARA</x:t>
         </x:is>
       </x:c>
       <x:c r="K19" s="23">
@@ -1146,29 +1146,29 @@
         </x:is>
       </x:c>
       <x:c r="B20" t="n" s="5">
-        <x:v>0</x:v>
+        <x:v>689.97</x:v>
       </x:c>
       <x:c r="C20" t="inlineStr" s="7">
         <x:is>
-          <x:t>10-10-10, 10-10-10, Carrier enterprise, Club Member, Parts Received , PLM</x:t>
+          <x:t>2-YR Labor Warranty, 2-YR Labor Warranty, 2-YR Labor Warranty, Club Member, Gemaire, Parts Received </x:t>
         </x:is>
       </x:c>
       <x:c r="D20" t="inlineStr" s="9">
         <x:is>
-          <x:t>586982846</x:t>
+          <x:t>587253199</x:t>
         </x:is>
       </x:c>
       <x:c r="E20" t="inlineStr" s="11">
         <x:is>
-          <x:t>586982846</x:t>
+          <x:t>587253199</x:t>
         </x:is>
       </x:c>
       <x:c r="F20" s="13">
-        <x:v>46105</x:v>
+        <x:v>46106</x:v>
       </x:c>
       <x:c r="G20" t="inlineStr" s="15">
         <x:is>
-          <x:t>Rickey McClam </x:t>
+          <x:t>PP Barrington Wilson</x:t>
         </x:is>
       </x:c>
       <x:c r="H20" t="inlineStr" s="17">
@@ -1178,19 +1178,19 @@
       </x:c>
       <x:c r="I20" t="inlineStr" s="19">
         <x:is>
-          <x:t>PLM - HVAC - Service - 12</x:t>
+          <x:t>CS - HVAC - Service - 12</x:t>
         </x:is>
       </x:c>
       <x:c r="J20" t="inlineStr" s="21">
         <x:is>
-          <x:t>Gwyn Bonasoro</x:t>
+          <x:t>Dane Lyons</x:t>
         </x:is>
       </x:c>
       <x:c r="K20" s="23">
-        <x:v>46101</x:v>
+        <x:v>46105</x:v>
       </x:c>
       <x:c r="L20" s="25">
-        <x:v>46101</x:v>
+        <x:v>46105</x:v>
       </x:c>
     </x:row>
     <x:row r="21">
@@ -1200,29 +1200,29 @@
         </x:is>
       </x:c>
       <x:c r="B21" t="n" s="5">
-        <x:v>0</x:v>
+        <x:v>722.79</x:v>
       </x:c>
       <x:c r="C21" t="inlineStr" s="7">
         <x:is>
-          <x:t>Carrier enterprise, Parts Received , PLM, Potential Member</x:t>
+          <x:t>Baker Supply, Parts Ordered, PLM, Potential Member</x:t>
         </x:is>
       </x:c>
       <x:c r="D21" t="inlineStr" s="9">
         <x:is>
-          <x:t>586835264</x:t>
+          <x:t>459781920</x:t>
         </x:is>
       </x:c>
       <x:c r="E21" t="inlineStr" s="11">
         <x:is>
-          <x:t>586835264</x:t>
+          <x:t>459781920</x:t>
         </x:is>
       </x:c>
       <x:c r="F21" s="13">
-        <x:v>46105</x:v>
+        <x:v>46106</x:v>
       </x:c>
       <x:c r="G21" t="inlineStr" s="15">
         <x:is>
-          <x:t>PP Michael Chenoy</x:t>
+          <x:t>PLM-Quentin Stewart</x:t>
         </x:is>
       </x:c>
       <x:c r="H21" t="inlineStr" s="17">
@@ -1237,14 +1237,14 @@
       </x:c>
       <x:c r="J21" t="inlineStr" s="21">
         <x:is>
-          <x:t>WILSON, CARA</x:t>
+          <x:t>Gluck Carolyn</x:t>
         </x:is>
       </x:c>
       <x:c r="K21" s="23">
-        <x:v>46100</x:v>
+        <x:v>45726</x:v>
       </x:c>
       <x:c r="L21" s="25">
-        <x:v>46100</x:v>
+        <x:v>45726</x:v>
       </x:c>
     </x:row>
     <x:row r="22">
@@ -1258,25 +1258,25 @@
       </x:c>
       <x:c r="C22" t="inlineStr" s="7">
         <x:is>
-          <x:t>Club Member, Need to order part (NTO)</x:t>
+          <x:t>Carrier enterprise, Club Member, Parts Received </x:t>
         </x:is>
       </x:c>
       <x:c r="D22" t="inlineStr" s="9">
         <x:is>
-          <x:t>587448096</x:t>
+          <x:t>586083412</x:t>
         </x:is>
       </x:c>
       <x:c r="E22" t="inlineStr" s="11">
         <x:is>
-          <x:t>587448096</x:t>
+          <x:t>586083412</x:t>
         </x:is>
       </x:c>
       <x:c r="F22" s="13">
-        <x:v>46106</x:v>
+        <x:v>46107</x:v>
       </x:c>
       <x:c r="G22" t="inlineStr" s="15">
         <x:is>
-          <x:t/>
+          <x:t>Michael Kertesz </x:t>
         </x:is>
       </x:c>
       <x:c r="H22" t="inlineStr" s="17">
@@ -1286,19 +1286,19 @@
       </x:c>
       <x:c r="I22" t="inlineStr" s="19">
         <x:is>
-          <x:t>PLM - HVAC - Service - 12</x:t>
+          <x:t>CS - HVAC - Service - 12</x:t>
         </x:is>
       </x:c>
       <x:c r="J22" t="inlineStr" s="21">
         <x:is>
-          <x:t>Cassandra Sexton</x:t>
+          <x:t>Gregory  Tsesler</x:t>
         </x:is>
       </x:c>
       <x:c r="K22" s="23">
-        <x:v>46106</x:v>
+        <x:v>46093</x:v>
       </x:c>
       <x:c r="L22" s="25">
-        <x:v>46106</x:v>
+        <x:v>46093</x:v>
       </x:c>
     </x:row>
     <x:row r="23">
@@ -1312,25 +1312,25 @@
       </x:c>
       <x:c r="C23" t="inlineStr" s="7">
         <x:is>
-          <x:t>Club Member, Need to order part (NTO)</x:t>
+          <x:t>10-10-10, Club Member, Parts Ordered, Trane Supply</x:t>
         </x:is>
       </x:c>
       <x:c r="D23" t="inlineStr" s="9">
         <x:is>
-          <x:t>587375373</x:t>
+          <x:t>586864800</x:t>
         </x:is>
       </x:c>
       <x:c r="E23" t="inlineStr" s="11">
         <x:is>
-          <x:t>587375373</x:t>
+          <x:t>586864800</x:t>
         </x:is>
       </x:c>
       <x:c r="F23" s="13">
-        <x:v>46106</x:v>
+        <x:v>46107</x:v>
       </x:c>
       <x:c r="G23" t="inlineStr" s="15">
         <x:is>
-          <x:t>PP Ryley Johnson</x:t>
+          <x:t>PP David Escobar</x:t>
         </x:is>
       </x:c>
       <x:c r="H23" t="inlineStr" s="17">
@@ -1345,14 +1345,14 @@
       </x:c>
       <x:c r="J23" t="inlineStr" s="21">
         <x:is>
-          <x:t>Laurie Kline</x:t>
+          <x:t>Hope Gadea</x:t>
         </x:is>
       </x:c>
       <x:c r="K23" s="23">
-        <x:v>46106</x:v>
+        <x:v>46100</x:v>
       </x:c>
       <x:c r="L23" s="25">
-        <x:v>46106</x:v>
+        <x:v>46100</x:v>
       </x:c>
     </x:row>
     <x:row r="24">
@@ -1362,29 +1362,29 @@
         </x:is>
       </x:c>
       <x:c r="B24" t="n" s="5">
-        <x:v>710.85</x:v>
+        <x:v>294.96</x:v>
       </x:c>
       <x:c r="C24" t="inlineStr" s="7">
         <x:is>
-          <x:t>Gemaire, Parts Ordered, Potential Member</x:t>
+          <x:t>10-10-10, 10-10-10, Club Member, Club Member (Additional System), MULTI- 2, Parts Ordered, Trane Supply</x:t>
         </x:is>
       </x:c>
       <x:c r="D24" t="inlineStr" s="9">
         <x:is>
-          <x:t>580795172</x:t>
+          <x:t>554624809</x:t>
         </x:is>
       </x:c>
       <x:c r="E24" t="inlineStr" s="11">
         <x:is>
-          <x:t>580795172</x:t>
+          <x:t>554624809</x:t>
         </x:is>
       </x:c>
       <x:c r="F24" s="13">
-        <x:v>46106</x:v>
+        <x:v>46107</x:v>
       </x:c>
       <x:c r="G24" t="inlineStr" s="15">
         <x:is>
-          <x:t>PP Alejandro Espinosa</x:t>
+          <x:t>PP Carlos Machado</x:t>
         </x:is>
       </x:c>
       <x:c r="H24" t="inlineStr" s="17">
@@ -1399,14 +1399,14 @@
       </x:c>
       <x:c r="J24" t="inlineStr" s="21">
         <x:is>
-          <x:t>Paul Serota</x:t>
+          <x:t>Michael &amp; Delle Lenzen</x:t>
         </x:is>
       </x:c>
       <x:c r="K24" s="23">
-        <x:v>46054</x:v>
+        <x:v>45996</x:v>
       </x:c>
       <x:c r="L24" s="25">
-        <x:v>46054</x:v>
+        <x:v>45996</x:v>
       </x:c>
     </x:row>
     <x:row r="25">
@@ -1416,51 +1416,51 @@
         </x:is>
       </x:c>
       <x:c r="B25" t="n" s="5">
-        <x:v>689.97</x:v>
+        <x:v>344.21</x:v>
       </x:c>
       <x:c r="C25" t="inlineStr" s="7">
         <x:is>
-          <x:t>2-YR Labor Warranty, 2-YR Labor Warranty, 2-YR Labor Warranty, Club Member, Gemaire, Parts Received </x:t>
+          <x:t>10-10-10, Club Member, Parts Received </x:t>
         </x:is>
       </x:c>
       <x:c r="D25" t="inlineStr" s="9">
         <x:is>
-          <x:t>587253199</x:t>
+          <x:t>587448160</x:t>
         </x:is>
       </x:c>
       <x:c r="E25" t="inlineStr" s="11">
         <x:is>
-          <x:t>587253199</x:t>
+          <x:t>587448160</x:t>
         </x:is>
       </x:c>
       <x:c r="F25" s="13">
+        <x:v>46107</x:v>
+      </x:c>
+      <x:c r="G25" t="inlineStr" s="15">
+        <x:is>
+          <x:t>Rolin Moimeme</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="H25" t="inlineStr" s="17">
+        <x:is>
+          <x:t>Hold</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="I25" t="inlineStr" s="19">
+        <x:is>
+          <x:t>CS - HVAC - Service - 12</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="J25" t="inlineStr" s="21">
+        <x:is>
+          <x:t>Rene Ceusters</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="K25" s="23">
         <x:v>46106</x:v>
       </x:c>
-      <x:c r="G25" t="inlineStr" s="15">
-        <x:is>
-          <x:t>PP Barrington Wilson</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="H25" t="inlineStr" s="17">
-        <x:is>
-          <x:t>Hold</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="I25" t="inlineStr" s="19">
-        <x:is>
-          <x:t>CS - HVAC - Service - 12</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="J25" t="inlineStr" s="21">
-        <x:is>
-          <x:t>Dane Lyons</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="K25" s="23">
-        <x:v>46105</x:v>
-      </x:c>
       <x:c r="L25" s="25">
-        <x:v>46105</x:v>
+        <x:v>46106</x:v>
       </x:c>
     </x:row>
     <x:row r="26">
@@ -1474,21 +1474,21 @@
       </x:c>
       <x:c r="C26" t="inlineStr" s="7">
         <x:is>
-          <x:t>10-Year Labor, Carrier enterprise, Club Member, Parts Received , PLM</x:t>
+          <x:t>Club Member, LW- 2 YEAR LABOR, Parts Ordered, Trane Supply</x:t>
         </x:is>
       </x:c>
       <x:c r="D26" t="inlineStr" s="9">
         <x:is>
-          <x:t>587167128</x:t>
+          <x:t>587077196</x:t>
         </x:is>
       </x:c>
       <x:c r="E26" t="inlineStr" s="11">
         <x:is>
-          <x:t>587167128</x:t>
+          <x:t>587077196</x:t>
         </x:is>
       </x:c>
       <x:c r="F26" s="13">
-        <x:v>46106</x:v>
+        <x:v>46107</x:v>
       </x:c>
       <x:c r="G26" t="inlineStr" s="15">
         <x:is>
@@ -1502,19 +1502,19 @@
       </x:c>
       <x:c r="I26" t="inlineStr" s="19">
         <x:is>
-          <x:t>PLM - HVAC - Service - 12</x:t>
+          <x:t>CS - HVAC - Service - 12</x:t>
         </x:is>
       </x:c>
       <x:c r="J26" t="inlineStr" s="21">
         <x:is>
-          <x:t>Marsha &amp; David Gordon</x:t>
+          <x:t>Timberwalk Association Inc</x:t>
         </x:is>
       </x:c>
       <x:c r="K26" s="23">
-        <x:v>46104</x:v>
+        <x:v>46102</x:v>
       </x:c>
       <x:c r="L26" s="25">
-        <x:v>46104</x:v>
+        <x:v>46102</x:v>
       </x:c>
     </x:row>
     <x:row r="27">
@@ -1524,29 +1524,29 @@
         </x:is>
       </x:c>
       <x:c r="B27" t="n" s="5">
-        <x:v>945.4</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="C27" t="inlineStr" s="7">
         <x:is>
-          <x:t>Club Member, Need to order part (NTO), PLM</x:t>
+          <x:t>5 YEAR WARRANTY, 5 YEAR WARRANTY, 5 YEAR WARRANTY, 5 YEAR WARRANTY, 5 YEAR WARRANTY, 5 YEAR WARRANTY, Club Member 3 sys, Gemaire, MULTI- 3, Parts Ordered</x:t>
         </x:is>
       </x:c>
       <x:c r="D27" t="inlineStr" s="9">
         <x:is>
-          <x:t>587403893</x:t>
+          <x:t>586595677</x:t>
         </x:is>
       </x:c>
       <x:c r="E27" t="inlineStr" s="11">
         <x:is>
-          <x:t>587403893</x:t>
+          <x:t>586595677</x:t>
         </x:is>
       </x:c>
       <x:c r="F27" s="13">
-        <x:v>46106</x:v>
+        <x:v>46107</x:v>
       </x:c>
       <x:c r="G27" t="inlineStr" s="15">
         <x:is>
-          <x:t>Rolin Moimeme</x:t>
+          <x:t>PP Alejandro Espinosa</x:t>
         </x:is>
       </x:c>
       <x:c r="H27" t="inlineStr" s="17">
@@ -1561,14 +1561,14 @@
       </x:c>
       <x:c r="J27" t="inlineStr" s="21">
         <x:is>
-          <x:t>WALKER, CAMERON</x:t>
+          <x:t>Bob Lauson</x:t>
         </x:is>
       </x:c>
       <x:c r="K27" s="23">
-        <x:v>46106</x:v>
+        <x:v>46098</x:v>
       </x:c>
       <x:c r="L27" s="25">
-        <x:v>46106</x:v>
+        <x:v>46098</x:v>
       </x:c>
     </x:row>
     <x:row r="28">
@@ -1578,29 +1578,29 @@
         </x:is>
       </x:c>
       <x:c r="B28" t="n" s="5">
-        <x:v>722.79</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="C28" t="inlineStr" s="7">
         <x:is>
-          <x:t>Baker Supply, Parts Ordered, PLM, Potential Member</x:t>
+          <x:t>10-Year Labor, 10-Year Labor, 10-Year Labor, 10-Year Labor, Goodman distribution , MULTI- 5, Parts Ordered, PLM, Potential Member</x:t>
         </x:is>
       </x:c>
       <x:c r="D28" t="inlineStr" s="9">
         <x:is>
-          <x:t>459781920</x:t>
+          <x:t>587266021</x:t>
         </x:is>
       </x:c>
       <x:c r="E28" t="inlineStr" s="11">
         <x:is>
-          <x:t>459781920</x:t>
+          <x:t>587266021</x:t>
         </x:is>
       </x:c>
       <x:c r="F28" s="13">
-        <x:v>46106</x:v>
+        <x:v>46107</x:v>
       </x:c>
       <x:c r="G28" t="inlineStr" s="15">
         <x:is>
-          <x:t>PLM-Quentin Stewart</x:t>
+          <x:t>PP Cesar Levy</x:t>
         </x:is>
       </x:c>
       <x:c r="H28" t="inlineStr" s="17">
@@ -1615,14 +1615,14 @@
       </x:c>
       <x:c r="J28" t="inlineStr" s="21">
         <x:is>
-          <x:t>Gluck Carolyn</x:t>
+          <x:t>Nevalee &amp; Paul Oneil</x:t>
         </x:is>
       </x:c>
       <x:c r="K28" s="23">
-        <x:v>45726</x:v>
+        <x:v>46105</x:v>
       </x:c>
       <x:c r="L28" s="25">
-        <x:v>45726</x:v>
+        <x:v>46105</x:v>
       </x:c>
     </x:row>
     <x:row r="29">
@@ -1632,21 +1632,21 @@
         </x:is>
       </x:c>
       <x:c r="B29" t="n" s="5">
-        <x:v>0</x:v>
+        <x:v>1340.1</x:v>
       </x:c>
       <x:c r="C29" t="inlineStr" s="7">
         <x:is>
-          <x:t>Carrier enterprise, Club Member, Parts Received </x:t>
+          <x:t>Club Member, Club Member (Additional System), Gemaire, MULTI- 3, Parts Received , PLM</x:t>
         </x:is>
       </x:c>
       <x:c r="D29" t="inlineStr" s="9">
         <x:is>
-          <x:t>586083412</x:t>
+          <x:t>587281524</x:t>
         </x:is>
       </x:c>
       <x:c r="E29" t="inlineStr" s="11">
         <x:is>
-          <x:t>586083412</x:t>
+          <x:t>587281524</x:t>
         </x:is>
       </x:c>
       <x:c r="F29" s="13">
@@ -1654,7 +1654,7 @@
       </x:c>
       <x:c r="G29" t="inlineStr" s="15">
         <x:is>
-          <x:t>Michael Kertesz </x:t>
+          <x:t>PP Alejandro Espinosa</x:t>
         </x:is>
       </x:c>
       <x:c r="H29" t="inlineStr" s="17">
@@ -1664,19 +1664,19 @@
       </x:c>
       <x:c r="I29" t="inlineStr" s="19">
         <x:is>
-          <x:t>CS - HVAC - Service - 12</x:t>
+          <x:t>PLM - HVAC - Service - 12</x:t>
         </x:is>
       </x:c>
       <x:c r="J29" t="inlineStr" s="21">
         <x:is>
-          <x:t>Gregory  Tsesler</x:t>
+          <x:t>Robert Lake</x:t>
         </x:is>
       </x:c>
       <x:c r="K29" s="23">
-        <x:v>46093</x:v>
+        <x:v>46105</x:v>
       </x:c>
       <x:c r="L29" s="25">
-        <x:v>46093</x:v>
+        <x:v>46105</x:v>
       </x:c>
     </x:row>
     <x:row r="30">
@@ -1686,21 +1686,21 @@
         </x:is>
       </x:c>
       <x:c r="B30" t="n" s="5">
-        <x:v>0</x:v>
+        <x:v>1536.7</x:v>
       </x:c>
       <x:c r="C30" t="inlineStr" s="7">
         <x:is>
-          <x:t>10-10-10, Club Member, Parts Ordered, Trane Supply</x:t>
+          <x:t>Need to order part (NTO), PLM</x:t>
         </x:is>
       </x:c>
       <x:c r="D30" t="inlineStr" s="9">
         <x:is>
-          <x:t>586864800</x:t>
+          <x:t>587489793</x:t>
         </x:is>
       </x:c>
       <x:c r="E30" t="inlineStr" s="11">
         <x:is>
-          <x:t>586864800</x:t>
+          <x:t>587489793</x:t>
         </x:is>
       </x:c>
       <x:c r="F30" s="13">
@@ -1708,7 +1708,7 @@
       </x:c>
       <x:c r="G30" t="inlineStr" s="15">
         <x:is>
-          <x:t>PP David Escobar</x:t>
+          <x:t>PP Tyriq McCall</x:t>
         </x:is>
       </x:c>
       <x:c r="H30" t="inlineStr" s="17">
@@ -1718,19 +1718,19 @@
       </x:c>
       <x:c r="I30" t="inlineStr" s="19">
         <x:is>
-          <x:t>CS - HVAC - Service - 12</x:t>
+          <x:t>PLM - HVAC - Service - 12</x:t>
         </x:is>
       </x:c>
       <x:c r="J30" t="inlineStr" s="21">
         <x:is>
-          <x:t>Hope Gadea</x:t>
+          <x:t>PASAMI, LLC</x:t>
         </x:is>
       </x:c>
       <x:c r="K30" s="23">
-        <x:v>46100</x:v>
+        <x:v>46107</x:v>
       </x:c>
       <x:c r="L30" s="25">
-        <x:v>46100</x:v>
+        <x:v>46107</x:v>
       </x:c>
     </x:row>
     <x:row r="31">
@@ -1740,21 +1740,21 @@
         </x:is>
       </x:c>
       <x:c r="B31" t="n" s="5">
-        <x:v>294.96</x:v>
+        <x:v>3247.45</x:v>
       </x:c>
       <x:c r="C31" t="inlineStr" s="7">
         <x:is>
-          <x:t>10-10-10, 10-10-10, Club Member, Club Member (Additional System), MULTI- 2, Parts Ordered, Trane Supply</x:t>
+          <x:t>10-Year Labor, Club Member, Club Member 2 sys , Gemaire, Parts Received , PLM</x:t>
         </x:is>
       </x:c>
       <x:c r="D31" t="inlineStr" s="9">
         <x:is>
-          <x:t>554624809</x:t>
+          <x:t>587314216</x:t>
         </x:is>
       </x:c>
       <x:c r="E31" t="inlineStr" s="11">
         <x:is>
-          <x:t>554624809</x:t>
+          <x:t>587314216</x:t>
         </x:is>
       </x:c>
       <x:c r="F31" s="13">
@@ -1762,7 +1762,7 @@
       </x:c>
       <x:c r="G31" t="inlineStr" s="15">
         <x:is>
-          <x:t>PP Carlos Machado</x:t>
+          <x:t>Rolin Moimeme</x:t>
         </x:is>
       </x:c>
       <x:c r="H31" t="inlineStr" s="17">
@@ -1777,14 +1777,14 @@
       </x:c>
       <x:c r="J31" t="inlineStr" s="21">
         <x:is>
-          <x:t>Michael &amp; Delle Lenzen</x:t>
+          <x:t>FRIEDMAN, SAMANTHA</x:t>
         </x:is>
       </x:c>
       <x:c r="K31" s="23">
-        <x:v>45996</x:v>
+        <x:v>46105</x:v>
       </x:c>
       <x:c r="L31" s="25">
-        <x:v>45996</x:v>
+        <x:v>46105</x:v>
       </x:c>
     </x:row>
     <x:row r="32">
@@ -1794,21 +1794,21 @@
         </x:is>
       </x:c>
       <x:c r="B32" t="n" s="5">
-        <x:v>344.21</x:v>
+        <x:v>292.95</x:v>
       </x:c>
       <x:c r="C32" t="inlineStr" s="7">
         <x:is>
-          <x:t>10-10-10, Club Member, Parts Received </x:t>
+          <x:t>Baker Supply, Club Member, Parts Ordered, PLM</x:t>
         </x:is>
       </x:c>
       <x:c r="D32" t="inlineStr" s="9">
         <x:is>
-          <x:t>587448160</x:t>
+          <x:t>587301961</x:t>
         </x:is>
       </x:c>
       <x:c r="E32" t="inlineStr" s="11">
         <x:is>
-          <x:t>587448160</x:t>
+          <x:t>587301961</x:t>
         </x:is>
       </x:c>
       <x:c r="F32" s="13">
@@ -1816,7 +1816,7 @@
       </x:c>
       <x:c r="G32" t="inlineStr" s="15">
         <x:is>
-          <x:t>Rolin Moimeme</x:t>
+          <x:t>Jesse Dague</x:t>
         </x:is>
       </x:c>
       <x:c r="H32" t="inlineStr" s="17">
@@ -1831,387 +1831,63 @@
       </x:c>
       <x:c r="J32" t="inlineStr" s="21">
         <x:is>
-          <x:t>Rene Ceusters</x:t>
+          <x:t>CHACON, LERA</x:t>
         </x:is>
       </x:c>
       <x:c r="K32" s="23">
-        <x:v>46106</x:v>
+        <x:v>46105</x:v>
       </x:c>
       <x:c r="L32" s="25">
-        <x:v>46106</x:v>
+        <x:v>46105</x:v>
       </x:c>
     </x:row>
     <x:row r="33">
-      <x:c r="A33" t="inlineStr" s="3">
-        <x:is>
-          <x:t>HC - Return to Repair</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B33" t="n" s="5">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="C33" t="inlineStr" s="7">
-        <x:is>
-          <x:t>Club Member, LW- 2 YEAR LABOR, Parts Ordered, Trane Supply</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D33" t="inlineStr" s="9">
-        <x:is>
-          <x:t>587077196</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="E33" t="inlineStr" s="11">
-        <x:is>
-          <x:t>587077196</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="F33" s="13">
-        <x:v>46107</x:v>
-      </x:c>
-      <x:c r="G33" t="inlineStr" s="15">
-        <x:is>
-          <x:t>Tyler Gallatin</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="H33" t="inlineStr" s="17">
-        <x:is>
-          <x:t>Hold</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="I33" t="inlineStr" s="19">
-        <x:is>
-          <x:t>CS - HVAC - Service - 12</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="J33" t="inlineStr" s="21">
-        <x:is>
-          <x:t>Timberwalk Association Inc</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="K33" s="23">
-        <x:v>46102</x:v>
-      </x:c>
-      <x:c r="L33" s="25">
-        <x:v>46102</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="34">
-      <x:c r="A34" t="inlineStr" s="3">
-        <x:is>
-          <x:t>HC - Return to Repair</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B34" t="n" s="5">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="C34" t="inlineStr" s="7">
-        <x:is>
-          <x:t>5 YEAR WARRANTY, 5 YEAR WARRANTY, 5 YEAR WARRANTY, 5 YEAR WARRANTY, 5 YEAR WARRANTY, 5 YEAR WARRANTY, Club Member 3 sys, Gemaire, MULTI- 3, Parts Ordered</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D34" t="inlineStr" s="9">
-        <x:is>
-          <x:t>586595677</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="E34" t="inlineStr" s="11">
-        <x:is>
-          <x:t>586595677</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="F34" s="13">
-        <x:v>46107</x:v>
-      </x:c>
-      <x:c r="G34" t="inlineStr" s="15">
-        <x:is>
-          <x:t>PP Alejandro Espinosa</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="H34" t="inlineStr" s="17">
-        <x:is>
-          <x:t>Hold</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="I34" t="inlineStr" s="19">
-        <x:is>
-          <x:t>PLM - HVAC - Service - 12</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="J34" t="inlineStr" s="21">
-        <x:is>
-          <x:t>Bob Lauson</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="K34" s="23">
-        <x:v>46098</x:v>
-      </x:c>
-      <x:c r="L34" s="25">
-        <x:v>46098</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="35">
-      <x:c r="A35" t="inlineStr" s="3">
-        <x:is>
-          <x:t>HC - Return to Repair</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B35" t="n" s="5">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="C35" t="inlineStr" s="7">
-        <x:is>
-          <x:t>10-Year Labor, 10-Year Labor, 10-Year Labor, 10-Year Labor, Goodman distribution , MULTI- 5, Parts Ordered, PLM, Potential Member</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D35" t="inlineStr" s="9">
-        <x:is>
-          <x:t>587266021</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="E35" t="inlineStr" s="11">
-        <x:is>
-          <x:t>587266021</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="F35" s="13">
-        <x:v>46107</x:v>
-      </x:c>
-      <x:c r="G35" t="inlineStr" s="15">
-        <x:is>
-          <x:t>PP Cesar Levy</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="H35" t="inlineStr" s="17">
-        <x:is>
-          <x:t>Hold</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="I35" t="inlineStr" s="19">
-        <x:is>
-          <x:t>PLM - HVAC - Service - 12</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="J35" t="inlineStr" s="21">
-        <x:is>
-          <x:t>Nevalee &amp; Paul Oneil</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="K35" s="23">
-        <x:v>46105</x:v>
-      </x:c>
-      <x:c r="L35" s="25">
-        <x:v>46105</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="36">
-      <x:c r="A36" t="inlineStr" s="3">
-        <x:is>
-          <x:t>HC - Return to Repair</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B36" t="n" s="5">
-        <x:v>1340.1</x:v>
-      </x:c>
-      <x:c r="C36" t="inlineStr" s="7">
-        <x:is>
-          <x:t>Club Member, Club Member (Additional System), Gemaire, MULTI- 3, Parts Received , PLM</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D36" t="inlineStr" s="9">
-        <x:is>
-          <x:t>587281524</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="E36" t="inlineStr" s="11">
-        <x:is>
-          <x:t>587281524</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="F36" s="13">
-        <x:v>46107</x:v>
-      </x:c>
-      <x:c r="G36" t="inlineStr" s="15">
-        <x:is>
-          <x:t>PP Alejandro Espinosa</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="H36" t="inlineStr" s="17">
-        <x:is>
-          <x:t>Hold</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="I36" t="inlineStr" s="19">
-        <x:is>
-          <x:t>PLM - HVAC - Service - 12</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="J36" t="inlineStr" s="21">
-        <x:is>
-          <x:t>Robert Lake</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="K36" s="23">
-        <x:v>46105</x:v>
-      </x:c>
-      <x:c r="L36" s="25">
-        <x:v>46105</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="37">
-      <x:c r="A37" t="inlineStr" s="3">
-        <x:is>
-          <x:t>HC - Return to Repair</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B37" t="n" s="5">
-        <x:v>3247.45</x:v>
-      </x:c>
-      <x:c r="C37" t="inlineStr" s="7">
-        <x:is>
-          <x:t>10-Year Labor, Club Member, Club Member 2 sys , Gemaire, Parts Received , PLM</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D37" t="inlineStr" s="9">
-        <x:is>
-          <x:t>587314216</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="E37" t="inlineStr" s="11">
-        <x:is>
-          <x:t>587314216</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="F37" s="13">
-        <x:v>46107</x:v>
-      </x:c>
-      <x:c r="G37" t="inlineStr" s="15">
-        <x:is>
-          <x:t>Rolin Moimeme</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="H37" t="inlineStr" s="17">
-        <x:is>
-          <x:t>Hold</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="I37" t="inlineStr" s="19">
-        <x:is>
-          <x:t>CS - HVAC - Service - 12</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="J37" t="inlineStr" s="21">
-        <x:is>
-          <x:t>FRIEDMAN, SAMANTHA</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="K37" s="23">
-        <x:v>46105</x:v>
-      </x:c>
-      <x:c r="L37" s="25">
-        <x:v>46105</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="38">
-      <x:c r="A38" t="inlineStr" s="3">
-        <x:is>
-          <x:t>HC - Return to Repair</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B38" t="n" s="5">
-        <x:v>292.95</x:v>
-      </x:c>
-      <x:c r="C38" t="inlineStr" s="7">
-        <x:is>
-          <x:t>Baker Supply, Club Member, Parts Ordered, PLM</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D38" t="inlineStr" s="9">
-        <x:is>
-          <x:t>587301961</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="E38" t="inlineStr" s="11">
-        <x:is>
-          <x:t>587301961</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="F38" s="13">
-        <x:v>46107</x:v>
-      </x:c>
-      <x:c r="G38" t="inlineStr" s="15">
-        <x:is>
-          <x:t>Jesse Dague</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="H38" t="inlineStr" s="17">
-        <x:is>
-          <x:t>Hold</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="I38" t="inlineStr" s="19">
-        <x:is>
-          <x:t>CS - HVAC - Service - 12</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="J38" t="inlineStr" s="21">
-        <x:is>
-          <x:t>CHACON, LERA</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="K38" s="23">
-        <x:v>46105</x:v>
-      </x:c>
-      <x:c r="L38" s="25">
-        <x:v>46105</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="39">
-      <x:c r="A39" t="n" s="4">
-        <x:v>37</x:v>
-      </x:c>
-      <x:c r="B39" t="n" s="6">
-        <x:v>503.8672972972972972972972973</x:v>
-      </x:c>
-      <x:c r="C39" t="inlineStr" s="8">
+      <x:c r="A33" t="n" s="4">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="B33" t="n" s="6">
+        <x:v>542.56612903225806451612903226</x:v>
+      </x:c>
+      <x:c r="C33" t="inlineStr" s="8">
         <x:is>
           <x:t/>
         </x:is>
       </x:c>
-      <x:c r="D39" t="n" s="10">
-        <x:v>37</x:v>
-      </x:c>
-      <x:c r="E39" t="inlineStr" s="12">
+      <x:c r="D33" t="n" s="10">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="E33" t="inlineStr" s="12">
         <x:is>
           <x:t/>
         </x:is>
       </x:c>
-      <x:c r="F39" s="14">
+      <x:c r="F33" s="14">
         <x:v/>
       </x:c>
-      <x:c r="G39" t="inlineStr" s="16">
+      <x:c r="G33" t="inlineStr" s="16">
         <x:is>
           <x:t/>
         </x:is>
       </x:c>
-      <x:c r="H39" t="inlineStr" s="18">
+      <x:c r="H33" t="inlineStr" s="18">
         <x:is>
           <x:t/>
         </x:is>
       </x:c>
-      <x:c r="I39" t="inlineStr" s="20">
+      <x:c r="I33" t="inlineStr" s="20">
         <x:is>
           <x:t/>
         </x:is>
       </x:c>
-      <x:c r="J39" t="inlineStr" s="22">
+      <x:c r="J33" t="inlineStr" s="22">
         <x:is>
           <x:t/>
         </x:is>
       </x:c>
-      <x:c r="K39" s="24">
+      <x:c r="K33" s="24">
         <x:v/>
       </x:c>
-      <x:c r="L39" s="26">
+      <x:c r="L33" s="26">
         <x:v/>
       </x:c>
     </x:row>

--- a/data/parts_report_past.xlsx
+++ b/data/parts_report_past.xlsx
@@ -5,8 +5,8 @@
     <x:workbookView/>
   </x:bookViews>
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R09a54d20f48c4ab0"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Filters" sheetId="2" r:id="Rbbf377f01dbe4108"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rdbd7d091975f4f4c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Filters" sheetId="2" r:id="Rb28e9c57b0e34009"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -1258,17 +1258,17 @@
       </x:c>
       <x:c r="C22" t="inlineStr" s="7">
         <x:is>
-          <x:t>Carrier enterprise, Club Member, Parts Received </x:t>
+          <x:t>10-10-10, Club Member, Parts Ordered, Trane Supply</x:t>
         </x:is>
       </x:c>
       <x:c r="D22" t="inlineStr" s="9">
         <x:is>
-          <x:t>586083412</x:t>
+          <x:t>586864800</x:t>
         </x:is>
       </x:c>
       <x:c r="E22" t="inlineStr" s="11">
         <x:is>
-          <x:t>586083412</x:t>
+          <x:t>586864800</x:t>
         </x:is>
       </x:c>
       <x:c r="F22" s="13">
@@ -1276,7 +1276,7 @@
       </x:c>
       <x:c r="G22" t="inlineStr" s="15">
         <x:is>
-          <x:t>Michael Kertesz </x:t>
+          <x:t>PP David Escobar</x:t>
         </x:is>
       </x:c>
       <x:c r="H22" t="inlineStr" s="17">
@@ -1291,14 +1291,14 @@
       </x:c>
       <x:c r="J22" t="inlineStr" s="21">
         <x:is>
-          <x:t>Gregory  Tsesler</x:t>
+          <x:t>Hope Gadea</x:t>
         </x:is>
       </x:c>
       <x:c r="K22" s="23">
-        <x:v>46093</x:v>
+        <x:v>46100</x:v>
       </x:c>
       <x:c r="L22" s="25">
-        <x:v>46093</x:v>
+        <x:v>46100</x:v>
       </x:c>
     </x:row>
     <x:row r="23">
@@ -1308,21 +1308,21 @@
         </x:is>
       </x:c>
       <x:c r="B23" t="n" s="5">
-        <x:v>0</x:v>
+        <x:v>294.96</x:v>
       </x:c>
       <x:c r="C23" t="inlineStr" s="7">
         <x:is>
-          <x:t>10-10-10, Club Member, Parts Ordered, Trane Supply</x:t>
+          <x:t>10-10-10, 10-10-10, Club Member, Club Member (Additional System), MULTI- 2, Parts Ordered, Trane Supply</x:t>
         </x:is>
       </x:c>
       <x:c r="D23" t="inlineStr" s="9">
         <x:is>
-          <x:t>586864800</x:t>
+          <x:t>554624809</x:t>
         </x:is>
       </x:c>
       <x:c r="E23" t="inlineStr" s="11">
         <x:is>
-          <x:t>586864800</x:t>
+          <x:t>554624809</x:t>
         </x:is>
       </x:c>
       <x:c r="F23" s="13">
@@ -1330,7 +1330,7 @@
       </x:c>
       <x:c r="G23" t="inlineStr" s="15">
         <x:is>
-          <x:t>PP David Escobar</x:t>
+          <x:t>PP Carlos Machado</x:t>
         </x:is>
       </x:c>
       <x:c r="H23" t="inlineStr" s="17">
@@ -1345,14 +1345,14 @@
       </x:c>
       <x:c r="J23" t="inlineStr" s="21">
         <x:is>
-          <x:t>Hope Gadea</x:t>
+          <x:t>Michael &amp; Delle Lenzen</x:t>
         </x:is>
       </x:c>
       <x:c r="K23" s="23">
-        <x:v>46100</x:v>
+        <x:v>45996</x:v>
       </x:c>
       <x:c r="L23" s="25">
-        <x:v>46100</x:v>
+        <x:v>45996</x:v>
       </x:c>
     </x:row>
     <x:row r="24">
@@ -1362,21 +1362,21 @@
         </x:is>
       </x:c>
       <x:c r="B24" t="n" s="5">
-        <x:v>294.96</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="C24" t="inlineStr" s="7">
         <x:is>
-          <x:t>10-10-10, 10-10-10, Club Member, Club Member (Additional System), MULTI- 2, Parts Ordered, Trane Supply</x:t>
+          <x:t>Club Member, LW- 2 YEAR LABOR, Parts Ordered, Trane Supply</x:t>
         </x:is>
       </x:c>
       <x:c r="D24" t="inlineStr" s="9">
         <x:is>
-          <x:t>554624809</x:t>
+          <x:t>587077196</x:t>
         </x:is>
       </x:c>
       <x:c r="E24" t="inlineStr" s="11">
         <x:is>
-          <x:t>554624809</x:t>
+          <x:t>587077196</x:t>
         </x:is>
       </x:c>
       <x:c r="F24" s="13">
@@ -1384,7 +1384,7 @@
       </x:c>
       <x:c r="G24" t="inlineStr" s="15">
         <x:is>
-          <x:t>PP Carlos Machado</x:t>
+          <x:t>Tyler Gallatin</x:t>
         </x:is>
       </x:c>
       <x:c r="H24" t="inlineStr" s="17">
@@ -1399,14 +1399,14 @@
       </x:c>
       <x:c r="J24" t="inlineStr" s="21">
         <x:is>
-          <x:t>Michael &amp; Delle Lenzen</x:t>
+          <x:t>Timberwalk Association Inc</x:t>
         </x:is>
       </x:c>
       <x:c r="K24" s="23">
-        <x:v>45996</x:v>
+        <x:v>46102</x:v>
       </x:c>
       <x:c r="L24" s="25">
-        <x:v>45996</x:v>
+        <x:v>46102</x:v>
       </x:c>
     </x:row>
     <x:row r="25">
@@ -1416,21 +1416,21 @@
         </x:is>
       </x:c>
       <x:c r="B25" t="n" s="5">
-        <x:v>344.21</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="C25" t="inlineStr" s="7">
         <x:is>
-          <x:t>10-10-10, Club Member, Parts Received </x:t>
+          <x:t>5 YEAR WARRANTY, 5 YEAR WARRANTY, 5 YEAR WARRANTY, 5 YEAR WARRANTY, 5 YEAR WARRANTY, 5 YEAR WARRANTY, Club Member 3 sys, Gemaire, MULTI- 3, Parts Ordered</x:t>
         </x:is>
       </x:c>
       <x:c r="D25" t="inlineStr" s="9">
         <x:is>
-          <x:t>587448160</x:t>
+          <x:t>586595677</x:t>
         </x:is>
       </x:c>
       <x:c r="E25" t="inlineStr" s="11">
         <x:is>
-          <x:t>587448160</x:t>
+          <x:t>586595677</x:t>
         </x:is>
       </x:c>
       <x:c r="F25" s="13">
@@ -1438,7 +1438,7 @@
       </x:c>
       <x:c r="G25" t="inlineStr" s="15">
         <x:is>
-          <x:t>Rolin Moimeme</x:t>
+          <x:t>PP Alejandro Espinosa</x:t>
         </x:is>
       </x:c>
       <x:c r="H25" t="inlineStr" s="17">
@@ -1448,19 +1448,19 @@
       </x:c>
       <x:c r="I25" t="inlineStr" s="19">
         <x:is>
-          <x:t>CS - HVAC - Service - 12</x:t>
+          <x:t>PLM - HVAC - Service - 12</x:t>
         </x:is>
       </x:c>
       <x:c r="J25" t="inlineStr" s="21">
         <x:is>
-          <x:t>Rene Ceusters</x:t>
+          <x:t>Bob Lauson</x:t>
         </x:is>
       </x:c>
       <x:c r="K25" s="23">
-        <x:v>46106</x:v>
+        <x:v>46098</x:v>
       </x:c>
       <x:c r="L25" s="25">
-        <x:v>46106</x:v>
+        <x:v>46098</x:v>
       </x:c>
     </x:row>
     <x:row r="26">
@@ -1474,17 +1474,17 @@
       </x:c>
       <x:c r="C26" t="inlineStr" s="7">
         <x:is>
-          <x:t>Club Member, LW- 2 YEAR LABOR, Parts Ordered, Trane Supply</x:t>
+          <x:t>10-Year Labor, 10-Year Labor, 10-Year Labor, 10-Year Labor, Goodman distribution , MULTI- 5, Parts Ordered, PLM, Potential Member</x:t>
         </x:is>
       </x:c>
       <x:c r="D26" t="inlineStr" s="9">
         <x:is>
-          <x:t>587077196</x:t>
+          <x:t>587266021</x:t>
         </x:is>
       </x:c>
       <x:c r="E26" t="inlineStr" s="11">
         <x:is>
-          <x:t>587077196</x:t>
+          <x:t>587266021</x:t>
         </x:is>
       </x:c>
       <x:c r="F26" s="13">
@@ -1492,7 +1492,7 @@
       </x:c>
       <x:c r="G26" t="inlineStr" s="15">
         <x:is>
-          <x:t>Tyler Gallatin</x:t>
+          <x:t>PP Cesar Levy</x:t>
         </x:is>
       </x:c>
       <x:c r="H26" t="inlineStr" s="17">
@@ -1502,19 +1502,19 @@
       </x:c>
       <x:c r="I26" t="inlineStr" s="19">
         <x:is>
-          <x:t>CS - HVAC - Service - 12</x:t>
+          <x:t>PLM - HVAC - Service - 12</x:t>
         </x:is>
       </x:c>
       <x:c r="J26" t="inlineStr" s="21">
         <x:is>
-          <x:t>Timberwalk Association Inc</x:t>
+          <x:t>Nevalee &amp; Paul Oneil</x:t>
         </x:is>
       </x:c>
       <x:c r="K26" s="23">
-        <x:v>46102</x:v>
+        <x:v>46105</x:v>
       </x:c>
       <x:c r="L26" s="25">
-        <x:v>46102</x:v>
+        <x:v>46105</x:v>
       </x:c>
     </x:row>
     <x:row r="27">
@@ -1524,21 +1524,21 @@
         </x:is>
       </x:c>
       <x:c r="B27" t="n" s="5">
-        <x:v>0</x:v>
+        <x:v>1340.1</x:v>
       </x:c>
       <x:c r="C27" t="inlineStr" s="7">
         <x:is>
-          <x:t>5 YEAR WARRANTY, 5 YEAR WARRANTY, 5 YEAR WARRANTY, 5 YEAR WARRANTY, 5 YEAR WARRANTY, 5 YEAR WARRANTY, Club Member 3 sys, Gemaire, MULTI- 3, Parts Ordered</x:t>
+          <x:t>Club Member, Club Member (Additional System), Gemaire, MULTI- 3, Parts Received , PLM</x:t>
         </x:is>
       </x:c>
       <x:c r="D27" t="inlineStr" s="9">
         <x:is>
-          <x:t>586595677</x:t>
+          <x:t>587281524</x:t>
         </x:is>
       </x:c>
       <x:c r="E27" t="inlineStr" s="11">
         <x:is>
-          <x:t>586595677</x:t>
+          <x:t>587281524</x:t>
         </x:is>
       </x:c>
       <x:c r="F27" s="13">
@@ -1561,14 +1561,14 @@
       </x:c>
       <x:c r="J27" t="inlineStr" s="21">
         <x:is>
-          <x:t>Bob Lauson</x:t>
+          <x:t>Robert Lake</x:t>
         </x:is>
       </x:c>
       <x:c r="K27" s="23">
-        <x:v>46098</x:v>
+        <x:v>46105</x:v>
       </x:c>
       <x:c r="L27" s="25">
-        <x:v>46098</x:v>
+        <x:v>46105</x:v>
       </x:c>
     </x:row>
     <x:row r="28">
@@ -1578,21 +1578,21 @@
         </x:is>
       </x:c>
       <x:c r="B28" t="n" s="5">
-        <x:v>0</x:v>
+        <x:v>1605.6</x:v>
       </x:c>
       <x:c r="C28" t="inlineStr" s="7">
         <x:is>
-          <x:t>10-Year Labor, 10-Year Labor, 10-Year Labor, 10-Year Labor, Goodman distribution , MULTI- 5, Parts Ordered, PLM, Potential Member</x:t>
+          <x:t>Club Member, Parts Received , PLM</x:t>
         </x:is>
       </x:c>
       <x:c r="D28" t="inlineStr" s="9">
         <x:is>
-          <x:t>587266021</x:t>
+          <x:t>587548046</x:t>
         </x:is>
       </x:c>
       <x:c r="E28" t="inlineStr" s="11">
         <x:is>
-          <x:t>587266021</x:t>
+          <x:t>587548046</x:t>
         </x:is>
       </x:c>
       <x:c r="F28" s="13">
@@ -1600,7 +1600,7 @@
       </x:c>
       <x:c r="G28" t="inlineStr" s="15">
         <x:is>
-          <x:t>PP Cesar Levy</x:t>
+          <x:t>PP Gurpreet Parihar</x:t>
         </x:is>
       </x:c>
       <x:c r="H28" t="inlineStr" s="17">
@@ -1610,19 +1610,19 @@
       </x:c>
       <x:c r="I28" t="inlineStr" s="19">
         <x:is>
-          <x:t>PLM - HVAC - Service - 12</x:t>
+          <x:t>CS - HVAC - Service - 12</x:t>
         </x:is>
       </x:c>
       <x:c r="J28" t="inlineStr" s="21">
         <x:is>
-          <x:t>Nevalee &amp; Paul Oneil</x:t>
+          <x:t>Eric Yisk</x:t>
         </x:is>
       </x:c>
       <x:c r="K28" s="23">
-        <x:v>46105</x:v>
+        <x:v>46107</x:v>
       </x:c>
       <x:c r="L28" s="25">
-        <x:v>46105</x:v>
+        <x:v>46107</x:v>
       </x:c>
     </x:row>
     <x:row r="29">
@@ -1632,21 +1632,21 @@
         </x:is>
       </x:c>
       <x:c r="B29" t="n" s="5">
-        <x:v>1340.1</x:v>
+        <x:v>3247.45</x:v>
       </x:c>
       <x:c r="C29" t="inlineStr" s="7">
         <x:is>
-          <x:t>Club Member, Club Member (Additional System), Gemaire, MULTI- 3, Parts Received , PLM</x:t>
+          <x:t>10-Year Labor, Club Member, Club Member 2 sys , Gemaire, Parts Received , PLM</x:t>
         </x:is>
       </x:c>
       <x:c r="D29" t="inlineStr" s="9">
         <x:is>
-          <x:t>587281524</x:t>
+          <x:t>587314216</x:t>
         </x:is>
       </x:c>
       <x:c r="E29" t="inlineStr" s="11">
         <x:is>
-          <x:t>587281524</x:t>
+          <x:t>587314216</x:t>
         </x:is>
       </x:c>
       <x:c r="F29" s="13">
@@ -1654,7 +1654,7 @@
       </x:c>
       <x:c r="G29" t="inlineStr" s="15">
         <x:is>
-          <x:t>PP Alejandro Espinosa</x:t>
+          <x:t>Rolin Moimeme</x:t>
         </x:is>
       </x:c>
       <x:c r="H29" t="inlineStr" s="17">
@@ -1664,12 +1664,12 @@
       </x:c>
       <x:c r="I29" t="inlineStr" s="19">
         <x:is>
-          <x:t>PLM - HVAC - Service - 12</x:t>
+          <x:t>CS - HVAC - Service - 12</x:t>
         </x:is>
       </x:c>
       <x:c r="J29" t="inlineStr" s="21">
         <x:is>
-          <x:t>Robert Lake</x:t>
+          <x:t>FRIEDMAN, SAMANTHA</x:t>
         </x:is>
       </x:c>
       <x:c r="K29" s="23">
@@ -1686,21 +1686,21 @@
         </x:is>
       </x:c>
       <x:c r="B30" t="n" s="5">
-        <x:v>1536.7</x:v>
+        <x:v>292.95</x:v>
       </x:c>
       <x:c r="C30" t="inlineStr" s="7">
         <x:is>
-          <x:t>Need to order part (NTO), PLM</x:t>
+          <x:t>Baker Supply, Club Member, Parts Ordered, PLM</x:t>
         </x:is>
       </x:c>
       <x:c r="D30" t="inlineStr" s="9">
         <x:is>
-          <x:t>587489793</x:t>
+          <x:t>587301961</x:t>
         </x:is>
       </x:c>
       <x:c r="E30" t="inlineStr" s="11">
         <x:is>
-          <x:t>587489793</x:t>
+          <x:t>587301961</x:t>
         </x:is>
       </x:c>
       <x:c r="F30" s="13">
@@ -1708,7 +1708,7 @@
       </x:c>
       <x:c r="G30" t="inlineStr" s="15">
         <x:is>
-          <x:t>PP Tyriq McCall</x:t>
+          <x:t>Jesse Dague</x:t>
         </x:is>
       </x:c>
       <x:c r="H30" t="inlineStr" s="17">
@@ -1718,176 +1718,68 @@
       </x:c>
       <x:c r="I30" t="inlineStr" s="19">
         <x:is>
-          <x:t>PLM - HVAC - Service - 12</x:t>
+          <x:t>CS - HVAC - Service - 12</x:t>
         </x:is>
       </x:c>
       <x:c r="J30" t="inlineStr" s="21">
         <x:is>
-          <x:t>PASAMI, LLC</x:t>
+          <x:t>CHACON, LERA</x:t>
         </x:is>
       </x:c>
       <x:c r="K30" s="23">
-        <x:v>46107</x:v>
+        <x:v>46105</x:v>
       </x:c>
       <x:c r="L30" s="25">
-        <x:v>46107</x:v>
+        <x:v>46105</x:v>
       </x:c>
     </x:row>
     <x:row r="31">
-      <x:c r="A31" t="inlineStr" s="3">
-        <x:is>
-          <x:t>HC - Return to Repair</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B31" t="n" s="5">
-        <x:v>3247.45</x:v>
-      </x:c>
-      <x:c r="C31" t="inlineStr" s="7">
-        <x:is>
-          <x:t>10-Year Labor, Club Member, Club Member 2 sys , Gemaire, Parts Received , PLM</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D31" t="inlineStr" s="9">
-        <x:is>
-          <x:t>587314216</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="E31" t="inlineStr" s="11">
-        <x:is>
-          <x:t>587314216</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="F31" s="13">
-        <x:v>46107</x:v>
-      </x:c>
-      <x:c r="G31" t="inlineStr" s="15">
-        <x:is>
-          <x:t>Rolin Moimeme</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="H31" t="inlineStr" s="17">
-        <x:is>
-          <x:t>Hold</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="I31" t="inlineStr" s="19">
-        <x:is>
-          <x:t>CS - HVAC - Service - 12</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="J31" t="inlineStr" s="21">
-        <x:is>
-          <x:t>FRIEDMAN, SAMANTHA</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="K31" s="23">
-        <x:v>46105</x:v>
-      </x:c>
-      <x:c r="L31" s="25">
-        <x:v>46105</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="32">
-      <x:c r="A32" t="inlineStr" s="3">
-        <x:is>
-          <x:t>HC - Return to Repair</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B32" t="n" s="5">
-        <x:v>292.95</x:v>
-      </x:c>
-      <x:c r="C32" t="inlineStr" s="7">
-        <x:is>
-          <x:t>Baker Supply, Club Member, Parts Ordered, PLM</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D32" t="inlineStr" s="9">
-        <x:is>
-          <x:t>587301961</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="E32" t="inlineStr" s="11">
-        <x:is>
-          <x:t>587301961</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="F32" s="13">
-        <x:v>46107</x:v>
-      </x:c>
-      <x:c r="G32" t="inlineStr" s="15">
-        <x:is>
-          <x:t>Jesse Dague</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="H32" t="inlineStr" s="17">
-        <x:is>
-          <x:t>Hold</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="I32" t="inlineStr" s="19">
-        <x:is>
-          <x:t>CS - HVAC - Service - 12</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="J32" t="inlineStr" s="21">
-        <x:is>
-          <x:t>CHACON, LERA</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="K32" s="23">
-        <x:v>46105</x:v>
-      </x:c>
-      <x:c r="L32" s="25">
-        <x:v>46105</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="33">
-      <x:c r="A33" t="n" s="4">
-        <x:v>31</x:v>
-      </x:c>
-      <x:c r="B33" t="n" s="6">
-        <x:v>542.56612903225806451612903226</x:v>
-      </x:c>
-      <x:c r="C33" t="inlineStr" s="8">
+      <x:c r="A31" t="n" s="4">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="B31" t="n" s="6">
+        <x:v>570.49103448275862068965517241</x:v>
+      </x:c>
+      <x:c r="C31" t="inlineStr" s="8">
         <x:is>
           <x:t/>
         </x:is>
       </x:c>
-      <x:c r="D33" t="n" s="10">
-        <x:v>31</x:v>
-      </x:c>
-      <x:c r="E33" t="inlineStr" s="12">
+      <x:c r="D31" t="n" s="10">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="E31" t="inlineStr" s="12">
         <x:is>
           <x:t/>
         </x:is>
       </x:c>
-      <x:c r="F33" s="14">
+      <x:c r="F31" s="14">
         <x:v/>
       </x:c>
-      <x:c r="G33" t="inlineStr" s="16">
+      <x:c r="G31" t="inlineStr" s="16">
         <x:is>
           <x:t/>
         </x:is>
       </x:c>
-      <x:c r="H33" t="inlineStr" s="18">
+      <x:c r="H31" t="inlineStr" s="18">
         <x:is>
           <x:t/>
         </x:is>
       </x:c>
-      <x:c r="I33" t="inlineStr" s="20">
+      <x:c r="I31" t="inlineStr" s="20">
         <x:is>
           <x:t/>
         </x:is>
       </x:c>
-      <x:c r="J33" t="inlineStr" s="22">
+      <x:c r="J31" t="inlineStr" s="22">
         <x:is>
           <x:t/>
         </x:is>
       </x:c>
-      <x:c r="K33" s="24">
+      <x:c r="K31" s="24">
         <x:v/>
       </x:c>
-      <x:c r="L33" s="26">
+      <x:c r="L31" s="26">
         <x:v/>
       </x:c>
     </x:row>

--- a/data/parts_report_past.xlsx
+++ b/data/parts_report_past.xlsx
@@ -5,8 +5,8 @@
     <x:workbookView/>
   </x:bookViews>
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rdbd7d091975f4f4c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Filters" sheetId="2" r:id="Rb28e9c57b0e34009"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R431b099d0e1b462e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Filters" sheetId="2" r:id="Rc42a338121264e57"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -1258,7 +1258,7 @@
       </x:c>
       <x:c r="C22" t="inlineStr" s="7">
         <x:is>
-          <x:t>10-10-10, Club Member, Parts Ordered, Trane Supply</x:t>
+          <x:t>10-10-10, Club Member, Parts Received , Trane Supply</x:t>
         </x:is>
       </x:c>
       <x:c r="D22" t="inlineStr" s="9">
@@ -1366,17 +1366,17 @@
       </x:c>
       <x:c r="C24" t="inlineStr" s="7">
         <x:is>
-          <x:t>Club Member, LW- 2 YEAR LABOR, Parts Ordered, Trane Supply</x:t>
+          <x:t>10-Year Labor, 10-Year Labor, 10-Year Labor, 10-Year Labor, Goodman distribution , MULTI- 5, Parts Received , PLM, Potential Member</x:t>
         </x:is>
       </x:c>
       <x:c r="D24" t="inlineStr" s="9">
         <x:is>
-          <x:t>587077196</x:t>
+          <x:t>587266021</x:t>
         </x:is>
       </x:c>
       <x:c r="E24" t="inlineStr" s="11">
         <x:is>
-          <x:t>587077196</x:t>
+          <x:t>587266021</x:t>
         </x:is>
       </x:c>
       <x:c r="F24" s="13">
@@ -1384,7 +1384,7 @@
       </x:c>
       <x:c r="G24" t="inlineStr" s="15">
         <x:is>
-          <x:t>Tyler Gallatin</x:t>
+          <x:t>PP Cesar Levy</x:t>
         </x:is>
       </x:c>
       <x:c r="H24" t="inlineStr" s="17">
@@ -1394,19 +1394,19 @@
       </x:c>
       <x:c r="I24" t="inlineStr" s="19">
         <x:is>
-          <x:t>CS - HVAC - Service - 12</x:t>
+          <x:t>PLM - HVAC - Service - 12</x:t>
         </x:is>
       </x:c>
       <x:c r="J24" t="inlineStr" s="21">
         <x:is>
-          <x:t>Timberwalk Association Inc</x:t>
+          <x:t>Nevalee &amp; Paul Oneil</x:t>
         </x:is>
       </x:c>
       <x:c r="K24" s="23">
-        <x:v>46102</x:v>
+        <x:v>46105</x:v>
       </x:c>
       <x:c r="L24" s="25">
-        <x:v>46102</x:v>
+        <x:v>46105</x:v>
       </x:c>
     </x:row>
     <x:row r="25">
@@ -1416,21 +1416,21 @@
         </x:is>
       </x:c>
       <x:c r="B25" t="n" s="5">
-        <x:v>0</x:v>
+        <x:v>1340.1</x:v>
       </x:c>
       <x:c r="C25" t="inlineStr" s="7">
         <x:is>
-          <x:t>5 YEAR WARRANTY, 5 YEAR WARRANTY, 5 YEAR WARRANTY, 5 YEAR WARRANTY, 5 YEAR WARRANTY, 5 YEAR WARRANTY, Club Member 3 sys, Gemaire, MULTI- 3, Parts Ordered</x:t>
+          <x:t>Club Member, Club Member (Additional System), Gemaire, MULTI- 3, Parts Received , PLM</x:t>
         </x:is>
       </x:c>
       <x:c r="D25" t="inlineStr" s="9">
         <x:is>
-          <x:t>586595677</x:t>
+          <x:t>587281524</x:t>
         </x:is>
       </x:c>
       <x:c r="E25" t="inlineStr" s="11">
         <x:is>
-          <x:t>586595677</x:t>
+          <x:t>587281524</x:t>
         </x:is>
       </x:c>
       <x:c r="F25" s="13">
@@ -1453,14 +1453,14 @@
       </x:c>
       <x:c r="J25" t="inlineStr" s="21">
         <x:is>
-          <x:t>Bob Lauson</x:t>
+          <x:t>Robert Lake</x:t>
         </x:is>
       </x:c>
       <x:c r="K25" s="23">
-        <x:v>46098</x:v>
+        <x:v>46105</x:v>
       </x:c>
       <x:c r="L25" s="25">
-        <x:v>46098</x:v>
+        <x:v>46105</x:v>
       </x:c>
     </x:row>
     <x:row r="26">
@@ -1470,21 +1470,21 @@
         </x:is>
       </x:c>
       <x:c r="B26" t="n" s="5">
-        <x:v>0</x:v>
+        <x:v>1605.6</x:v>
       </x:c>
       <x:c r="C26" t="inlineStr" s="7">
         <x:is>
-          <x:t>10-Year Labor, 10-Year Labor, 10-Year Labor, 10-Year Labor, Goodman distribution , MULTI- 5, Parts Ordered, PLM, Potential Member</x:t>
+          <x:t>Club Member, Parts Received , PLM</x:t>
         </x:is>
       </x:c>
       <x:c r="D26" t="inlineStr" s="9">
         <x:is>
-          <x:t>587266021</x:t>
+          <x:t>587548046</x:t>
         </x:is>
       </x:c>
       <x:c r="E26" t="inlineStr" s="11">
         <x:is>
-          <x:t>587266021</x:t>
+          <x:t>587548046</x:t>
         </x:is>
       </x:c>
       <x:c r="F26" s="13">
@@ -1492,7 +1492,7 @@
       </x:c>
       <x:c r="G26" t="inlineStr" s="15">
         <x:is>
-          <x:t>PP Cesar Levy</x:t>
+          <x:t>PP Gurpreet Parihar</x:t>
         </x:is>
       </x:c>
       <x:c r="H26" t="inlineStr" s="17">
@@ -1502,19 +1502,19 @@
       </x:c>
       <x:c r="I26" t="inlineStr" s="19">
         <x:is>
-          <x:t>PLM - HVAC - Service - 12</x:t>
+          <x:t>CS - HVAC - Service - 12</x:t>
         </x:is>
       </x:c>
       <x:c r="J26" t="inlineStr" s="21">
         <x:is>
-          <x:t>Nevalee &amp; Paul Oneil</x:t>
+          <x:t>Eric Yisk</x:t>
         </x:is>
       </x:c>
       <x:c r="K26" s="23">
-        <x:v>46105</x:v>
+        <x:v>46107</x:v>
       </x:c>
       <x:c r="L26" s="25">
-        <x:v>46105</x:v>
+        <x:v>46107</x:v>
       </x:c>
     </x:row>
     <x:row r="27">
@@ -1524,21 +1524,21 @@
         </x:is>
       </x:c>
       <x:c r="B27" t="n" s="5">
-        <x:v>1340.1</x:v>
+        <x:v>3247.45</x:v>
       </x:c>
       <x:c r="C27" t="inlineStr" s="7">
         <x:is>
-          <x:t>Club Member, Club Member (Additional System), Gemaire, MULTI- 3, Parts Received , PLM</x:t>
+          <x:t>10-Year Labor, Club Member, Club Member 2 sys , Gemaire, Parts Received , PLM</x:t>
         </x:is>
       </x:c>
       <x:c r="D27" t="inlineStr" s="9">
         <x:is>
-          <x:t>587281524</x:t>
+          <x:t>587314216</x:t>
         </x:is>
       </x:c>
       <x:c r="E27" t="inlineStr" s="11">
         <x:is>
-          <x:t>587281524</x:t>
+          <x:t>587314216</x:t>
         </x:is>
       </x:c>
       <x:c r="F27" s="13">
@@ -1546,7 +1546,7 @@
       </x:c>
       <x:c r="G27" t="inlineStr" s="15">
         <x:is>
-          <x:t>PP Alejandro Espinosa</x:t>
+          <x:t>Rolin Moimeme</x:t>
         </x:is>
       </x:c>
       <x:c r="H27" t="inlineStr" s="17">
@@ -1556,12 +1556,12 @@
       </x:c>
       <x:c r="I27" t="inlineStr" s="19">
         <x:is>
-          <x:t>PLM - HVAC - Service - 12</x:t>
+          <x:t>CS - HVAC - Service - 12</x:t>
         </x:is>
       </x:c>
       <x:c r="J27" t="inlineStr" s="21">
         <x:is>
-          <x:t>Robert Lake</x:t>
+          <x:t>FRIEDMAN, SAMANTHA</x:t>
         </x:is>
       </x:c>
       <x:c r="K27" s="23">
@@ -1578,29 +1578,29 @@
         </x:is>
       </x:c>
       <x:c r="B28" t="n" s="5">
-        <x:v>1605.6</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="C28" t="inlineStr" s="7">
         <x:is>
-          <x:t>Club Member, Parts Received , PLM</x:t>
+          <x:t>Club Member, Gemaire, Parts Ordered</x:t>
         </x:is>
       </x:c>
       <x:c r="D28" t="inlineStr" s="9">
         <x:is>
-          <x:t>587548046</x:t>
+          <x:t>587448096</x:t>
         </x:is>
       </x:c>
       <x:c r="E28" t="inlineStr" s="11">
         <x:is>
-          <x:t>587548046</x:t>
+          <x:t>587448096</x:t>
         </x:is>
       </x:c>
       <x:c r="F28" s="13">
-        <x:v>46107</x:v>
+        <x:v>46108</x:v>
       </x:c>
       <x:c r="G28" t="inlineStr" s="15">
         <x:is>
-          <x:t>PP Gurpreet Parihar</x:t>
+          <x:t/>
         </x:is>
       </x:c>
       <x:c r="H28" t="inlineStr" s="17">
@@ -1610,19 +1610,19 @@
       </x:c>
       <x:c r="I28" t="inlineStr" s="19">
         <x:is>
-          <x:t>CS - HVAC - Service - 12</x:t>
+          <x:t>PLM - HVAC - Service - 12</x:t>
         </x:is>
       </x:c>
       <x:c r="J28" t="inlineStr" s="21">
         <x:is>
-          <x:t>Eric Yisk</x:t>
+          <x:t>Cassandra Sexton</x:t>
         </x:is>
       </x:c>
       <x:c r="K28" s="23">
-        <x:v>46107</x:v>
+        <x:v>46106</x:v>
       </x:c>
       <x:c r="L28" s="25">
-        <x:v>46107</x:v>
+        <x:v>46106</x:v>
       </x:c>
     </x:row>
     <x:row r="29">
@@ -1632,25 +1632,25 @@
         </x:is>
       </x:c>
       <x:c r="B29" t="n" s="5">
-        <x:v>3247.45</x:v>
+        <x:v>289.85</x:v>
       </x:c>
       <x:c r="C29" t="inlineStr" s="7">
         <x:is>
-          <x:t>10-Year Labor, Club Member, Club Member 2 sys , Gemaire, Parts Received , PLM</x:t>
+          <x:t>10-10-10, 10-10-10, 10-10-10, 10-10-10, 10-10-10, Carrier enterprise, Club Member, Parts Received </x:t>
         </x:is>
       </x:c>
       <x:c r="D29" t="inlineStr" s="9">
         <x:is>
-          <x:t>587314216</x:t>
+          <x:t>587426826</x:t>
         </x:is>
       </x:c>
       <x:c r="E29" t="inlineStr" s="11">
         <x:is>
-          <x:t>587314216</x:t>
+          <x:t>587426826</x:t>
         </x:is>
       </x:c>
       <x:c r="F29" s="13">
-        <x:v>46107</x:v>
+        <x:v>46108</x:v>
       </x:c>
       <x:c r="G29" t="inlineStr" s="15">
         <x:is>
@@ -1669,14 +1669,14 @@
       </x:c>
       <x:c r="J29" t="inlineStr" s="21">
         <x:is>
-          <x:t>FRIEDMAN, SAMANTHA</x:t>
+          <x:t>Bill Esposito</x:t>
         </x:is>
       </x:c>
       <x:c r="K29" s="23">
-        <x:v>46105</x:v>
+        <x:v>46106</x:v>
       </x:c>
       <x:c r="L29" s="25">
-        <x:v>46105</x:v>
+        <x:v>46106</x:v>
       </x:c>
     </x:row>
     <x:row r="30">
@@ -1686,100 +1686,586 @@
         </x:is>
       </x:c>
       <x:c r="B30" t="n" s="5">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="C30" t="inlineStr" s="7">
+        <x:is>
+          <x:t>Club Member, LW- 2 YEAR LABOR, Parts Ordered, Trane Supply</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D30" t="inlineStr" s="9">
+        <x:is>
+          <x:t>587077196</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E30" t="inlineStr" s="11">
+        <x:is>
+          <x:t>587077196</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F30" s="13">
+        <x:v>46108</x:v>
+      </x:c>
+      <x:c r="G30" t="inlineStr" s="15">
+        <x:is>
+          <x:t>Tyler Gallatin</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="H30" t="inlineStr" s="17">
+        <x:is>
+          <x:t>Hold</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="I30" t="inlineStr" s="19">
+        <x:is>
+          <x:t>CS - HVAC - Service - 12</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="J30" t="inlineStr" s="21">
+        <x:is>
+          <x:t>Timberwalk Association Inc</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="K30" s="23">
+        <x:v>46102</x:v>
+      </x:c>
+      <x:c r="L30" s="25">
+        <x:v>46102</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="31">
+      <x:c r="A31" t="inlineStr" s="3">
+        <x:is>
+          <x:t>HC - Return to Repair</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B31" t="n" s="5">
+        <x:v>1248.8</x:v>
+      </x:c>
+      <x:c r="C31" t="inlineStr" s="7">
+        <x:is>
+          <x:t>Club Member, Lennox Supply, Parts Ordered</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D31" t="inlineStr" s="9">
+        <x:is>
+          <x:t>587303898</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E31" t="inlineStr" s="11">
+        <x:is>
+          <x:t>587303898</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F31" s="13">
+        <x:v>46108</x:v>
+      </x:c>
+      <x:c r="G31" t="inlineStr" s="15">
+        <x:is>
+          <x:t>Xavier Mateo</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="H31" t="inlineStr" s="17">
+        <x:is>
+          <x:t>Hold</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="I31" t="inlineStr" s="19">
+        <x:is>
+          <x:t>CS - HVAC - Service - 12</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="J31" t="inlineStr" s="21">
+        <x:is>
+          <x:t>ROBERT MCCABE</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="K31" s="23">
+        <x:v>46105</x:v>
+      </x:c>
+      <x:c r="L31" s="25">
+        <x:v>46105</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="32">
+      <x:c r="A32" t="inlineStr" s="3">
+        <x:is>
+          <x:t>HC - Return to Repair</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B32" t="n" s="5">
+        <x:v>1267.95</x:v>
+      </x:c>
+      <x:c r="C32" t="inlineStr" s="7">
+        <x:is>
+          <x:t>Club Member 3 sys, Gemaire, Parts Ordered</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D32" t="inlineStr" s="9">
+        <x:is>
+          <x:t>578585007</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E32" t="inlineStr" s="11">
+        <x:is>
+          <x:t>578585007</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F32" s="13">
+        <x:v>46108</x:v>
+      </x:c>
+      <x:c r="G32" t="inlineStr" s="15">
+        <x:is>
+          <x:t>PP Cesar Levy</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="H32" t="inlineStr" s="17">
+        <x:is>
+          <x:t>Hold</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="I32" t="inlineStr" s="19">
+        <x:is>
+          <x:t>CS - HVAC - Service - 12</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="J32" t="inlineStr" s="21">
+        <x:is>
+          <x:t>Serghei Arsentiev</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="K32" s="23">
+        <x:v>46037</x:v>
+      </x:c>
+      <x:c r="L32" s="25">
+        <x:v>46037</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="33">
+      <x:c r="A33" t="inlineStr" s="3">
+        <x:is>
+          <x:t>HC - Return to Repair</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B33" t="n" s="5">
         <x:v>292.95</x:v>
       </x:c>
-      <x:c r="C30" t="inlineStr" s="7">
+      <x:c r="C33" t="inlineStr" s="7">
+        <x:is>
+          <x:t>Baker Supply, Club Member, Parts Received , PLM</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D33" t="inlineStr" s="9">
+        <x:is>
+          <x:t>586875916</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E33" t="inlineStr" s="11">
+        <x:is>
+          <x:t>586875916</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F33" s="13">
+        <x:v>46108</x:v>
+      </x:c>
+      <x:c r="G33" t="inlineStr" s="15">
+        <x:is>
+          <x:t>PP Barrington Wilson</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="H33" t="inlineStr" s="17">
+        <x:is>
+          <x:t>Hold</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="I33" t="inlineStr" s="19">
+        <x:is>
+          <x:t>CS - HVAC - Service - 12</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="J33" t="inlineStr" s="21">
+        <x:is>
+          <x:t>Anna Tyulmenkova</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="K33" s="23">
+        <x:v>46100</x:v>
+      </x:c>
+      <x:c r="L33" s="25">
+        <x:v>46100</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="34">
+      <x:c r="A34" t="inlineStr" s="3">
+        <x:is>
+          <x:t>HC - Return to Repair</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B34" t="n" s="5">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="C34" t="inlineStr" s="7">
+        <x:is>
+          <x:t>Carrier enterprise, Parts Ordered, PLM, Potential Member</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D34" t="inlineStr" s="9">
+        <x:is>
+          <x:t>583259145</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E34" t="inlineStr" s="11">
+        <x:is>
+          <x:t>583259145</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F34" s="13">
+        <x:v>46108</x:v>
+      </x:c>
+      <x:c r="G34" t="inlineStr" s="15">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+      <x:c r="H34" t="inlineStr" s="17">
+        <x:is>
+          <x:t>Hold</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="I34" t="inlineStr" s="19">
+        <x:is>
+          <x:t>CS - HVAC - Service - 12</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="J34" t="inlineStr" s="21">
+        <x:is>
+          <x:t>John Moore</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="K34" s="23">
+        <x:v>46070</x:v>
+      </x:c>
+      <x:c r="L34" s="25">
+        <x:v>46070</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="35">
+      <x:c r="A35" t="inlineStr" s="3">
+        <x:is>
+          <x:t>HC - Return to Repair</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B35" t="n" s="5">
+        <x:v>808.4</x:v>
+      </x:c>
+      <x:c r="C35" t="inlineStr" s="7">
+        <x:is>
+          <x:t>Club Member, Need to order part (NTO), PLM</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D35" t="inlineStr" s="9">
+        <x:is>
+          <x:t>587598604</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E35" t="inlineStr" s="11">
+        <x:is>
+          <x:t>587598604</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F35" s="13">
+        <x:v>46108</x:v>
+      </x:c>
+      <x:c r="G35" t="inlineStr" s="15">
+        <x:is>
+          <x:t>PP Barrington Wilson</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="H35" t="inlineStr" s="17">
+        <x:is>
+          <x:t>Hold</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="I35" t="inlineStr" s="19">
+        <x:is>
+          <x:t>PLM - HVAC - Service - 12</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="J35" t="inlineStr" s="21">
+        <x:is>
+          <x:t>DIVINCENZO, ANTHONY</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="K35" s="23">
+        <x:v>46107</x:v>
+      </x:c>
+      <x:c r="L35" s="25">
+        <x:v>46107</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="36">
+      <x:c r="A36" t="inlineStr" s="3">
+        <x:is>
+          <x:t>HC - Return to Repair</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B36" t="n" s="5">
+        <x:v>292.95</x:v>
+      </x:c>
+      <x:c r="C36" t="inlineStr" s="7">
         <x:is>
           <x:t>Baker Supply, Club Member, Parts Ordered, PLM</x:t>
         </x:is>
       </x:c>
-      <x:c r="D30" t="inlineStr" s="9">
+      <x:c r="D36" t="inlineStr" s="9">
         <x:is>
           <x:t>587301961</x:t>
         </x:is>
       </x:c>
-      <x:c r="E30" t="inlineStr" s="11">
+      <x:c r="E36" t="inlineStr" s="11">
         <x:is>
           <x:t>587301961</x:t>
         </x:is>
       </x:c>
-      <x:c r="F30" s="13">
-        <x:v>46107</x:v>
-      </x:c>
-      <x:c r="G30" t="inlineStr" s="15">
+      <x:c r="F36" s="13">
+        <x:v>46108</x:v>
+      </x:c>
+      <x:c r="G36" t="inlineStr" s="15">
         <x:is>
           <x:t>Jesse Dague</x:t>
         </x:is>
       </x:c>
-      <x:c r="H30" t="inlineStr" s="17">
-        <x:is>
-          <x:t>Hold</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="I30" t="inlineStr" s="19">
+      <x:c r="H36" t="inlineStr" s="17">
+        <x:is>
+          <x:t>Hold</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="I36" t="inlineStr" s="19">
         <x:is>
           <x:t>CS - HVAC - Service - 12</x:t>
         </x:is>
       </x:c>
-      <x:c r="J30" t="inlineStr" s="21">
+      <x:c r="J36" t="inlineStr" s="21">
         <x:is>
           <x:t>CHACON, LERA</x:t>
         </x:is>
       </x:c>
-      <x:c r="K30" s="23">
+      <x:c r="K36" s="23">
         <x:v>46105</x:v>
       </x:c>
-      <x:c r="L30" s="25">
+      <x:c r="L36" s="25">
         <x:v>46105</x:v>
       </x:c>
     </x:row>
-    <x:row r="31">
-      <x:c r="A31" t="n" s="4">
-        <x:v>29</x:v>
-      </x:c>
-      <x:c r="B31" t="n" s="6">
-        <x:v>570.49103448275862068965517241</x:v>
-      </x:c>
-      <x:c r="C31" t="inlineStr" s="8">
+    <x:row r="37">
+      <x:c r="A37" t="inlineStr" s="3">
+        <x:is>
+          <x:t>HC - Return to Repair</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B37" t="n" s="5">
+        <x:v>2405.92</x:v>
+      </x:c>
+      <x:c r="C37" t="inlineStr" s="7">
+        <x:is>
+          <x:t>Baker Supply, Parts Ordered, Potential Member</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D37" t="inlineStr" s="9">
+        <x:is>
+          <x:t>578394047</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E37" t="inlineStr" s="11">
+        <x:is>
+          <x:t>578394047</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F37" s="13">
+        <x:v>46108</x:v>
+      </x:c>
+      <x:c r="G37" t="inlineStr" s="15">
+        <x:is>
+          <x:t>PP Gurpreet Parihar</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="H37" t="inlineStr" s="17">
+        <x:is>
+          <x:t>Hold</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="I37" t="inlineStr" s="19">
+        <x:is>
+          <x:t>PLM - HVAC - Service - 12</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="J37" t="inlineStr" s="21">
+        <x:is>
+          <x:t>Edgar Irving</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="K37" s="23">
+        <x:v>46036</x:v>
+      </x:c>
+      <x:c r="L37" s="25">
+        <x:v>46036</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="38">
+      <x:c r="A38" t="inlineStr" s="3">
+        <x:is>
+          <x:t>HC - Return to Repair</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B38" t="n" s="5">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="C38" t="inlineStr" s="7">
+        <x:is>
+          <x:t>10-Year Labor, 10-Year Labor, 10-Year Labor, 10-Year Labor, 10-Year Labor, Club Member, Goodman distribution , Parts Ordered</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D38" t="inlineStr" s="9">
+        <x:is>
+          <x:t>585388429</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E38" t="inlineStr" s="11">
+        <x:is>
+          <x:t>585388429</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F38" s="13">
+        <x:v>46108</x:v>
+      </x:c>
+      <x:c r="G38" t="inlineStr" s="15">
+        <x:is>
+          <x:t>Rickey McClam </x:t>
+        </x:is>
+      </x:c>
+      <x:c r="H38" t="inlineStr" s="17">
+        <x:is>
+          <x:t>Hold</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="I38" t="inlineStr" s="19">
+        <x:is>
+          <x:t>CS - HVAC - Service - 12</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="J38" t="inlineStr" s="21">
+        <x:is>
+          <x:t>Charles Funkey</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="K38" s="23">
+        <x:v>46086</x:v>
+      </x:c>
+      <x:c r="L38" s="25">
+        <x:v>46086</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="39">
+      <x:c r="A39" t="inlineStr" s="3">
+        <x:is>
+          <x:t>HC - Return to Repair</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B39" t="n" s="5">
+        <x:v>2125</x:v>
+      </x:c>
+      <x:c r="C39" t="inlineStr" s="7">
+        <x:is>
+          <x:t>Carrier enterprise, Parts Received , Potential Member</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D39" t="inlineStr" s="9">
+        <x:is>
+          <x:t>587416074</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E39" t="inlineStr" s="11">
+        <x:is>
+          <x:t>587416074</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F39" s="13">
+        <x:v>46108</x:v>
+      </x:c>
+      <x:c r="G39" t="inlineStr" s="15">
+        <x:is>
+          <x:t>PP Michael Chenoy</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="H39" t="inlineStr" s="17">
+        <x:is>
+          <x:t>Hold</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="I39" t="inlineStr" s="19">
+        <x:is>
+          <x:t>PLM - HVAC - Service - 12</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="J39" t="inlineStr" s="21">
+        <x:is>
+          <x:t>Jian Jia </x:t>
+        </x:is>
+      </x:c>
+      <x:c r="K39" s="23">
+        <x:v>46106</x:v>
+      </x:c>
+      <x:c r="L39" s="25">
+        <x:v>46106</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="40">
+      <x:c r="A40" t="n" s="4">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="B40" t="n" s="6">
+        <x:v>657.45026315789473684210526316</x:v>
+      </x:c>
+      <x:c r="C40" t="inlineStr" s="8">
         <x:is>
           <x:t/>
         </x:is>
       </x:c>
-      <x:c r="D31" t="n" s="10">
-        <x:v>29</x:v>
-      </x:c>
-      <x:c r="E31" t="inlineStr" s="12">
+      <x:c r="D40" t="n" s="10">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="E40" t="inlineStr" s="12">
         <x:is>
           <x:t/>
         </x:is>
       </x:c>
-      <x:c r="F31" s="14">
+      <x:c r="F40" s="14">
         <x:v/>
       </x:c>
-      <x:c r="G31" t="inlineStr" s="16">
+      <x:c r="G40" t="inlineStr" s="16">
         <x:is>
           <x:t/>
         </x:is>
       </x:c>
-      <x:c r="H31" t="inlineStr" s="18">
+      <x:c r="H40" t="inlineStr" s="18">
         <x:is>
           <x:t/>
         </x:is>
       </x:c>
-      <x:c r="I31" t="inlineStr" s="20">
+      <x:c r="I40" t="inlineStr" s="20">
         <x:is>
           <x:t/>
         </x:is>
       </x:c>
-      <x:c r="J31" t="inlineStr" s="22">
+      <x:c r="J40" t="inlineStr" s="22">
         <x:is>
           <x:t/>
         </x:is>
       </x:c>
-      <x:c r="K31" s="24">
+      <x:c r="K40" s="24">
         <x:v/>
       </x:c>
-      <x:c r="L31" s="26">
+      <x:c r="L40" s="26">
         <x:v/>
       </x:c>
     </x:row>
@@ -1810,7 +2296,7 @@
       </x:c>
       <x:c r="B2" t="inlineStr" s="28">
         <x:is>
-          <x:t>03/26/25 - 03/26/26</x:t>
+          <x:t>03/27/25 - 03/27/26</x:t>
         </x:is>
       </x:c>
     </x:row>
@@ -1876,7 +2362,7 @@
     <x:mergeCell ref="A8:B8"/>
   </x:mergeCells>
   <x:hyperlinks>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A8" r:id="hyperlinkId1" location="/new/reports/459565681?DateType=3&amp;BusinessUnitId=2415185%2C2415187%2C15775258%2C2415186%2C2415190%2C182981963%2C182981958%2C182981961%2C182981957&amp;IncludeAdjustmentInvoices=false&amp;IsScheduling=True&amp;From=2025-03-26&amp;To=2026-03-26" display="View Report"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A8" r:id="hyperlinkId1" location="/new/reports/459565681?DateType=3&amp;BusinessUnitId=2415185%2C2415187%2C15775258%2C2415186%2C2415190%2C182981963%2C182981958%2C182981961%2C182981957&amp;IncludeAdjustmentInvoices=false&amp;IsScheduling=True&amp;From=2025-03-27&amp;To=2026-03-27" display="View Report"/>
   </x:hyperlinks>
 </x:worksheet>
 </file>
--- a/data/parts_report_past.xlsx
+++ b/data/parts_report_past.xlsx
@@ -5,8 +5,8 @@
     <x:workbookView/>
   </x:bookViews>
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R431b099d0e1b462e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Filters" sheetId="2" r:id="Rc42a338121264e57"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R5d3c5b9ee3bb4cb0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Filters" sheetId="2" r:id="Re04a7bc8b8684abd"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -1092,51 +1092,51 @@
         </x:is>
       </x:c>
       <x:c r="B19" t="n" s="5">
-        <x:v>0</x:v>
+        <x:v>689.97</x:v>
       </x:c>
       <x:c r="C19" t="inlineStr" s="7">
         <x:is>
-          <x:t>Carrier enterprise, Parts Received , PLM, Potential Member</x:t>
+          <x:t>2-YR Labor Warranty, 2-YR Labor Warranty, 2-YR Labor Warranty, Club Member, Gemaire, Parts Received </x:t>
         </x:is>
       </x:c>
       <x:c r="D19" t="inlineStr" s="9">
         <x:is>
-          <x:t>586835264</x:t>
+          <x:t>587253199</x:t>
         </x:is>
       </x:c>
       <x:c r="E19" t="inlineStr" s="11">
         <x:is>
-          <x:t>586835264</x:t>
+          <x:t>587253199</x:t>
         </x:is>
       </x:c>
       <x:c r="F19" s="13">
+        <x:v>46106</x:v>
+      </x:c>
+      <x:c r="G19" t="inlineStr" s="15">
+        <x:is>
+          <x:t>PP Barrington Wilson</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="H19" t="inlineStr" s="17">
+        <x:is>
+          <x:t>Hold</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="I19" t="inlineStr" s="19">
+        <x:is>
+          <x:t>CS - HVAC - Service - 12</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="J19" t="inlineStr" s="21">
+        <x:is>
+          <x:t>Dane Lyons</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="K19" s="23">
         <x:v>46105</x:v>
       </x:c>
-      <x:c r="G19" t="inlineStr" s="15">
-        <x:is>
-          <x:t>PP Michael Chenoy</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="H19" t="inlineStr" s="17">
-        <x:is>
-          <x:t>Hold</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="I19" t="inlineStr" s="19">
-        <x:is>
-          <x:t>PLM - HVAC - Service - 12</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="J19" t="inlineStr" s="21">
-        <x:is>
-          <x:t>WILSON, CARA</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="K19" s="23">
-        <x:v>46100</x:v>
-      </x:c>
       <x:c r="L19" s="25">
-        <x:v>46100</x:v>
+        <x:v>46105</x:v>
       </x:c>
     </x:row>
     <x:row r="20">
@@ -1146,21 +1146,21 @@
         </x:is>
       </x:c>
       <x:c r="B20" t="n" s="5">
-        <x:v>689.97</x:v>
+        <x:v>722.79</x:v>
       </x:c>
       <x:c r="C20" t="inlineStr" s="7">
         <x:is>
-          <x:t>2-YR Labor Warranty, 2-YR Labor Warranty, 2-YR Labor Warranty, Club Member, Gemaire, Parts Received </x:t>
+          <x:t>Baker Supply, Parts Ordered, PLM, Potential Member</x:t>
         </x:is>
       </x:c>
       <x:c r="D20" t="inlineStr" s="9">
         <x:is>
-          <x:t>587253199</x:t>
+          <x:t>459781920</x:t>
         </x:is>
       </x:c>
       <x:c r="E20" t="inlineStr" s="11">
         <x:is>
-          <x:t>587253199</x:t>
+          <x:t>459781920</x:t>
         </x:is>
       </x:c>
       <x:c r="F20" s="13">
@@ -1168,7 +1168,7 @@
       </x:c>
       <x:c r="G20" t="inlineStr" s="15">
         <x:is>
-          <x:t>PP Barrington Wilson</x:t>
+          <x:t>PLM-Quentin Stewart</x:t>
         </x:is>
       </x:c>
       <x:c r="H20" t="inlineStr" s="17">
@@ -1178,19 +1178,19 @@
       </x:c>
       <x:c r="I20" t="inlineStr" s="19">
         <x:is>
-          <x:t>CS - HVAC - Service - 12</x:t>
+          <x:t>PLM - HVAC - Service - 12</x:t>
         </x:is>
       </x:c>
       <x:c r="J20" t="inlineStr" s="21">
         <x:is>
-          <x:t>Dane Lyons</x:t>
+          <x:t>Gluck Carolyn</x:t>
         </x:is>
       </x:c>
       <x:c r="K20" s="23">
-        <x:v>46105</x:v>
+        <x:v>45726</x:v>
       </x:c>
       <x:c r="L20" s="25">
-        <x:v>46105</x:v>
+        <x:v>45726</x:v>
       </x:c>
     </x:row>
     <x:row r="21">
@@ -1200,29 +1200,29 @@
         </x:is>
       </x:c>
       <x:c r="B21" t="n" s="5">
-        <x:v>722.79</x:v>
+        <x:v>294.96</x:v>
       </x:c>
       <x:c r="C21" t="inlineStr" s="7">
         <x:is>
-          <x:t>Baker Supply, Parts Ordered, PLM, Potential Member</x:t>
+          <x:t>10-10-10, 10-10-10, Club Member, Club Member (Additional System), MULTI- 2, Parts Ordered, Trane Supply</x:t>
         </x:is>
       </x:c>
       <x:c r="D21" t="inlineStr" s="9">
         <x:is>
-          <x:t>459781920</x:t>
+          <x:t>554624809</x:t>
         </x:is>
       </x:c>
       <x:c r="E21" t="inlineStr" s="11">
         <x:is>
-          <x:t>459781920</x:t>
+          <x:t>554624809</x:t>
         </x:is>
       </x:c>
       <x:c r="F21" s="13">
-        <x:v>46106</x:v>
+        <x:v>46107</x:v>
       </x:c>
       <x:c r="G21" t="inlineStr" s="15">
         <x:is>
-          <x:t>PLM-Quentin Stewart</x:t>
+          <x:t>PP Carlos Machado</x:t>
         </x:is>
       </x:c>
       <x:c r="H21" t="inlineStr" s="17">
@@ -1232,19 +1232,19 @@
       </x:c>
       <x:c r="I21" t="inlineStr" s="19">
         <x:is>
-          <x:t>PLM - HVAC - Service - 12</x:t>
+          <x:t>CS - HVAC - Service - 12</x:t>
         </x:is>
       </x:c>
       <x:c r="J21" t="inlineStr" s="21">
         <x:is>
-          <x:t>Gluck Carolyn</x:t>
+          <x:t>Michael &amp; Delle Lenzen</x:t>
         </x:is>
       </x:c>
       <x:c r="K21" s="23">
-        <x:v>45726</x:v>
+        <x:v>45996</x:v>
       </x:c>
       <x:c r="L21" s="25">
-        <x:v>45726</x:v>
+        <x:v>45996</x:v>
       </x:c>
     </x:row>
     <x:row r="22">
@@ -1254,21 +1254,21 @@
         </x:is>
       </x:c>
       <x:c r="B22" t="n" s="5">
-        <x:v>0</x:v>
+        <x:v>3247.45</x:v>
       </x:c>
       <x:c r="C22" t="inlineStr" s="7">
         <x:is>
-          <x:t>10-10-10, Club Member, Parts Received , Trane Supply</x:t>
+          <x:t>10-Year Labor, Club Member, Club Member 2 sys , Gemaire, Parts Received , PLM</x:t>
         </x:is>
       </x:c>
       <x:c r="D22" t="inlineStr" s="9">
         <x:is>
-          <x:t>586864800</x:t>
+          <x:t>587314216</x:t>
         </x:is>
       </x:c>
       <x:c r="E22" t="inlineStr" s="11">
         <x:is>
-          <x:t>586864800</x:t>
+          <x:t>587314216</x:t>
         </x:is>
       </x:c>
       <x:c r="F22" s="13">
@@ -1276,7 +1276,7 @@
       </x:c>
       <x:c r="G22" t="inlineStr" s="15">
         <x:is>
-          <x:t>PP David Escobar</x:t>
+          <x:t>Rolin Moimeme</x:t>
         </x:is>
       </x:c>
       <x:c r="H22" t="inlineStr" s="17">
@@ -1291,14 +1291,14 @@
       </x:c>
       <x:c r="J22" t="inlineStr" s="21">
         <x:is>
-          <x:t>Hope Gadea</x:t>
+          <x:t>FRIEDMAN, SAMANTHA</x:t>
         </x:is>
       </x:c>
       <x:c r="K22" s="23">
-        <x:v>46100</x:v>
+        <x:v>46105</x:v>
       </x:c>
       <x:c r="L22" s="25">
-        <x:v>46100</x:v>
+        <x:v>46105</x:v>
       </x:c>
     </x:row>
     <x:row r="23">
@@ -1308,29 +1308,29 @@
         </x:is>
       </x:c>
       <x:c r="B23" t="n" s="5">
-        <x:v>294.96</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="C23" t="inlineStr" s="7">
         <x:is>
-          <x:t>10-10-10, 10-10-10, Club Member, Club Member (Additional System), MULTI- 2, Parts Ordered, Trane Supply</x:t>
+          <x:t>Club Member, Gemaire, Parts Ordered</x:t>
         </x:is>
       </x:c>
       <x:c r="D23" t="inlineStr" s="9">
         <x:is>
-          <x:t>554624809</x:t>
+          <x:t>587448096</x:t>
         </x:is>
       </x:c>
       <x:c r="E23" t="inlineStr" s="11">
         <x:is>
-          <x:t>554624809</x:t>
+          <x:t>587448096</x:t>
         </x:is>
       </x:c>
       <x:c r="F23" s="13">
-        <x:v>46107</x:v>
+        <x:v>46108</x:v>
       </x:c>
       <x:c r="G23" t="inlineStr" s="15">
         <x:is>
-          <x:t>PP Carlos Machado</x:t>
+          <x:t/>
         </x:is>
       </x:c>
       <x:c r="H23" t="inlineStr" s="17">
@@ -1340,19 +1340,19 @@
       </x:c>
       <x:c r="I23" t="inlineStr" s="19">
         <x:is>
-          <x:t>CS - HVAC - Service - 12</x:t>
+          <x:t>PLM - HVAC - Service - 12</x:t>
         </x:is>
       </x:c>
       <x:c r="J23" t="inlineStr" s="21">
         <x:is>
-          <x:t>Michael &amp; Delle Lenzen</x:t>
+          <x:t>Cassandra Sexton</x:t>
         </x:is>
       </x:c>
       <x:c r="K23" s="23">
-        <x:v>45996</x:v>
+        <x:v>46106</x:v>
       </x:c>
       <x:c r="L23" s="25">
-        <x:v>45996</x:v>
+        <x:v>46106</x:v>
       </x:c>
     </x:row>
     <x:row r="24">
@@ -1366,25 +1366,25 @@
       </x:c>
       <x:c r="C24" t="inlineStr" s="7">
         <x:is>
-          <x:t>10-Year Labor, 10-Year Labor, 10-Year Labor, 10-Year Labor, Goodman distribution , MULTI- 5, Parts Received , PLM, Potential Member</x:t>
+          <x:t>Club Member, LW- 2 YEAR LABOR, Parts Ordered, Trane Supply</x:t>
         </x:is>
       </x:c>
       <x:c r="D24" t="inlineStr" s="9">
         <x:is>
-          <x:t>587266021</x:t>
+          <x:t>587077196</x:t>
         </x:is>
       </x:c>
       <x:c r="E24" t="inlineStr" s="11">
         <x:is>
-          <x:t>587266021</x:t>
+          <x:t>587077196</x:t>
         </x:is>
       </x:c>
       <x:c r="F24" s="13">
-        <x:v>46107</x:v>
+        <x:v>46108</x:v>
       </x:c>
       <x:c r="G24" t="inlineStr" s="15">
         <x:is>
-          <x:t>PP Cesar Levy</x:t>
+          <x:t>Tyler Gallatin</x:t>
         </x:is>
       </x:c>
       <x:c r="H24" t="inlineStr" s="17">
@@ -1394,19 +1394,19 @@
       </x:c>
       <x:c r="I24" t="inlineStr" s="19">
         <x:is>
-          <x:t>PLM - HVAC - Service - 12</x:t>
+          <x:t>CS - HVAC - Service - 12</x:t>
         </x:is>
       </x:c>
       <x:c r="J24" t="inlineStr" s="21">
         <x:is>
-          <x:t>Nevalee &amp; Paul Oneil</x:t>
+          <x:t>Timberwalk Association Inc</x:t>
         </x:is>
       </x:c>
       <x:c r="K24" s="23">
-        <x:v>46105</x:v>
+        <x:v>46102</x:v>
       </x:c>
       <x:c r="L24" s="25">
-        <x:v>46105</x:v>
+        <x:v>46102</x:v>
       </x:c>
     </x:row>
     <x:row r="25">
@@ -1416,29 +1416,29 @@
         </x:is>
       </x:c>
       <x:c r="B25" t="n" s="5">
-        <x:v>1340.1</x:v>
+        <x:v>1248.8</x:v>
       </x:c>
       <x:c r="C25" t="inlineStr" s="7">
         <x:is>
-          <x:t>Club Member, Club Member (Additional System), Gemaire, MULTI- 3, Parts Received , PLM</x:t>
+          <x:t>Club Member, Lennox Supply, Parts Ordered</x:t>
         </x:is>
       </x:c>
       <x:c r="D25" t="inlineStr" s="9">
         <x:is>
-          <x:t>587281524</x:t>
+          <x:t>587303898</x:t>
         </x:is>
       </x:c>
       <x:c r="E25" t="inlineStr" s="11">
         <x:is>
-          <x:t>587281524</x:t>
+          <x:t>587303898</x:t>
         </x:is>
       </x:c>
       <x:c r="F25" s="13">
-        <x:v>46107</x:v>
+        <x:v>46108</x:v>
       </x:c>
       <x:c r="G25" t="inlineStr" s="15">
         <x:is>
-          <x:t>PP Alejandro Espinosa</x:t>
+          <x:t>Xavier Mateo</x:t>
         </x:is>
       </x:c>
       <x:c r="H25" t="inlineStr" s="17">
@@ -1448,12 +1448,12 @@
       </x:c>
       <x:c r="I25" t="inlineStr" s="19">
         <x:is>
-          <x:t>PLM - HVAC - Service - 12</x:t>
+          <x:t>CS - HVAC - Service - 12</x:t>
         </x:is>
       </x:c>
       <x:c r="J25" t="inlineStr" s="21">
         <x:is>
-          <x:t>Robert Lake</x:t>
+          <x:t>ROBERT MCCABE</x:t>
         </x:is>
       </x:c>
       <x:c r="K25" s="23">
@@ -1470,29 +1470,29 @@
         </x:is>
       </x:c>
       <x:c r="B26" t="n" s="5">
-        <x:v>1605.6</x:v>
+        <x:v>1267.95</x:v>
       </x:c>
       <x:c r="C26" t="inlineStr" s="7">
         <x:is>
-          <x:t>Club Member, Parts Received , PLM</x:t>
+          <x:t>Club Member 3 sys, Gemaire, Parts Received </x:t>
         </x:is>
       </x:c>
       <x:c r="D26" t="inlineStr" s="9">
         <x:is>
-          <x:t>587548046</x:t>
+          <x:t>578585007</x:t>
         </x:is>
       </x:c>
       <x:c r="E26" t="inlineStr" s="11">
         <x:is>
-          <x:t>587548046</x:t>
+          <x:t>578585007</x:t>
         </x:is>
       </x:c>
       <x:c r="F26" s="13">
-        <x:v>46107</x:v>
+        <x:v>46108</x:v>
       </x:c>
       <x:c r="G26" t="inlineStr" s="15">
         <x:is>
-          <x:t>PP Gurpreet Parihar</x:t>
+          <x:t>PP Cesar Levy</x:t>
         </x:is>
       </x:c>
       <x:c r="H26" t="inlineStr" s="17">
@@ -1507,14 +1507,14 @@
       </x:c>
       <x:c r="J26" t="inlineStr" s="21">
         <x:is>
-          <x:t>Eric Yisk</x:t>
+          <x:t>Serghei Arsentiev</x:t>
         </x:is>
       </x:c>
       <x:c r="K26" s="23">
-        <x:v>46107</x:v>
+        <x:v>46037</x:v>
       </x:c>
       <x:c r="L26" s="25">
-        <x:v>46107</x:v>
+        <x:v>46037</x:v>
       </x:c>
     </x:row>
     <x:row r="27">
@@ -1524,29 +1524,29 @@
         </x:is>
       </x:c>
       <x:c r="B27" t="n" s="5">
-        <x:v>3247.45</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="C27" t="inlineStr" s="7">
         <x:is>
-          <x:t>10-Year Labor, Club Member, Club Member 2 sys , Gemaire, Parts Received , PLM</x:t>
+          <x:t>Carrier enterprise, Parts Ordered, PLM, Potential Member</x:t>
         </x:is>
       </x:c>
       <x:c r="D27" t="inlineStr" s="9">
         <x:is>
-          <x:t>587314216</x:t>
+          <x:t>583259145</x:t>
         </x:is>
       </x:c>
       <x:c r="E27" t="inlineStr" s="11">
         <x:is>
-          <x:t>587314216</x:t>
+          <x:t>583259145</x:t>
         </x:is>
       </x:c>
       <x:c r="F27" s="13">
-        <x:v>46107</x:v>
+        <x:v>46108</x:v>
       </x:c>
       <x:c r="G27" t="inlineStr" s="15">
         <x:is>
-          <x:t>Rolin Moimeme</x:t>
+          <x:t/>
         </x:is>
       </x:c>
       <x:c r="H27" t="inlineStr" s="17">
@@ -1561,14 +1561,14 @@
       </x:c>
       <x:c r="J27" t="inlineStr" s="21">
         <x:is>
-          <x:t>FRIEDMAN, SAMANTHA</x:t>
+          <x:t>John Moore</x:t>
         </x:is>
       </x:c>
       <x:c r="K27" s="23">
-        <x:v>46105</x:v>
+        <x:v>46070</x:v>
       </x:c>
       <x:c r="L27" s="25">
-        <x:v>46105</x:v>
+        <x:v>46070</x:v>
       </x:c>
     </x:row>
     <x:row r="28">
@@ -1578,21 +1578,21 @@
         </x:is>
       </x:c>
       <x:c r="B28" t="n" s="5">
-        <x:v>0</x:v>
+        <x:v>808.4</x:v>
       </x:c>
       <x:c r="C28" t="inlineStr" s="7">
         <x:is>
-          <x:t>Club Member, Gemaire, Parts Ordered</x:t>
+          <x:t>Carrier enterprise, Club Member, Parts Ordered, PLM</x:t>
         </x:is>
       </x:c>
       <x:c r="D28" t="inlineStr" s="9">
         <x:is>
-          <x:t>587448096</x:t>
+          <x:t>587598604</x:t>
         </x:is>
       </x:c>
       <x:c r="E28" t="inlineStr" s="11">
         <x:is>
-          <x:t>587448096</x:t>
+          <x:t>587598604</x:t>
         </x:is>
       </x:c>
       <x:c r="F28" s="13">
@@ -1600,7 +1600,7 @@
       </x:c>
       <x:c r="G28" t="inlineStr" s="15">
         <x:is>
-          <x:t/>
+          <x:t>PP Barrington Wilson</x:t>
         </x:is>
       </x:c>
       <x:c r="H28" t="inlineStr" s="17">
@@ -1615,14 +1615,14 @@
       </x:c>
       <x:c r="J28" t="inlineStr" s="21">
         <x:is>
-          <x:t>Cassandra Sexton</x:t>
+          <x:t>DIVINCENZO, ANTHONY</x:t>
         </x:is>
       </x:c>
       <x:c r="K28" s="23">
-        <x:v>46106</x:v>
+        <x:v>46107</x:v>
       </x:c>
       <x:c r="L28" s="25">
-        <x:v>46106</x:v>
+        <x:v>46107</x:v>
       </x:c>
     </x:row>
     <x:row r="29">
@@ -1632,21 +1632,21 @@
         </x:is>
       </x:c>
       <x:c r="B29" t="n" s="5">
-        <x:v>289.85</x:v>
+        <x:v>292.95</x:v>
       </x:c>
       <x:c r="C29" t="inlineStr" s="7">
         <x:is>
-          <x:t>10-10-10, 10-10-10, 10-10-10, 10-10-10, 10-10-10, Carrier enterprise, Club Member, Parts Received </x:t>
+          <x:t>Baker Supply, Club Member, Parts Received , PLM</x:t>
         </x:is>
       </x:c>
       <x:c r="D29" t="inlineStr" s="9">
         <x:is>
-          <x:t>587426826</x:t>
+          <x:t>587301961</x:t>
         </x:is>
       </x:c>
       <x:c r="E29" t="inlineStr" s="11">
         <x:is>
-          <x:t>587426826</x:t>
+          <x:t>587301961</x:t>
         </x:is>
       </x:c>
       <x:c r="F29" s="13">
@@ -1654,7 +1654,7 @@
       </x:c>
       <x:c r="G29" t="inlineStr" s="15">
         <x:is>
-          <x:t>Rolin Moimeme</x:t>
+          <x:t>Jesse Dague</x:t>
         </x:is>
       </x:c>
       <x:c r="H29" t="inlineStr" s="17">
@@ -1669,14 +1669,14 @@
       </x:c>
       <x:c r="J29" t="inlineStr" s="21">
         <x:is>
-          <x:t>Bill Esposito</x:t>
+          <x:t>CHACON, LERA</x:t>
         </x:is>
       </x:c>
       <x:c r="K29" s="23">
-        <x:v>46106</x:v>
+        <x:v>46105</x:v>
       </x:c>
       <x:c r="L29" s="25">
-        <x:v>46106</x:v>
+        <x:v>46105</x:v>
       </x:c>
     </x:row>
     <x:row r="30">
@@ -1686,21 +1686,21 @@
         </x:is>
       </x:c>
       <x:c r="B30" t="n" s="5">
-        <x:v>0</x:v>
+        <x:v>2405.92</x:v>
       </x:c>
       <x:c r="C30" t="inlineStr" s="7">
         <x:is>
-          <x:t>Club Member, LW- 2 YEAR LABOR, Parts Ordered, Trane Supply</x:t>
+          <x:t>Baker Supply, Parts Ordered, Potential Member</x:t>
         </x:is>
       </x:c>
       <x:c r="D30" t="inlineStr" s="9">
         <x:is>
-          <x:t>587077196</x:t>
+          <x:t>578394047</x:t>
         </x:is>
       </x:c>
       <x:c r="E30" t="inlineStr" s="11">
         <x:is>
-          <x:t>587077196</x:t>
+          <x:t>578394047</x:t>
         </x:is>
       </x:c>
       <x:c r="F30" s="13">
@@ -1708,7 +1708,7 @@
       </x:c>
       <x:c r="G30" t="inlineStr" s="15">
         <x:is>
-          <x:t>Tyler Gallatin</x:t>
+          <x:t>PP Gurpreet Parihar</x:t>
         </x:is>
       </x:c>
       <x:c r="H30" t="inlineStr" s="17">
@@ -1718,19 +1718,19 @@
       </x:c>
       <x:c r="I30" t="inlineStr" s="19">
         <x:is>
-          <x:t>CS - HVAC - Service - 12</x:t>
+          <x:t>PLM - HVAC - Service - 12</x:t>
         </x:is>
       </x:c>
       <x:c r="J30" t="inlineStr" s="21">
         <x:is>
-          <x:t>Timberwalk Association Inc</x:t>
+          <x:t>Edgar Irving</x:t>
         </x:is>
       </x:c>
       <x:c r="K30" s="23">
-        <x:v>46102</x:v>
+        <x:v>46036</x:v>
       </x:c>
       <x:c r="L30" s="25">
-        <x:v>46102</x:v>
+        <x:v>46036</x:v>
       </x:c>
     </x:row>
     <x:row r="31">
@@ -1740,21 +1740,21 @@
         </x:is>
       </x:c>
       <x:c r="B31" t="n" s="5">
-        <x:v>1248.8</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="C31" t="inlineStr" s="7">
         <x:is>
-          <x:t>Club Member, Lennox Supply, Parts Ordered</x:t>
+          <x:t>10-Year Labor, 10-Year Labor, 10-Year Labor, 10-Year Labor, 10-Year Labor, Club Member, Goodman distribution , Parts Ordered</x:t>
         </x:is>
       </x:c>
       <x:c r="D31" t="inlineStr" s="9">
         <x:is>
-          <x:t>587303898</x:t>
+          <x:t>585388429</x:t>
         </x:is>
       </x:c>
       <x:c r="E31" t="inlineStr" s="11">
         <x:is>
-          <x:t>587303898</x:t>
+          <x:t>585388429</x:t>
         </x:is>
       </x:c>
       <x:c r="F31" s="13">
@@ -1762,7 +1762,7 @@
       </x:c>
       <x:c r="G31" t="inlineStr" s="15">
         <x:is>
-          <x:t>Xavier Mateo</x:t>
+          <x:t>Rickey McClam </x:t>
         </x:is>
       </x:c>
       <x:c r="H31" t="inlineStr" s="17">
@@ -1777,14 +1777,14 @@
       </x:c>
       <x:c r="J31" t="inlineStr" s="21">
         <x:is>
-          <x:t>ROBERT MCCABE</x:t>
+          <x:t>Charles Funkey</x:t>
         </x:is>
       </x:c>
       <x:c r="K31" s="23">
-        <x:v>46105</x:v>
+        <x:v>46086</x:v>
       </x:c>
       <x:c r="L31" s="25">
-        <x:v>46105</x:v>
+        <x:v>46086</x:v>
       </x:c>
     </x:row>
     <x:row r="32">
@@ -1794,21 +1794,21 @@
         </x:is>
       </x:c>
       <x:c r="B32" t="n" s="5">
-        <x:v>1267.95</x:v>
+        <x:v>2125</x:v>
       </x:c>
       <x:c r="C32" t="inlineStr" s="7">
         <x:is>
-          <x:t>Club Member 3 sys, Gemaire, Parts Ordered</x:t>
+          <x:t>Carrier enterprise, Parts Received , Potential Member</x:t>
         </x:is>
       </x:c>
       <x:c r="D32" t="inlineStr" s="9">
         <x:is>
-          <x:t>578585007</x:t>
+          <x:t>587416074</x:t>
         </x:is>
       </x:c>
       <x:c r="E32" t="inlineStr" s="11">
         <x:is>
-          <x:t>578585007</x:t>
+          <x:t>587416074</x:t>
         </x:is>
       </x:c>
       <x:c r="F32" s="13">
@@ -1816,7 +1816,7 @@
       </x:c>
       <x:c r="G32" t="inlineStr" s="15">
         <x:is>
-          <x:t>PP Cesar Levy</x:t>
+          <x:t>PP Michael Chenoy</x:t>
         </x:is>
       </x:c>
       <x:c r="H32" t="inlineStr" s="17">
@@ -1826,446 +1826,68 @@
       </x:c>
       <x:c r="I32" t="inlineStr" s="19">
         <x:is>
-          <x:t>CS - HVAC - Service - 12</x:t>
+          <x:t>PLM - HVAC - Service - 12</x:t>
         </x:is>
       </x:c>
       <x:c r="J32" t="inlineStr" s="21">
         <x:is>
-          <x:t>Serghei Arsentiev</x:t>
+          <x:t>Jian Jia </x:t>
         </x:is>
       </x:c>
       <x:c r="K32" s="23">
-        <x:v>46037</x:v>
+        <x:v>46106</x:v>
       </x:c>
       <x:c r="L32" s="25">
-        <x:v>46037</x:v>
+        <x:v>46106</x:v>
       </x:c>
     </x:row>
     <x:row r="33">
-      <x:c r="A33" t="inlineStr" s="3">
-        <x:is>
-          <x:t>HC - Return to Repair</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B33" t="n" s="5">
-        <x:v>292.95</x:v>
-      </x:c>
-      <x:c r="C33" t="inlineStr" s="7">
-        <x:is>
-          <x:t>Baker Supply, Club Member, Parts Received , PLM</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D33" t="inlineStr" s="9">
-        <x:is>
-          <x:t>586875916</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="E33" t="inlineStr" s="11">
-        <x:is>
-          <x:t>586875916</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="F33" s="13">
-        <x:v>46108</x:v>
-      </x:c>
-      <x:c r="G33" t="inlineStr" s="15">
-        <x:is>
-          <x:t>PP Barrington Wilson</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="H33" t="inlineStr" s="17">
-        <x:is>
-          <x:t>Hold</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="I33" t="inlineStr" s="19">
-        <x:is>
-          <x:t>CS - HVAC - Service - 12</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="J33" t="inlineStr" s="21">
-        <x:is>
-          <x:t>Anna Tyulmenkova</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="K33" s="23">
-        <x:v>46100</x:v>
-      </x:c>
-      <x:c r="L33" s="25">
-        <x:v>46100</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="34">
-      <x:c r="A34" t="inlineStr" s="3">
-        <x:is>
-          <x:t>HC - Return to Repair</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B34" t="n" s="5">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="C34" t="inlineStr" s="7">
-        <x:is>
-          <x:t>Carrier enterprise, Parts Ordered, PLM, Potential Member</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D34" t="inlineStr" s="9">
-        <x:is>
-          <x:t>583259145</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="E34" t="inlineStr" s="11">
-        <x:is>
-          <x:t>583259145</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="F34" s="13">
-        <x:v>46108</x:v>
-      </x:c>
-      <x:c r="G34" t="inlineStr" s="15">
+      <x:c r="A33" t="n" s="4">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="B33" t="n" s="6">
+        <x:v>692.08419354838709677419354839</x:v>
+      </x:c>
+      <x:c r="C33" t="inlineStr" s="8">
         <x:is>
           <x:t/>
         </x:is>
       </x:c>
-      <x:c r="H34" t="inlineStr" s="17">
-        <x:is>
-          <x:t>Hold</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="I34" t="inlineStr" s="19">
-        <x:is>
-          <x:t>CS - HVAC - Service - 12</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="J34" t="inlineStr" s="21">
-        <x:is>
-          <x:t>John Moore</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="K34" s="23">
-        <x:v>46070</x:v>
-      </x:c>
-      <x:c r="L34" s="25">
-        <x:v>46070</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="35">
-      <x:c r="A35" t="inlineStr" s="3">
-        <x:is>
-          <x:t>HC - Return to Repair</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B35" t="n" s="5">
-        <x:v>808.4</x:v>
-      </x:c>
-      <x:c r="C35" t="inlineStr" s="7">
-        <x:is>
-          <x:t>Club Member, Need to order part (NTO), PLM</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D35" t="inlineStr" s="9">
-        <x:is>
-          <x:t>587598604</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="E35" t="inlineStr" s="11">
-        <x:is>
-          <x:t>587598604</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="F35" s="13">
-        <x:v>46108</x:v>
-      </x:c>
-      <x:c r="G35" t="inlineStr" s="15">
-        <x:is>
-          <x:t>PP Barrington Wilson</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="H35" t="inlineStr" s="17">
-        <x:is>
-          <x:t>Hold</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="I35" t="inlineStr" s="19">
-        <x:is>
-          <x:t>PLM - HVAC - Service - 12</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="J35" t="inlineStr" s="21">
-        <x:is>
-          <x:t>DIVINCENZO, ANTHONY</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="K35" s="23">
-        <x:v>46107</x:v>
-      </x:c>
-      <x:c r="L35" s="25">
-        <x:v>46107</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="36">
-      <x:c r="A36" t="inlineStr" s="3">
-        <x:is>
-          <x:t>HC - Return to Repair</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B36" t="n" s="5">
-        <x:v>292.95</x:v>
-      </x:c>
-      <x:c r="C36" t="inlineStr" s="7">
-        <x:is>
-          <x:t>Baker Supply, Club Member, Parts Ordered, PLM</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D36" t="inlineStr" s="9">
-        <x:is>
-          <x:t>587301961</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="E36" t="inlineStr" s="11">
-        <x:is>
-          <x:t>587301961</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="F36" s="13">
-        <x:v>46108</x:v>
-      </x:c>
-      <x:c r="G36" t="inlineStr" s="15">
-        <x:is>
-          <x:t>Jesse Dague</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="H36" t="inlineStr" s="17">
-        <x:is>
-          <x:t>Hold</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="I36" t="inlineStr" s="19">
-        <x:is>
-          <x:t>CS - HVAC - Service - 12</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="J36" t="inlineStr" s="21">
-        <x:is>
-          <x:t>CHACON, LERA</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="K36" s="23">
-        <x:v>46105</x:v>
-      </x:c>
-      <x:c r="L36" s="25">
-        <x:v>46105</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="37">
-      <x:c r="A37" t="inlineStr" s="3">
-        <x:is>
-          <x:t>HC - Return to Repair</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B37" t="n" s="5">
-        <x:v>2405.92</x:v>
-      </x:c>
-      <x:c r="C37" t="inlineStr" s="7">
-        <x:is>
-          <x:t>Baker Supply, Parts Ordered, Potential Member</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D37" t="inlineStr" s="9">
-        <x:is>
-          <x:t>578394047</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="E37" t="inlineStr" s="11">
-        <x:is>
-          <x:t>578394047</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="F37" s="13">
-        <x:v>46108</x:v>
-      </x:c>
-      <x:c r="G37" t="inlineStr" s="15">
-        <x:is>
-          <x:t>PP Gurpreet Parihar</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="H37" t="inlineStr" s="17">
-        <x:is>
-          <x:t>Hold</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="I37" t="inlineStr" s="19">
-        <x:is>
-          <x:t>PLM - HVAC - Service - 12</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="J37" t="inlineStr" s="21">
-        <x:is>
-          <x:t>Edgar Irving</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="K37" s="23">
-        <x:v>46036</x:v>
-      </x:c>
-      <x:c r="L37" s="25">
-        <x:v>46036</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="38">
-      <x:c r="A38" t="inlineStr" s="3">
-        <x:is>
-          <x:t>HC - Return to Repair</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B38" t="n" s="5">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="C38" t="inlineStr" s="7">
-        <x:is>
-          <x:t>10-Year Labor, 10-Year Labor, 10-Year Labor, 10-Year Labor, 10-Year Labor, Club Member, Goodman distribution , Parts Ordered</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D38" t="inlineStr" s="9">
-        <x:is>
-          <x:t>585388429</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="E38" t="inlineStr" s="11">
-        <x:is>
-          <x:t>585388429</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="F38" s="13">
-        <x:v>46108</x:v>
-      </x:c>
-      <x:c r="G38" t="inlineStr" s="15">
-        <x:is>
-          <x:t>Rickey McClam </x:t>
-        </x:is>
-      </x:c>
-      <x:c r="H38" t="inlineStr" s="17">
-        <x:is>
-          <x:t>Hold</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="I38" t="inlineStr" s="19">
-        <x:is>
-          <x:t>CS - HVAC - Service - 12</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="J38" t="inlineStr" s="21">
-        <x:is>
-          <x:t>Charles Funkey</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="K38" s="23">
-        <x:v>46086</x:v>
-      </x:c>
-      <x:c r="L38" s="25">
-        <x:v>46086</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="39">
-      <x:c r="A39" t="inlineStr" s="3">
-        <x:is>
-          <x:t>HC - Return to Repair</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B39" t="n" s="5">
-        <x:v>2125</x:v>
-      </x:c>
-      <x:c r="C39" t="inlineStr" s="7">
-        <x:is>
-          <x:t>Carrier enterprise, Parts Received , Potential Member</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D39" t="inlineStr" s="9">
-        <x:is>
-          <x:t>587416074</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="E39" t="inlineStr" s="11">
-        <x:is>
-          <x:t>587416074</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="F39" s="13">
-        <x:v>46108</x:v>
-      </x:c>
-      <x:c r="G39" t="inlineStr" s="15">
-        <x:is>
-          <x:t>PP Michael Chenoy</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="H39" t="inlineStr" s="17">
-        <x:is>
-          <x:t>Hold</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="I39" t="inlineStr" s="19">
-        <x:is>
-          <x:t>PLM - HVAC - Service - 12</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="J39" t="inlineStr" s="21">
-        <x:is>
-          <x:t>Jian Jia </x:t>
-        </x:is>
-      </x:c>
-      <x:c r="K39" s="23">
-        <x:v>46106</x:v>
-      </x:c>
-      <x:c r="L39" s="25">
-        <x:v>46106</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="40">
-      <x:c r="A40" t="n" s="4">
-        <x:v>38</x:v>
-      </x:c>
-      <x:c r="B40" t="n" s="6">
-        <x:v>657.45026315789473684210526316</x:v>
-      </x:c>
-      <x:c r="C40" t="inlineStr" s="8">
+      <x:c r="D33" t="n" s="10">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="E33" t="inlineStr" s="12">
         <x:is>
           <x:t/>
         </x:is>
       </x:c>
-      <x:c r="D40" t="n" s="10">
-        <x:v>38</x:v>
-      </x:c>
-      <x:c r="E40" t="inlineStr" s="12">
+      <x:c r="F33" s="14">
+        <x:v/>
+      </x:c>
+      <x:c r="G33" t="inlineStr" s="16">
         <x:is>
           <x:t/>
         </x:is>
       </x:c>
-      <x:c r="F40" s="14">
+      <x:c r="H33" t="inlineStr" s="18">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+      <x:c r="I33" t="inlineStr" s="20">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+      <x:c r="J33" t="inlineStr" s="22">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+      <x:c r="K33" s="24">
         <x:v/>
       </x:c>
-      <x:c r="G40" t="inlineStr" s="16">
-        <x:is>
-          <x:t/>
-        </x:is>
-      </x:c>
-      <x:c r="H40" t="inlineStr" s="18">
-        <x:is>
-          <x:t/>
-        </x:is>
-      </x:c>
-      <x:c r="I40" t="inlineStr" s="20">
-        <x:is>
-          <x:t/>
-        </x:is>
-      </x:c>
-      <x:c r="J40" t="inlineStr" s="22">
-        <x:is>
-          <x:t/>
-        </x:is>
-      </x:c>
-      <x:c r="K40" s="24">
-        <x:v/>
-      </x:c>
-      <x:c r="L40" s="26">
+      <x:c r="L33" s="26">
         <x:v/>
       </x:c>
     </x:row>

--- a/data/parts_report_past.xlsx
+++ b/data/parts_report_past.xlsx
@@ -5,8 +5,8 @@
     <x:workbookView/>
   </x:bookViews>
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R5d3c5b9ee3bb4cb0"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Filters" sheetId="2" r:id="Re04a7bc8b8684abd"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rca6e9244e0be4e06"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Filters" sheetId="2" r:id="R31f840ab955e4ea8"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -930,21 +930,21 @@
         </x:is>
       </x:c>
       <x:c r="B16" t="n" s="5">
-        <x:v>1615.83</x:v>
+        <x:v>225</x:v>
       </x:c>
       <x:c r="C16" t="inlineStr" s="7">
         <x:is>
-          <x:t>Club Member, Parts Received </x:t>
+          <x:t>12-Year Labor, 12-Year Labor, 12-Year Labor, 12-Year Labor, 12-Year Labor, Carrier enterprise, Club Member 2 sys , MULTI- 2, Parts Received , PLM</x:t>
         </x:is>
       </x:c>
       <x:c r="D16" t="inlineStr" s="9">
         <x:is>
-          <x:t>587337488</x:t>
+          <x:t>586903562</x:t>
         </x:is>
       </x:c>
       <x:c r="E16" t="inlineStr" s="11">
         <x:is>
-          <x:t>587337488</x:t>
+          <x:t>586903562</x:t>
         </x:is>
       </x:c>
       <x:c r="F16" s="13">
@@ -952,7 +952,7 @@
       </x:c>
       <x:c r="G16" t="inlineStr" s="15">
         <x:is>
-          <x:t>PP Demitri Semexant</x:t>
+          <x:t>PP Braxton Patterson </x:t>
         </x:is>
       </x:c>
       <x:c r="H16" t="inlineStr" s="17">
@@ -967,14 +967,14 @@
       </x:c>
       <x:c r="J16" t="inlineStr" s="21">
         <x:is>
-          <x:t>Sabrina Rodriguez</x:t>
+          <x:t>Ruth  Hochberg</x:t>
         </x:is>
       </x:c>
       <x:c r="K16" s="23">
-        <x:v>46105</x:v>
+        <x:v>46100</x:v>
       </x:c>
       <x:c r="L16" s="25">
-        <x:v>46105</x:v>
+        <x:v>46100</x:v>
       </x:c>
     </x:row>
     <x:row r="17">
@@ -984,21 +984,21 @@
         </x:is>
       </x:c>
       <x:c r="B17" t="n" s="5">
-        <x:v>225</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="C17" t="inlineStr" s="7">
         <x:is>
-          <x:t>12-Year Labor, 12-Year Labor, 12-Year Labor, 12-Year Labor, 12-Year Labor, Carrier enterprise, Club Member 2 sys , MULTI- 2, Parts Received , PLM</x:t>
+          <x:t>10-10-10, 10-10-10, Carrier enterprise, Club Member, Parts Received , PLM</x:t>
         </x:is>
       </x:c>
       <x:c r="D17" t="inlineStr" s="9">
         <x:is>
-          <x:t>586903562</x:t>
+          <x:t>586982846</x:t>
         </x:is>
       </x:c>
       <x:c r="E17" t="inlineStr" s="11">
         <x:is>
-          <x:t>586903562</x:t>
+          <x:t>586982846</x:t>
         </x:is>
       </x:c>
       <x:c r="F17" s="13">
@@ -1006,7 +1006,7 @@
       </x:c>
       <x:c r="G17" t="inlineStr" s="15">
         <x:is>
-          <x:t>PP Braxton Patterson </x:t>
+          <x:t>Rickey McClam </x:t>
         </x:is>
       </x:c>
       <x:c r="H17" t="inlineStr" s="17">
@@ -1016,19 +1016,19 @@
       </x:c>
       <x:c r="I17" t="inlineStr" s="19">
         <x:is>
-          <x:t>CS - HVAC - Service - 12</x:t>
+          <x:t>PLM - HVAC - Service - 12</x:t>
         </x:is>
       </x:c>
       <x:c r="J17" t="inlineStr" s="21">
         <x:is>
-          <x:t>Ruth  Hochberg</x:t>
+          <x:t>Gwyn Bonasoro</x:t>
         </x:is>
       </x:c>
       <x:c r="K17" s="23">
-        <x:v>46100</x:v>
+        <x:v>46101</x:v>
       </x:c>
       <x:c r="L17" s="25">
-        <x:v>46100</x:v>
+        <x:v>46101</x:v>
       </x:c>
     </x:row>
     <x:row r="18">
@@ -1038,51 +1038,51 @@
         </x:is>
       </x:c>
       <x:c r="B18" t="n" s="5">
-        <x:v>0</x:v>
+        <x:v>689.97</x:v>
       </x:c>
       <x:c r="C18" t="inlineStr" s="7">
         <x:is>
-          <x:t>10-10-10, 10-10-10, Carrier enterprise, Club Member, Parts Received , PLM</x:t>
+          <x:t>2-YR Labor Warranty, 2-YR Labor Warranty, 2-YR Labor Warranty, Club Member, Gemaire, Parts Received </x:t>
         </x:is>
       </x:c>
       <x:c r="D18" t="inlineStr" s="9">
         <x:is>
-          <x:t>586982846</x:t>
+          <x:t>587253199</x:t>
         </x:is>
       </x:c>
       <x:c r="E18" t="inlineStr" s="11">
         <x:is>
-          <x:t>586982846</x:t>
+          <x:t>587253199</x:t>
         </x:is>
       </x:c>
       <x:c r="F18" s="13">
+        <x:v>46106</x:v>
+      </x:c>
+      <x:c r="G18" t="inlineStr" s="15">
+        <x:is>
+          <x:t>PP Barrington Wilson</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="H18" t="inlineStr" s="17">
+        <x:is>
+          <x:t>Hold</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="I18" t="inlineStr" s="19">
+        <x:is>
+          <x:t>CS - HVAC - Service - 12</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="J18" t="inlineStr" s="21">
+        <x:is>
+          <x:t>Dane Lyons</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="K18" s="23">
         <x:v>46105</x:v>
       </x:c>
-      <x:c r="G18" t="inlineStr" s="15">
-        <x:is>
-          <x:t>Rickey McClam </x:t>
-        </x:is>
-      </x:c>
-      <x:c r="H18" t="inlineStr" s="17">
-        <x:is>
-          <x:t>Hold</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="I18" t="inlineStr" s="19">
-        <x:is>
-          <x:t>PLM - HVAC - Service - 12</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="J18" t="inlineStr" s="21">
-        <x:is>
-          <x:t>Gwyn Bonasoro</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="K18" s="23">
-        <x:v>46101</x:v>
-      </x:c>
       <x:c r="L18" s="25">
-        <x:v>46101</x:v>
+        <x:v>46105</x:v>
       </x:c>
     </x:row>
     <x:row r="19">
@@ -1092,21 +1092,21 @@
         </x:is>
       </x:c>
       <x:c r="B19" t="n" s="5">
-        <x:v>689.97</x:v>
+        <x:v>722.79</x:v>
       </x:c>
       <x:c r="C19" t="inlineStr" s="7">
         <x:is>
-          <x:t>2-YR Labor Warranty, 2-YR Labor Warranty, 2-YR Labor Warranty, Club Member, Gemaire, Parts Received </x:t>
+          <x:t>Baker Supply, Parts Ordered, PLM, Potential Member</x:t>
         </x:is>
       </x:c>
       <x:c r="D19" t="inlineStr" s="9">
         <x:is>
-          <x:t>587253199</x:t>
+          <x:t>459781920</x:t>
         </x:is>
       </x:c>
       <x:c r="E19" t="inlineStr" s="11">
         <x:is>
-          <x:t>587253199</x:t>
+          <x:t>459781920</x:t>
         </x:is>
       </x:c>
       <x:c r="F19" s="13">
@@ -1114,7 +1114,7 @@
       </x:c>
       <x:c r="G19" t="inlineStr" s="15">
         <x:is>
-          <x:t>PP Barrington Wilson</x:t>
+          <x:t>PLM-Quentin Stewart</x:t>
         </x:is>
       </x:c>
       <x:c r="H19" t="inlineStr" s="17">
@@ -1124,19 +1124,19 @@
       </x:c>
       <x:c r="I19" t="inlineStr" s="19">
         <x:is>
-          <x:t>CS - HVAC - Service - 12</x:t>
+          <x:t>PLM - HVAC - Service - 12</x:t>
         </x:is>
       </x:c>
       <x:c r="J19" t="inlineStr" s="21">
         <x:is>
-          <x:t>Dane Lyons</x:t>
+          <x:t>Gluck Carolyn</x:t>
         </x:is>
       </x:c>
       <x:c r="K19" s="23">
-        <x:v>46105</x:v>
+        <x:v>45726</x:v>
       </x:c>
       <x:c r="L19" s="25">
-        <x:v>46105</x:v>
+        <x:v>45726</x:v>
       </x:c>
     </x:row>
     <x:row r="20">
@@ -1146,29 +1146,29 @@
         </x:is>
       </x:c>
       <x:c r="B20" t="n" s="5">
-        <x:v>722.79</x:v>
+        <x:v>294.96</x:v>
       </x:c>
       <x:c r="C20" t="inlineStr" s="7">
         <x:is>
-          <x:t>Baker Supply, Parts Ordered, PLM, Potential Member</x:t>
+          <x:t>10-10-10, 10-10-10, Club Member, Club Member (Additional System), MULTI- 2, Parts Ordered, Trane Supply</x:t>
         </x:is>
       </x:c>
       <x:c r="D20" t="inlineStr" s="9">
         <x:is>
-          <x:t>459781920</x:t>
+          <x:t>554624809</x:t>
         </x:is>
       </x:c>
       <x:c r="E20" t="inlineStr" s="11">
         <x:is>
-          <x:t>459781920</x:t>
+          <x:t>554624809</x:t>
         </x:is>
       </x:c>
       <x:c r="F20" s="13">
-        <x:v>46106</x:v>
+        <x:v>46107</x:v>
       </x:c>
       <x:c r="G20" t="inlineStr" s="15">
         <x:is>
-          <x:t>PLM-Quentin Stewart</x:t>
+          <x:t>PP Carlos Machado</x:t>
         </x:is>
       </x:c>
       <x:c r="H20" t="inlineStr" s="17">
@@ -1178,19 +1178,19 @@
       </x:c>
       <x:c r="I20" t="inlineStr" s="19">
         <x:is>
-          <x:t>PLM - HVAC - Service - 12</x:t>
+          <x:t>CS - HVAC - Service - 12</x:t>
         </x:is>
       </x:c>
       <x:c r="J20" t="inlineStr" s="21">
         <x:is>
-          <x:t>Gluck Carolyn</x:t>
+          <x:t>Michael &amp; Delle Lenzen</x:t>
         </x:is>
       </x:c>
       <x:c r="K20" s="23">
-        <x:v>45726</x:v>
+        <x:v>45996</x:v>
       </x:c>
       <x:c r="L20" s="25">
-        <x:v>45726</x:v>
+        <x:v>45996</x:v>
       </x:c>
     </x:row>
     <x:row r="21">
@@ -1200,21 +1200,21 @@
         </x:is>
       </x:c>
       <x:c r="B21" t="n" s="5">
-        <x:v>294.96</x:v>
+        <x:v>3247.45</x:v>
       </x:c>
       <x:c r="C21" t="inlineStr" s="7">
         <x:is>
-          <x:t>10-10-10, 10-10-10, Club Member, Club Member (Additional System), MULTI- 2, Parts Ordered, Trane Supply</x:t>
+          <x:t>10-Year Labor, Club Member, Club Member 2 sys , Gemaire, Parts Received , PLM</x:t>
         </x:is>
       </x:c>
       <x:c r="D21" t="inlineStr" s="9">
         <x:is>
-          <x:t>554624809</x:t>
+          <x:t>587314216</x:t>
         </x:is>
       </x:c>
       <x:c r="E21" t="inlineStr" s="11">
         <x:is>
-          <x:t>554624809</x:t>
+          <x:t>587314216</x:t>
         </x:is>
       </x:c>
       <x:c r="F21" s="13">
@@ -1222,7 +1222,7 @@
       </x:c>
       <x:c r="G21" t="inlineStr" s="15">
         <x:is>
-          <x:t>PP Carlos Machado</x:t>
+          <x:t>Rolin Moimeme</x:t>
         </x:is>
       </x:c>
       <x:c r="H21" t="inlineStr" s="17">
@@ -1237,14 +1237,14 @@
       </x:c>
       <x:c r="J21" t="inlineStr" s="21">
         <x:is>
-          <x:t>Michael &amp; Delle Lenzen</x:t>
+          <x:t>FRIEDMAN, SAMANTHA</x:t>
         </x:is>
       </x:c>
       <x:c r="K21" s="23">
-        <x:v>45996</x:v>
+        <x:v>46105</x:v>
       </x:c>
       <x:c r="L21" s="25">
-        <x:v>45996</x:v>
+        <x:v>46105</x:v>
       </x:c>
     </x:row>
     <x:row r="22">
@@ -1254,29 +1254,29 @@
         </x:is>
       </x:c>
       <x:c r="B22" t="n" s="5">
-        <x:v>3247.45</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="C22" t="inlineStr" s="7">
         <x:is>
-          <x:t>10-Year Labor, Club Member, Club Member 2 sys , Gemaire, Parts Received , PLM</x:t>
+          <x:t>Club Member, Gemaire, Parts Received </x:t>
         </x:is>
       </x:c>
       <x:c r="D22" t="inlineStr" s="9">
         <x:is>
-          <x:t>587314216</x:t>
+          <x:t>587448096</x:t>
         </x:is>
       </x:c>
       <x:c r="E22" t="inlineStr" s="11">
         <x:is>
-          <x:t>587314216</x:t>
+          <x:t>587448096</x:t>
         </x:is>
       </x:c>
       <x:c r="F22" s="13">
-        <x:v>46107</x:v>
+        <x:v>46108</x:v>
       </x:c>
       <x:c r="G22" t="inlineStr" s="15">
         <x:is>
-          <x:t>Rolin Moimeme</x:t>
+          <x:t/>
         </x:is>
       </x:c>
       <x:c r="H22" t="inlineStr" s="17">
@@ -1286,19 +1286,19 @@
       </x:c>
       <x:c r="I22" t="inlineStr" s="19">
         <x:is>
-          <x:t>CS - HVAC - Service - 12</x:t>
+          <x:t>PLM - HVAC - Service - 12</x:t>
         </x:is>
       </x:c>
       <x:c r="J22" t="inlineStr" s="21">
         <x:is>
-          <x:t>FRIEDMAN, SAMANTHA</x:t>
+          <x:t>Cassandra Sexton</x:t>
         </x:is>
       </x:c>
       <x:c r="K22" s="23">
-        <x:v>46105</x:v>
+        <x:v>46106</x:v>
       </x:c>
       <x:c r="L22" s="25">
-        <x:v>46105</x:v>
+        <x:v>46106</x:v>
       </x:c>
     </x:row>
     <x:row r="23">
@@ -1312,17 +1312,17 @@
       </x:c>
       <x:c r="C23" t="inlineStr" s="7">
         <x:is>
-          <x:t>Club Member, Gemaire, Parts Ordered</x:t>
+          <x:t>Club Member, LW- 2 YEAR LABOR, Parts Ordered, Trane Supply</x:t>
         </x:is>
       </x:c>
       <x:c r="D23" t="inlineStr" s="9">
         <x:is>
-          <x:t>587448096</x:t>
+          <x:t>587077196</x:t>
         </x:is>
       </x:c>
       <x:c r="E23" t="inlineStr" s="11">
         <x:is>
-          <x:t>587448096</x:t>
+          <x:t>587077196</x:t>
         </x:is>
       </x:c>
       <x:c r="F23" s="13">
@@ -1330,7 +1330,7 @@
       </x:c>
       <x:c r="G23" t="inlineStr" s="15">
         <x:is>
-          <x:t/>
+          <x:t>Tyler Gallatin</x:t>
         </x:is>
       </x:c>
       <x:c r="H23" t="inlineStr" s="17">
@@ -1340,19 +1340,19 @@
       </x:c>
       <x:c r="I23" t="inlineStr" s="19">
         <x:is>
-          <x:t>PLM - HVAC - Service - 12</x:t>
+          <x:t>CS - HVAC - Service - 12</x:t>
         </x:is>
       </x:c>
       <x:c r="J23" t="inlineStr" s="21">
         <x:is>
-          <x:t>Cassandra Sexton</x:t>
+          <x:t>Timberwalk Association Inc</x:t>
         </x:is>
       </x:c>
       <x:c r="K23" s="23">
-        <x:v>46106</x:v>
+        <x:v>46102</x:v>
       </x:c>
       <x:c r="L23" s="25">
-        <x:v>46106</x:v>
+        <x:v>46102</x:v>
       </x:c>
     </x:row>
     <x:row r="24">
@@ -1362,21 +1362,21 @@
         </x:is>
       </x:c>
       <x:c r="B24" t="n" s="5">
-        <x:v>0</x:v>
+        <x:v>1248.8</x:v>
       </x:c>
       <x:c r="C24" t="inlineStr" s="7">
         <x:is>
-          <x:t>Club Member, LW- 2 YEAR LABOR, Parts Ordered, Trane Supply</x:t>
+          <x:t>Club Member, Lennox Supply, Parts Received </x:t>
         </x:is>
       </x:c>
       <x:c r="D24" t="inlineStr" s="9">
         <x:is>
-          <x:t>587077196</x:t>
+          <x:t>587303898</x:t>
         </x:is>
       </x:c>
       <x:c r="E24" t="inlineStr" s="11">
         <x:is>
-          <x:t>587077196</x:t>
+          <x:t>587303898</x:t>
         </x:is>
       </x:c>
       <x:c r="F24" s="13">
@@ -1384,7 +1384,7 @@
       </x:c>
       <x:c r="G24" t="inlineStr" s="15">
         <x:is>
-          <x:t>Tyler Gallatin</x:t>
+          <x:t>Xavier Mateo</x:t>
         </x:is>
       </x:c>
       <x:c r="H24" t="inlineStr" s="17">
@@ -1399,14 +1399,14 @@
       </x:c>
       <x:c r="J24" t="inlineStr" s="21">
         <x:is>
-          <x:t>Timberwalk Association Inc</x:t>
+          <x:t>ROBERT MCCABE</x:t>
         </x:is>
       </x:c>
       <x:c r="K24" s="23">
-        <x:v>46102</x:v>
+        <x:v>46105</x:v>
       </x:c>
       <x:c r="L24" s="25">
-        <x:v>46102</x:v>
+        <x:v>46105</x:v>
       </x:c>
     </x:row>
     <x:row r="25">
@@ -1416,21 +1416,21 @@
         </x:is>
       </x:c>
       <x:c r="B25" t="n" s="5">
-        <x:v>1248.8</x:v>
+        <x:v>1267.95</x:v>
       </x:c>
       <x:c r="C25" t="inlineStr" s="7">
         <x:is>
-          <x:t>Club Member, Lennox Supply, Parts Ordered</x:t>
+          <x:t>Club Member 3 sys, Gemaire, Parts Received </x:t>
         </x:is>
       </x:c>
       <x:c r="D25" t="inlineStr" s="9">
         <x:is>
-          <x:t>587303898</x:t>
+          <x:t>578585007</x:t>
         </x:is>
       </x:c>
       <x:c r="E25" t="inlineStr" s="11">
         <x:is>
-          <x:t>587303898</x:t>
+          <x:t>578585007</x:t>
         </x:is>
       </x:c>
       <x:c r="F25" s="13">
@@ -1438,7 +1438,7 @@
       </x:c>
       <x:c r="G25" t="inlineStr" s="15">
         <x:is>
-          <x:t>Xavier Mateo</x:t>
+          <x:t>PP Cesar Levy</x:t>
         </x:is>
       </x:c>
       <x:c r="H25" t="inlineStr" s="17">
@@ -1453,14 +1453,14 @@
       </x:c>
       <x:c r="J25" t="inlineStr" s="21">
         <x:is>
-          <x:t>ROBERT MCCABE</x:t>
+          <x:t>Serghei Arsentiev</x:t>
         </x:is>
       </x:c>
       <x:c r="K25" s="23">
-        <x:v>46105</x:v>
+        <x:v>46037</x:v>
       </x:c>
       <x:c r="L25" s="25">
-        <x:v>46105</x:v>
+        <x:v>46037</x:v>
       </x:c>
     </x:row>
     <x:row r="26">
@@ -1470,21 +1470,21 @@
         </x:is>
       </x:c>
       <x:c r="B26" t="n" s="5">
-        <x:v>1267.95</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="C26" t="inlineStr" s="7">
         <x:is>
-          <x:t>Club Member 3 sys, Gemaire, Parts Received </x:t>
+          <x:t>Carrier enterprise, Parts Ordered, PLM, Potential Member</x:t>
         </x:is>
       </x:c>
       <x:c r="D26" t="inlineStr" s="9">
         <x:is>
-          <x:t>578585007</x:t>
+          <x:t>583259145</x:t>
         </x:is>
       </x:c>
       <x:c r="E26" t="inlineStr" s="11">
         <x:is>
-          <x:t>578585007</x:t>
+          <x:t>583259145</x:t>
         </x:is>
       </x:c>
       <x:c r="F26" s="13">
@@ -1492,7 +1492,7 @@
       </x:c>
       <x:c r="G26" t="inlineStr" s="15">
         <x:is>
-          <x:t>PP Cesar Levy</x:t>
+          <x:t/>
         </x:is>
       </x:c>
       <x:c r="H26" t="inlineStr" s="17">
@@ -1507,14 +1507,14 @@
       </x:c>
       <x:c r="J26" t="inlineStr" s="21">
         <x:is>
-          <x:t>Serghei Arsentiev</x:t>
+          <x:t>John Moore</x:t>
         </x:is>
       </x:c>
       <x:c r="K26" s="23">
-        <x:v>46037</x:v>
+        <x:v>46070</x:v>
       </x:c>
       <x:c r="L26" s="25">
-        <x:v>46037</x:v>
+        <x:v>46070</x:v>
       </x:c>
     </x:row>
     <x:row r="27">
@@ -1524,21 +1524,21 @@
         </x:is>
       </x:c>
       <x:c r="B27" t="n" s="5">
-        <x:v>0</x:v>
+        <x:v>1605.6</x:v>
       </x:c>
       <x:c r="C27" t="inlineStr" s="7">
         <x:is>
-          <x:t>Carrier enterprise, Parts Ordered, PLM, Potential Member</x:t>
+          <x:t>Club Member, Club Member (Additional System), Parts Ordered, PLM</x:t>
         </x:is>
       </x:c>
       <x:c r="D27" t="inlineStr" s="9">
         <x:is>
-          <x:t>583259145</x:t>
+          <x:t>587681974</x:t>
         </x:is>
       </x:c>
       <x:c r="E27" t="inlineStr" s="11">
         <x:is>
-          <x:t>583259145</x:t>
+          <x:t>587681974</x:t>
         </x:is>
       </x:c>
       <x:c r="F27" s="13">
@@ -1546,7 +1546,7 @@
       </x:c>
       <x:c r="G27" t="inlineStr" s="15">
         <x:is>
-          <x:t/>
+          <x:t>PP Barrington Wilson</x:t>
         </x:is>
       </x:c>
       <x:c r="H27" t="inlineStr" s="17">
@@ -1561,14 +1561,14 @@
       </x:c>
       <x:c r="J27" t="inlineStr" s="21">
         <x:is>
-          <x:t>John Moore</x:t>
+          <x:t>MACLACHLAN, DAN</x:t>
         </x:is>
       </x:c>
       <x:c r="K27" s="23">
-        <x:v>46070</x:v>
+        <x:v>46108</x:v>
       </x:c>
       <x:c r="L27" s="25">
-        <x:v>46070</x:v>
+        <x:v>46108</x:v>
       </x:c>
     </x:row>
     <x:row r="28">
@@ -1578,21 +1578,21 @@
         </x:is>
       </x:c>
       <x:c r="B28" t="n" s="5">
-        <x:v>808.4</x:v>
+        <x:v>292.95</x:v>
       </x:c>
       <x:c r="C28" t="inlineStr" s="7">
         <x:is>
-          <x:t>Carrier enterprise, Club Member, Parts Ordered, PLM</x:t>
+          <x:t>Baker Supply, Club Member, Parts Received , PLM</x:t>
         </x:is>
       </x:c>
       <x:c r="D28" t="inlineStr" s="9">
         <x:is>
-          <x:t>587598604</x:t>
+          <x:t>587301961</x:t>
         </x:is>
       </x:c>
       <x:c r="E28" t="inlineStr" s="11">
         <x:is>
-          <x:t>587598604</x:t>
+          <x:t>587301961</x:t>
         </x:is>
       </x:c>
       <x:c r="F28" s="13">
@@ -1600,7 +1600,7 @@
       </x:c>
       <x:c r="G28" t="inlineStr" s="15">
         <x:is>
-          <x:t>PP Barrington Wilson</x:t>
+          <x:t>Jesse Dague</x:t>
         </x:is>
       </x:c>
       <x:c r="H28" t="inlineStr" s="17">
@@ -1610,19 +1610,19 @@
       </x:c>
       <x:c r="I28" t="inlineStr" s="19">
         <x:is>
-          <x:t>PLM - HVAC - Service - 12</x:t>
+          <x:t>CS - HVAC - Service - 12</x:t>
         </x:is>
       </x:c>
       <x:c r="J28" t="inlineStr" s="21">
         <x:is>
-          <x:t>DIVINCENZO, ANTHONY</x:t>
+          <x:t>CHACON, LERA</x:t>
         </x:is>
       </x:c>
       <x:c r="K28" s="23">
-        <x:v>46107</x:v>
+        <x:v>46105</x:v>
       </x:c>
       <x:c r="L28" s="25">
-        <x:v>46107</x:v>
+        <x:v>46105</x:v>
       </x:c>
     </x:row>
     <x:row r="29">
@@ -1632,21 +1632,21 @@
         </x:is>
       </x:c>
       <x:c r="B29" t="n" s="5">
-        <x:v>292.95</x:v>
+        <x:v>2405.92</x:v>
       </x:c>
       <x:c r="C29" t="inlineStr" s="7">
         <x:is>
-          <x:t>Baker Supply, Club Member, Parts Received , PLM</x:t>
+          <x:t>Baker Supply, Parts Ordered, Potential Member</x:t>
         </x:is>
       </x:c>
       <x:c r="D29" t="inlineStr" s="9">
         <x:is>
-          <x:t>587301961</x:t>
+          <x:t>578394047</x:t>
         </x:is>
       </x:c>
       <x:c r="E29" t="inlineStr" s="11">
         <x:is>
-          <x:t>587301961</x:t>
+          <x:t>578394047</x:t>
         </x:is>
       </x:c>
       <x:c r="F29" s="13">
@@ -1654,7 +1654,7 @@
       </x:c>
       <x:c r="G29" t="inlineStr" s="15">
         <x:is>
-          <x:t>Jesse Dague</x:t>
+          <x:t>PP Gurpreet Parihar</x:t>
         </x:is>
       </x:c>
       <x:c r="H29" t="inlineStr" s="17">
@@ -1664,19 +1664,19 @@
       </x:c>
       <x:c r="I29" t="inlineStr" s="19">
         <x:is>
-          <x:t>CS - HVAC - Service - 12</x:t>
+          <x:t>PLM - HVAC - Service - 12</x:t>
         </x:is>
       </x:c>
       <x:c r="J29" t="inlineStr" s="21">
         <x:is>
-          <x:t>CHACON, LERA</x:t>
+          <x:t>Edgar Irving</x:t>
         </x:is>
       </x:c>
       <x:c r="K29" s="23">
-        <x:v>46105</x:v>
+        <x:v>46036</x:v>
       </x:c>
       <x:c r="L29" s="25">
-        <x:v>46105</x:v>
+        <x:v>46036</x:v>
       </x:c>
     </x:row>
     <x:row r="30">
@@ -1686,21 +1686,21 @@
         </x:is>
       </x:c>
       <x:c r="B30" t="n" s="5">
-        <x:v>2405.92</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="C30" t="inlineStr" s="7">
         <x:is>
-          <x:t>Baker Supply, Parts Ordered, Potential Member</x:t>
+          <x:t>10-Year Labor, 10-Year Labor, 10-Year Labor, 10-Year Labor, 10-Year Labor, Club Member, Goodman distribution , Parts Ordered</x:t>
         </x:is>
       </x:c>
       <x:c r="D30" t="inlineStr" s="9">
         <x:is>
-          <x:t>578394047</x:t>
+          <x:t>585388429</x:t>
         </x:is>
       </x:c>
       <x:c r="E30" t="inlineStr" s="11">
         <x:is>
-          <x:t>578394047</x:t>
+          <x:t>585388429</x:t>
         </x:is>
       </x:c>
       <x:c r="F30" s="13">
@@ -1708,7 +1708,7 @@
       </x:c>
       <x:c r="G30" t="inlineStr" s="15">
         <x:is>
-          <x:t>PP Gurpreet Parihar</x:t>
+          <x:t>Rickey McClam </x:t>
         </x:is>
       </x:c>
       <x:c r="H30" t="inlineStr" s="17">
@@ -1718,19 +1718,19 @@
       </x:c>
       <x:c r="I30" t="inlineStr" s="19">
         <x:is>
-          <x:t>PLM - HVAC - Service - 12</x:t>
+          <x:t>CS - HVAC - Service - 12</x:t>
         </x:is>
       </x:c>
       <x:c r="J30" t="inlineStr" s="21">
         <x:is>
-          <x:t>Edgar Irving</x:t>
+          <x:t>Charles Funkey</x:t>
         </x:is>
       </x:c>
       <x:c r="K30" s="23">
-        <x:v>46036</x:v>
+        <x:v>46086</x:v>
       </x:c>
       <x:c r="L30" s="25">
-        <x:v>46036</x:v>
+        <x:v>46086</x:v>
       </x:c>
     </x:row>
     <x:row r="31">
@@ -1740,21 +1740,21 @@
         </x:is>
       </x:c>
       <x:c r="B31" t="n" s="5">
-        <x:v>0</x:v>
+        <x:v>2125</x:v>
       </x:c>
       <x:c r="C31" t="inlineStr" s="7">
         <x:is>
-          <x:t>10-Year Labor, 10-Year Labor, 10-Year Labor, 10-Year Labor, 10-Year Labor, Club Member, Goodman distribution , Parts Ordered</x:t>
+          <x:t>Carrier enterprise, Parts Received , Potential Member</x:t>
         </x:is>
       </x:c>
       <x:c r="D31" t="inlineStr" s="9">
         <x:is>
-          <x:t>585388429</x:t>
+          <x:t>587416074</x:t>
         </x:is>
       </x:c>
       <x:c r="E31" t="inlineStr" s="11">
         <x:is>
-          <x:t>585388429</x:t>
+          <x:t>587416074</x:t>
         </x:is>
       </x:c>
       <x:c r="F31" s="13">
@@ -1762,7 +1762,7 @@
       </x:c>
       <x:c r="G31" t="inlineStr" s="15">
         <x:is>
-          <x:t>Rickey McClam </x:t>
+          <x:t>PP Michael Chenoy</x:t>
         </x:is>
       </x:c>
       <x:c r="H31" t="inlineStr" s="17">
@@ -1772,122 +1772,68 @@
       </x:c>
       <x:c r="I31" t="inlineStr" s="19">
         <x:is>
-          <x:t>CS - HVAC - Service - 12</x:t>
+          <x:t>PLM - HVAC - Service - 12</x:t>
         </x:is>
       </x:c>
       <x:c r="J31" t="inlineStr" s="21">
         <x:is>
-          <x:t>Charles Funkey</x:t>
+          <x:t>Jian Jia </x:t>
         </x:is>
       </x:c>
       <x:c r="K31" s="23">
-        <x:v>46086</x:v>
+        <x:v>46106</x:v>
       </x:c>
       <x:c r="L31" s="25">
-        <x:v>46086</x:v>
+        <x:v>46106</x:v>
       </x:c>
     </x:row>
     <x:row r="32">
-      <x:c r="A32" t="inlineStr" s="3">
-        <x:is>
-          <x:t>HC - Return to Repair</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B32" t="n" s="5">
-        <x:v>2125</x:v>
-      </x:c>
-      <x:c r="C32" t="inlineStr" s="7">
-        <x:is>
-          <x:t>Carrier enterprise, Parts Received , Potential Member</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D32" t="inlineStr" s="9">
-        <x:is>
-          <x:t>587416074</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="E32" t="inlineStr" s="11">
-        <x:is>
-          <x:t>587416074</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="F32" s="13">
-        <x:v>46108</x:v>
-      </x:c>
-      <x:c r="G32" t="inlineStr" s="15">
-        <x:is>
-          <x:t>PP Michael Chenoy</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="H32" t="inlineStr" s="17">
-        <x:is>
-          <x:t>Hold</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="I32" t="inlineStr" s="19">
-        <x:is>
-          <x:t>PLM - HVAC - Service - 12</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="J32" t="inlineStr" s="21">
-        <x:is>
-          <x:t>Jian Jia </x:t>
-        </x:is>
-      </x:c>
-      <x:c r="K32" s="23">
-        <x:v>46106</x:v>
-      </x:c>
-      <x:c r="L32" s="25">
-        <x:v>46106</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="33">
-      <x:c r="A33" t="n" s="4">
-        <x:v>31</x:v>
-      </x:c>
-      <x:c r="B33" t="n" s="6">
-        <x:v>692.08419354838709677419354839</x:v>
-      </x:c>
-      <x:c r="C33" t="inlineStr" s="8">
+      <x:c r="A32" t="n" s="4">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="B32" t="n" s="6">
+        <x:v>687.866</x:v>
+      </x:c>
+      <x:c r="C32" t="inlineStr" s="8">
         <x:is>
           <x:t/>
         </x:is>
       </x:c>
-      <x:c r="D33" t="n" s="10">
-        <x:v>31</x:v>
-      </x:c>
-      <x:c r="E33" t="inlineStr" s="12">
+      <x:c r="D32" t="n" s="10">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="E32" t="inlineStr" s="12">
         <x:is>
           <x:t/>
         </x:is>
       </x:c>
-      <x:c r="F33" s="14">
+      <x:c r="F32" s="14">
         <x:v/>
       </x:c>
-      <x:c r="G33" t="inlineStr" s="16">
+      <x:c r="G32" t="inlineStr" s="16">
         <x:is>
           <x:t/>
         </x:is>
       </x:c>
-      <x:c r="H33" t="inlineStr" s="18">
+      <x:c r="H32" t="inlineStr" s="18">
         <x:is>
           <x:t/>
         </x:is>
       </x:c>
-      <x:c r="I33" t="inlineStr" s="20">
+      <x:c r="I32" t="inlineStr" s="20">
         <x:is>
           <x:t/>
         </x:is>
       </x:c>
-      <x:c r="J33" t="inlineStr" s="22">
+      <x:c r="J32" t="inlineStr" s="22">
         <x:is>
           <x:t/>
         </x:is>
       </x:c>
-      <x:c r="K33" s="24">
+      <x:c r="K32" s="24">
         <x:v/>
       </x:c>
-      <x:c r="L33" s="26">
+      <x:c r="L32" s="26">
         <x:v/>
       </x:c>
     </x:row>

--- a/data/parts_report_past.xlsx
+++ b/data/parts_report_past.xlsx
@@ -5,8 +5,8 @@
     <x:workbookView/>
   </x:bookViews>
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rca6e9244e0be4e06"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Filters" sheetId="2" r:id="R31f840ab955e4ea8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R5d3c5b9ee3bb4cb0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Filters" sheetId="2" r:id="Re04a7bc8b8684abd"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -930,21 +930,21 @@
         </x:is>
       </x:c>
       <x:c r="B16" t="n" s="5">
-        <x:v>225</x:v>
+        <x:v>1615.83</x:v>
       </x:c>
       <x:c r="C16" t="inlineStr" s="7">
         <x:is>
-          <x:t>12-Year Labor, 12-Year Labor, 12-Year Labor, 12-Year Labor, 12-Year Labor, Carrier enterprise, Club Member 2 sys , MULTI- 2, Parts Received , PLM</x:t>
+          <x:t>Club Member, Parts Received </x:t>
         </x:is>
       </x:c>
       <x:c r="D16" t="inlineStr" s="9">
         <x:is>
-          <x:t>586903562</x:t>
+          <x:t>587337488</x:t>
         </x:is>
       </x:c>
       <x:c r="E16" t="inlineStr" s="11">
         <x:is>
-          <x:t>586903562</x:t>
+          <x:t>587337488</x:t>
         </x:is>
       </x:c>
       <x:c r="F16" s="13">
@@ -952,7 +952,7 @@
       </x:c>
       <x:c r="G16" t="inlineStr" s="15">
         <x:is>
-          <x:t>PP Braxton Patterson </x:t>
+          <x:t>PP Demitri Semexant</x:t>
         </x:is>
       </x:c>
       <x:c r="H16" t="inlineStr" s="17">
@@ -967,14 +967,14 @@
       </x:c>
       <x:c r="J16" t="inlineStr" s="21">
         <x:is>
-          <x:t>Ruth  Hochberg</x:t>
+          <x:t>Sabrina Rodriguez</x:t>
         </x:is>
       </x:c>
       <x:c r="K16" s="23">
-        <x:v>46100</x:v>
+        <x:v>46105</x:v>
       </x:c>
       <x:c r="L16" s="25">
-        <x:v>46100</x:v>
+        <x:v>46105</x:v>
       </x:c>
     </x:row>
     <x:row r="17">
@@ -984,21 +984,21 @@
         </x:is>
       </x:c>
       <x:c r="B17" t="n" s="5">
-        <x:v>0</x:v>
+        <x:v>225</x:v>
       </x:c>
       <x:c r="C17" t="inlineStr" s="7">
         <x:is>
-          <x:t>10-10-10, 10-10-10, Carrier enterprise, Club Member, Parts Received , PLM</x:t>
+          <x:t>12-Year Labor, 12-Year Labor, 12-Year Labor, 12-Year Labor, 12-Year Labor, Carrier enterprise, Club Member 2 sys , MULTI- 2, Parts Received , PLM</x:t>
         </x:is>
       </x:c>
       <x:c r="D17" t="inlineStr" s="9">
         <x:is>
-          <x:t>586982846</x:t>
+          <x:t>586903562</x:t>
         </x:is>
       </x:c>
       <x:c r="E17" t="inlineStr" s="11">
         <x:is>
-          <x:t>586982846</x:t>
+          <x:t>586903562</x:t>
         </x:is>
       </x:c>
       <x:c r="F17" s="13">
@@ -1006,7 +1006,7 @@
       </x:c>
       <x:c r="G17" t="inlineStr" s="15">
         <x:is>
-          <x:t>Rickey McClam </x:t>
+          <x:t>PP Braxton Patterson </x:t>
         </x:is>
       </x:c>
       <x:c r="H17" t="inlineStr" s="17">
@@ -1016,19 +1016,19 @@
       </x:c>
       <x:c r="I17" t="inlineStr" s="19">
         <x:is>
-          <x:t>PLM - HVAC - Service - 12</x:t>
+          <x:t>CS - HVAC - Service - 12</x:t>
         </x:is>
       </x:c>
       <x:c r="J17" t="inlineStr" s="21">
         <x:is>
-          <x:t>Gwyn Bonasoro</x:t>
+          <x:t>Ruth  Hochberg</x:t>
         </x:is>
       </x:c>
       <x:c r="K17" s="23">
-        <x:v>46101</x:v>
+        <x:v>46100</x:v>
       </x:c>
       <x:c r="L17" s="25">
-        <x:v>46101</x:v>
+        <x:v>46100</x:v>
       </x:c>
     </x:row>
     <x:row r="18">
@@ -1038,29 +1038,29 @@
         </x:is>
       </x:c>
       <x:c r="B18" t="n" s="5">
-        <x:v>689.97</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="C18" t="inlineStr" s="7">
         <x:is>
-          <x:t>2-YR Labor Warranty, 2-YR Labor Warranty, 2-YR Labor Warranty, Club Member, Gemaire, Parts Received </x:t>
+          <x:t>10-10-10, 10-10-10, Carrier enterprise, Club Member, Parts Received , PLM</x:t>
         </x:is>
       </x:c>
       <x:c r="D18" t="inlineStr" s="9">
         <x:is>
-          <x:t>587253199</x:t>
+          <x:t>586982846</x:t>
         </x:is>
       </x:c>
       <x:c r="E18" t="inlineStr" s="11">
         <x:is>
-          <x:t>587253199</x:t>
+          <x:t>586982846</x:t>
         </x:is>
       </x:c>
       <x:c r="F18" s="13">
-        <x:v>46106</x:v>
+        <x:v>46105</x:v>
       </x:c>
       <x:c r="G18" t="inlineStr" s="15">
         <x:is>
-          <x:t>PP Barrington Wilson</x:t>
+          <x:t>Rickey McClam </x:t>
         </x:is>
       </x:c>
       <x:c r="H18" t="inlineStr" s="17">
@@ -1070,19 +1070,19 @@
       </x:c>
       <x:c r="I18" t="inlineStr" s="19">
         <x:is>
-          <x:t>CS - HVAC - Service - 12</x:t>
+          <x:t>PLM - HVAC - Service - 12</x:t>
         </x:is>
       </x:c>
       <x:c r="J18" t="inlineStr" s="21">
         <x:is>
-          <x:t>Dane Lyons</x:t>
+          <x:t>Gwyn Bonasoro</x:t>
         </x:is>
       </x:c>
       <x:c r="K18" s="23">
-        <x:v>46105</x:v>
+        <x:v>46101</x:v>
       </x:c>
       <x:c r="L18" s="25">
-        <x:v>46105</x:v>
+        <x:v>46101</x:v>
       </x:c>
     </x:row>
     <x:row r="19">
@@ -1092,21 +1092,21 @@
         </x:is>
       </x:c>
       <x:c r="B19" t="n" s="5">
-        <x:v>722.79</x:v>
+        <x:v>689.97</x:v>
       </x:c>
       <x:c r="C19" t="inlineStr" s="7">
         <x:is>
-          <x:t>Baker Supply, Parts Ordered, PLM, Potential Member</x:t>
+          <x:t>2-YR Labor Warranty, 2-YR Labor Warranty, 2-YR Labor Warranty, Club Member, Gemaire, Parts Received </x:t>
         </x:is>
       </x:c>
       <x:c r="D19" t="inlineStr" s="9">
         <x:is>
-          <x:t>459781920</x:t>
+          <x:t>587253199</x:t>
         </x:is>
       </x:c>
       <x:c r="E19" t="inlineStr" s="11">
         <x:is>
-          <x:t>459781920</x:t>
+          <x:t>587253199</x:t>
         </x:is>
       </x:c>
       <x:c r="F19" s="13">
@@ -1114,7 +1114,7 @@
       </x:c>
       <x:c r="G19" t="inlineStr" s="15">
         <x:is>
-          <x:t>PLM-Quentin Stewart</x:t>
+          <x:t>PP Barrington Wilson</x:t>
         </x:is>
       </x:c>
       <x:c r="H19" t="inlineStr" s="17">
@@ -1124,19 +1124,19 @@
       </x:c>
       <x:c r="I19" t="inlineStr" s="19">
         <x:is>
-          <x:t>PLM - HVAC - Service - 12</x:t>
+          <x:t>CS - HVAC - Service - 12</x:t>
         </x:is>
       </x:c>
       <x:c r="J19" t="inlineStr" s="21">
         <x:is>
-          <x:t>Gluck Carolyn</x:t>
+          <x:t>Dane Lyons</x:t>
         </x:is>
       </x:c>
       <x:c r="K19" s="23">
-        <x:v>45726</x:v>
+        <x:v>46105</x:v>
       </x:c>
       <x:c r="L19" s="25">
-        <x:v>45726</x:v>
+        <x:v>46105</x:v>
       </x:c>
     </x:row>
     <x:row r="20">
@@ -1146,29 +1146,29 @@
         </x:is>
       </x:c>
       <x:c r="B20" t="n" s="5">
-        <x:v>294.96</x:v>
+        <x:v>722.79</x:v>
       </x:c>
       <x:c r="C20" t="inlineStr" s="7">
         <x:is>
-          <x:t>10-10-10, 10-10-10, Club Member, Club Member (Additional System), MULTI- 2, Parts Ordered, Trane Supply</x:t>
+          <x:t>Baker Supply, Parts Ordered, PLM, Potential Member</x:t>
         </x:is>
       </x:c>
       <x:c r="D20" t="inlineStr" s="9">
         <x:is>
-          <x:t>554624809</x:t>
+          <x:t>459781920</x:t>
         </x:is>
       </x:c>
       <x:c r="E20" t="inlineStr" s="11">
         <x:is>
-          <x:t>554624809</x:t>
+          <x:t>459781920</x:t>
         </x:is>
       </x:c>
       <x:c r="F20" s="13">
-        <x:v>46107</x:v>
+        <x:v>46106</x:v>
       </x:c>
       <x:c r="G20" t="inlineStr" s="15">
         <x:is>
-          <x:t>PP Carlos Machado</x:t>
+          <x:t>PLM-Quentin Stewart</x:t>
         </x:is>
       </x:c>
       <x:c r="H20" t="inlineStr" s="17">
@@ -1178,19 +1178,19 @@
       </x:c>
       <x:c r="I20" t="inlineStr" s="19">
         <x:is>
-          <x:t>CS - HVAC - Service - 12</x:t>
+          <x:t>PLM - HVAC - Service - 12</x:t>
         </x:is>
       </x:c>
       <x:c r="J20" t="inlineStr" s="21">
         <x:is>
-          <x:t>Michael &amp; Delle Lenzen</x:t>
+          <x:t>Gluck Carolyn</x:t>
         </x:is>
       </x:c>
       <x:c r="K20" s="23">
-        <x:v>45996</x:v>
+        <x:v>45726</x:v>
       </x:c>
       <x:c r="L20" s="25">
-        <x:v>45996</x:v>
+        <x:v>45726</x:v>
       </x:c>
     </x:row>
     <x:row r="21">
@@ -1200,21 +1200,21 @@
         </x:is>
       </x:c>
       <x:c r="B21" t="n" s="5">
-        <x:v>3247.45</x:v>
+        <x:v>294.96</x:v>
       </x:c>
       <x:c r="C21" t="inlineStr" s="7">
         <x:is>
-          <x:t>10-Year Labor, Club Member, Club Member 2 sys , Gemaire, Parts Received , PLM</x:t>
+          <x:t>10-10-10, 10-10-10, Club Member, Club Member (Additional System), MULTI- 2, Parts Ordered, Trane Supply</x:t>
         </x:is>
       </x:c>
       <x:c r="D21" t="inlineStr" s="9">
         <x:is>
-          <x:t>587314216</x:t>
+          <x:t>554624809</x:t>
         </x:is>
       </x:c>
       <x:c r="E21" t="inlineStr" s="11">
         <x:is>
-          <x:t>587314216</x:t>
+          <x:t>554624809</x:t>
         </x:is>
       </x:c>
       <x:c r="F21" s="13">
@@ -1222,7 +1222,7 @@
       </x:c>
       <x:c r="G21" t="inlineStr" s="15">
         <x:is>
-          <x:t>Rolin Moimeme</x:t>
+          <x:t>PP Carlos Machado</x:t>
         </x:is>
       </x:c>
       <x:c r="H21" t="inlineStr" s="17">
@@ -1237,14 +1237,14 @@
       </x:c>
       <x:c r="J21" t="inlineStr" s="21">
         <x:is>
-          <x:t>FRIEDMAN, SAMANTHA</x:t>
+          <x:t>Michael &amp; Delle Lenzen</x:t>
         </x:is>
       </x:c>
       <x:c r="K21" s="23">
-        <x:v>46105</x:v>
+        <x:v>45996</x:v>
       </x:c>
       <x:c r="L21" s="25">
-        <x:v>46105</x:v>
+        <x:v>45996</x:v>
       </x:c>
     </x:row>
     <x:row r="22">
@@ -1254,29 +1254,29 @@
         </x:is>
       </x:c>
       <x:c r="B22" t="n" s="5">
-        <x:v>0</x:v>
+        <x:v>3247.45</x:v>
       </x:c>
       <x:c r="C22" t="inlineStr" s="7">
         <x:is>
-          <x:t>Club Member, Gemaire, Parts Received </x:t>
+          <x:t>10-Year Labor, Club Member, Club Member 2 sys , Gemaire, Parts Received , PLM</x:t>
         </x:is>
       </x:c>
       <x:c r="D22" t="inlineStr" s="9">
         <x:is>
-          <x:t>587448096</x:t>
+          <x:t>587314216</x:t>
         </x:is>
       </x:c>
       <x:c r="E22" t="inlineStr" s="11">
         <x:is>
-          <x:t>587448096</x:t>
+          <x:t>587314216</x:t>
         </x:is>
       </x:c>
       <x:c r="F22" s="13">
-        <x:v>46108</x:v>
+        <x:v>46107</x:v>
       </x:c>
       <x:c r="G22" t="inlineStr" s="15">
         <x:is>
-          <x:t/>
+          <x:t>Rolin Moimeme</x:t>
         </x:is>
       </x:c>
       <x:c r="H22" t="inlineStr" s="17">
@@ -1286,19 +1286,19 @@
       </x:c>
       <x:c r="I22" t="inlineStr" s="19">
         <x:is>
-          <x:t>PLM - HVAC - Service - 12</x:t>
+          <x:t>CS - HVAC - Service - 12</x:t>
         </x:is>
       </x:c>
       <x:c r="J22" t="inlineStr" s="21">
         <x:is>
-          <x:t>Cassandra Sexton</x:t>
+          <x:t>FRIEDMAN, SAMANTHA</x:t>
         </x:is>
       </x:c>
       <x:c r="K22" s="23">
-        <x:v>46106</x:v>
+        <x:v>46105</x:v>
       </x:c>
       <x:c r="L22" s="25">
-        <x:v>46106</x:v>
+        <x:v>46105</x:v>
       </x:c>
     </x:row>
     <x:row r="23">
@@ -1312,17 +1312,17 @@
       </x:c>
       <x:c r="C23" t="inlineStr" s="7">
         <x:is>
-          <x:t>Club Member, LW- 2 YEAR LABOR, Parts Ordered, Trane Supply</x:t>
+          <x:t>Club Member, Gemaire, Parts Ordered</x:t>
         </x:is>
       </x:c>
       <x:c r="D23" t="inlineStr" s="9">
         <x:is>
-          <x:t>587077196</x:t>
+          <x:t>587448096</x:t>
         </x:is>
       </x:c>
       <x:c r="E23" t="inlineStr" s="11">
         <x:is>
-          <x:t>587077196</x:t>
+          <x:t>587448096</x:t>
         </x:is>
       </x:c>
       <x:c r="F23" s="13">
@@ -1330,7 +1330,7 @@
       </x:c>
       <x:c r="G23" t="inlineStr" s="15">
         <x:is>
-          <x:t>Tyler Gallatin</x:t>
+          <x:t/>
         </x:is>
       </x:c>
       <x:c r="H23" t="inlineStr" s="17">
@@ -1340,19 +1340,19 @@
       </x:c>
       <x:c r="I23" t="inlineStr" s="19">
         <x:is>
-          <x:t>CS - HVAC - Service - 12</x:t>
+          <x:t>PLM - HVAC - Service - 12</x:t>
         </x:is>
       </x:c>
       <x:c r="J23" t="inlineStr" s="21">
         <x:is>
-          <x:t>Timberwalk Association Inc</x:t>
+          <x:t>Cassandra Sexton</x:t>
         </x:is>
       </x:c>
       <x:c r="K23" s="23">
-        <x:v>46102</x:v>
+        <x:v>46106</x:v>
       </x:c>
       <x:c r="L23" s="25">
-        <x:v>46102</x:v>
+        <x:v>46106</x:v>
       </x:c>
     </x:row>
     <x:row r="24">
@@ -1362,21 +1362,21 @@
         </x:is>
       </x:c>
       <x:c r="B24" t="n" s="5">
-        <x:v>1248.8</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="C24" t="inlineStr" s="7">
         <x:is>
-          <x:t>Club Member, Lennox Supply, Parts Received </x:t>
+          <x:t>Club Member, LW- 2 YEAR LABOR, Parts Ordered, Trane Supply</x:t>
         </x:is>
       </x:c>
       <x:c r="D24" t="inlineStr" s="9">
         <x:is>
-          <x:t>587303898</x:t>
+          <x:t>587077196</x:t>
         </x:is>
       </x:c>
       <x:c r="E24" t="inlineStr" s="11">
         <x:is>
-          <x:t>587303898</x:t>
+          <x:t>587077196</x:t>
         </x:is>
       </x:c>
       <x:c r="F24" s="13">
@@ -1384,7 +1384,7 @@
       </x:c>
       <x:c r="G24" t="inlineStr" s="15">
         <x:is>
-          <x:t>Xavier Mateo</x:t>
+          <x:t>Tyler Gallatin</x:t>
         </x:is>
       </x:c>
       <x:c r="H24" t="inlineStr" s="17">
@@ -1399,14 +1399,14 @@
       </x:c>
       <x:c r="J24" t="inlineStr" s="21">
         <x:is>
-          <x:t>ROBERT MCCABE</x:t>
+          <x:t>Timberwalk Association Inc</x:t>
         </x:is>
       </x:c>
       <x:c r="K24" s="23">
-        <x:v>46105</x:v>
+        <x:v>46102</x:v>
       </x:c>
       <x:c r="L24" s="25">
-        <x:v>46105</x:v>
+        <x:v>46102</x:v>
       </x:c>
     </x:row>
     <x:row r="25">
@@ -1416,21 +1416,21 @@
         </x:is>
       </x:c>
       <x:c r="B25" t="n" s="5">
-        <x:v>1267.95</x:v>
+        <x:v>1248.8</x:v>
       </x:c>
       <x:c r="C25" t="inlineStr" s="7">
         <x:is>
-          <x:t>Club Member 3 sys, Gemaire, Parts Received </x:t>
+          <x:t>Club Member, Lennox Supply, Parts Ordered</x:t>
         </x:is>
       </x:c>
       <x:c r="D25" t="inlineStr" s="9">
         <x:is>
-          <x:t>578585007</x:t>
+          <x:t>587303898</x:t>
         </x:is>
       </x:c>
       <x:c r="E25" t="inlineStr" s="11">
         <x:is>
-          <x:t>578585007</x:t>
+          <x:t>587303898</x:t>
         </x:is>
       </x:c>
       <x:c r="F25" s="13">
@@ -1438,7 +1438,7 @@
       </x:c>
       <x:c r="G25" t="inlineStr" s="15">
         <x:is>
-          <x:t>PP Cesar Levy</x:t>
+          <x:t>Xavier Mateo</x:t>
         </x:is>
       </x:c>
       <x:c r="H25" t="inlineStr" s="17">
@@ -1453,14 +1453,14 @@
       </x:c>
       <x:c r="J25" t="inlineStr" s="21">
         <x:is>
-          <x:t>Serghei Arsentiev</x:t>
+          <x:t>ROBERT MCCABE</x:t>
         </x:is>
       </x:c>
       <x:c r="K25" s="23">
-        <x:v>46037</x:v>
+        <x:v>46105</x:v>
       </x:c>
       <x:c r="L25" s="25">
-        <x:v>46037</x:v>
+        <x:v>46105</x:v>
       </x:c>
     </x:row>
     <x:row r="26">
@@ -1470,21 +1470,21 @@
         </x:is>
       </x:c>
       <x:c r="B26" t="n" s="5">
-        <x:v>0</x:v>
+        <x:v>1267.95</x:v>
       </x:c>
       <x:c r="C26" t="inlineStr" s="7">
         <x:is>
-          <x:t>Carrier enterprise, Parts Ordered, PLM, Potential Member</x:t>
+          <x:t>Club Member 3 sys, Gemaire, Parts Received </x:t>
         </x:is>
       </x:c>
       <x:c r="D26" t="inlineStr" s="9">
         <x:is>
-          <x:t>583259145</x:t>
+          <x:t>578585007</x:t>
         </x:is>
       </x:c>
       <x:c r="E26" t="inlineStr" s="11">
         <x:is>
-          <x:t>583259145</x:t>
+          <x:t>578585007</x:t>
         </x:is>
       </x:c>
       <x:c r="F26" s="13">
@@ -1492,7 +1492,7 @@
       </x:c>
       <x:c r="G26" t="inlineStr" s="15">
         <x:is>
-          <x:t/>
+          <x:t>PP Cesar Levy</x:t>
         </x:is>
       </x:c>
       <x:c r="H26" t="inlineStr" s="17">
@@ -1507,14 +1507,14 @@
       </x:c>
       <x:c r="J26" t="inlineStr" s="21">
         <x:is>
-          <x:t>John Moore</x:t>
+          <x:t>Serghei Arsentiev</x:t>
         </x:is>
       </x:c>
       <x:c r="K26" s="23">
-        <x:v>46070</x:v>
+        <x:v>46037</x:v>
       </x:c>
       <x:c r="L26" s="25">
-        <x:v>46070</x:v>
+        <x:v>46037</x:v>
       </x:c>
     </x:row>
     <x:row r="27">
@@ -1524,21 +1524,21 @@
         </x:is>
       </x:c>
       <x:c r="B27" t="n" s="5">
-        <x:v>1605.6</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="C27" t="inlineStr" s="7">
         <x:is>
-          <x:t>Club Member, Club Member (Additional System), Parts Ordered, PLM</x:t>
+          <x:t>Carrier enterprise, Parts Ordered, PLM, Potential Member</x:t>
         </x:is>
       </x:c>
       <x:c r="D27" t="inlineStr" s="9">
         <x:is>
-          <x:t>587681974</x:t>
+          <x:t>583259145</x:t>
         </x:is>
       </x:c>
       <x:c r="E27" t="inlineStr" s="11">
         <x:is>
-          <x:t>587681974</x:t>
+          <x:t>583259145</x:t>
         </x:is>
       </x:c>
       <x:c r="F27" s="13">
@@ -1546,7 +1546,7 @@
       </x:c>
       <x:c r="G27" t="inlineStr" s="15">
         <x:is>
-          <x:t>PP Barrington Wilson</x:t>
+          <x:t/>
         </x:is>
       </x:c>
       <x:c r="H27" t="inlineStr" s="17">
@@ -1561,14 +1561,14 @@
       </x:c>
       <x:c r="J27" t="inlineStr" s="21">
         <x:is>
-          <x:t>MACLACHLAN, DAN</x:t>
+          <x:t>John Moore</x:t>
         </x:is>
       </x:c>
       <x:c r="K27" s="23">
-        <x:v>46108</x:v>
+        <x:v>46070</x:v>
       </x:c>
       <x:c r="L27" s="25">
-        <x:v>46108</x:v>
+        <x:v>46070</x:v>
       </x:c>
     </x:row>
     <x:row r="28">
@@ -1578,21 +1578,21 @@
         </x:is>
       </x:c>
       <x:c r="B28" t="n" s="5">
-        <x:v>292.95</x:v>
+        <x:v>808.4</x:v>
       </x:c>
       <x:c r="C28" t="inlineStr" s="7">
         <x:is>
-          <x:t>Baker Supply, Club Member, Parts Received , PLM</x:t>
+          <x:t>Carrier enterprise, Club Member, Parts Ordered, PLM</x:t>
         </x:is>
       </x:c>
       <x:c r="D28" t="inlineStr" s="9">
         <x:is>
-          <x:t>587301961</x:t>
+          <x:t>587598604</x:t>
         </x:is>
       </x:c>
       <x:c r="E28" t="inlineStr" s="11">
         <x:is>
-          <x:t>587301961</x:t>
+          <x:t>587598604</x:t>
         </x:is>
       </x:c>
       <x:c r="F28" s="13">
@@ -1600,7 +1600,7 @@
       </x:c>
       <x:c r="G28" t="inlineStr" s="15">
         <x:is>
-          <x:t>Jesse Dague</x:t>
+          <x:t>PP Barrington Wilson</x:t>
         </x:is>
       </x:c>
       <x:c r="H28" t="inlineStr" s="17">
@@ -1610,19 +1610,19 @@
       </x:c>
       <x:c r="I28" t="inlineStr" s="19">
         <x:is>
-          <x:t>CS - HVAC - Service - 12</x:t>
+          <x:t>PLM - HVAC - Service - 12</x:t>
         </x:is>
       </x:c>
       <x:c r="J28" t="inlineStr" s="21">
         <x:is>
-          <x:t>CHACON, LERA</x:t>
+          <x:t>DIVINCENZO, ANTHONY</x:t>
         </x:is>
       </x:c>
       <x:c r="K28" s="23">
-        <x:v>46105</x:v>
+        <x:v>46107</x:v>
       </x:c>
       <x:c r="L28" s="25">
-        <x:v>46105</x:v>
+        <x:v>46107</x:v>
       </x:c>
     </x:row>
     <x:row r="29">
@@ -1632,21 +1632,21 @@
         </x:is>
       </x:c>
       <x:c r="B29" t="n" s="5">
-        <x:v>2405.92</x:v>
+        <x:v>292.95</x:v>
       </x:c>
       <x:c r="C29" t="inlineStr" s="7">
         <x:is>
-          <x:t>Baker Supply, Parts Ordered, Potential Member</x:t>
+          <x:t>Baker Supply, Club Member, Parts Received , PLM</x:t>
         </x:is>
       </x:c>
       <x:c r="D29" t="inlineStr" s="9">
         <x:is>
-          <x:t>578394047</x:t>
+          <x:t>587301961</x:t>
         </x:is>
       </x:c>
       <x:c r="E29" t="inlineStr" s="11">
         <x:is>
-          <x:t>578394047</x:t>
+          <x:t>587301961</x:t>
         </x:is>
       </x:c>
       <x:c r="F29" s="13">
@@ -1654,7 +1654,7 @@
       </x:c>
       <x:c r="G29" t="inlineStr" s="15">
         <x:is>
-          <x:t>PP Gurpreet Parihar</x:t>
+          <x:t>Jesse Dague</x:t>
         </x:is>
       </x:c>
       <x:c r="H29" t="inlineStr" s="17">
@@ -1664,19 +1664,19 @@
       </x:c>
       <x:c r="I29" t="inlineStr" s="19">
         <x:is>
-          <x:t>PLM - HVAC - Service - 12</x:t>
+          <x:t>CS - HVAC - Service - 12</x:t>
         </x:is>
       </x:c>
       <x:c r="J29" t="inlineStr" s="21">
         <x:is>
-          <x:t>Edgar Irving</x:t>
+          <x:t>CHACON, LERA</x:t>
         </x:is>
       </x:c>
       <x:c r="K29" s="23">
-        <x:v>46036</x:v>
+        <x:v>46105</x:v>
       </x:c>
       <x:c r="L29" s="25">
-        <x:v>46036</x:v>
+        <x:v>46105</x:v>
       </x:c>
     </x:row>
     <x:row r="30">
@@ -1686,21 +1686,21 @@
         </x:is>
       </x:c>
       <x:c r="B30" t="n" s="5">
-        <x:v>0</x:v>
+        <x:v>2405.92</x:v>
       </x:c>
       <x:c r="C30" t="inlineStr" s="7">
         <x:is>
-          <x:t>10-Year Labor, 10-Year Labor, 10-Year Labor, 10-Year Labor, 10-Year Labor, Club Member, Goodman distribution , Parts Ordered</x:t>
+          <x:t>Baker Supply, Parts Ordered, Potential Member</x:t>
         </x:is>
       </x:c>
       <x:c r="D30" t="inlineStr" s="9">
         <x:is>
-          <x:t>585388429</x:t>
+          <x:t>578394047</x:t>
         </x:is>
       </x:c>
       <x:c r="E30" t="inlineStr" s="11">
         <x:is>
-          <x:t>585388429</x:t>
+          <x:t>578394047</x:t>
         </x:is>
       </x:c>
       <x:c r="F30" s="13">
@@ -1708,7 +1708,7 @@
       </x:c>
       <x:c r="G30" t="inlineStr" s="15">
         <x:is>
-          <x:t>Rickey McClam </x:t>
+          <x:t>PP Gurpreet Parihar</x:t>
         </x:is>
       </x:c>
       <x:c r="H30" t="inlineStr" s="17">
@@ -1718,19 +1718,19 @@
       </x:c>
       <x:c r="I30" t="inlineStr" s="19">
         <x:is>
-          <x:t>CS - HVAC - Service - 12</x:t>
+          <x:t>PLM - HVAC - Service - 12</x:t>
         </x:is>
       </x:c>
       <x:c r="J30" t="inlineStr" s="21">
         <x:is>
-          <x:t>Charles Funkey</x:t>
+          <x:t>Edgar Irving</x:t>
         </x:is>
       </x:c>
       <x:c r="K30" s="23">
-        <x:v>46086</x:v>
+        <x:v>46036</x:v>
       </x:c>
       <x:c r="L30" s="25">
-        <x:v>46086</x:v>
+        <x:v>46036</x:v>
       </x:c>
     </x:row>
     <x:row r="31">
@@ -1740,21 +1740,21 @@
         </x:is>
       </x:c>
       <x:c r="B31" t="n" s="5">
-        <x:v>2125</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="C31" t="inlineStr" s="7">
         <x:is>
-          <x:t>Carrier enterprise, Parts Received , Potential Member</x:t>
+          <x:t>10-Year Labor, 10-Year Labor, 10-Year Labor, 10-Year Labor, 10-Year Labor, Club Member, Goodman distribution , Parts Ordered</x:t>
         </x:is>
       </x:c>
       <x:c r="D31" t="inlineStr" s="9">
         <x:is>
-          <x:t>587416074</x:t>
+          <x:t>585388429</x:t>
         </x:is>
       </x:c>
       <x:c r="E31" t="inlineStr" s="11">
         <x:is>
-          <x:t>587416074</x:t>
+          <x:t>585388429</x:t>
         </x:is>
       </x:c>
       <x:c r="F31" s="13">
@@ -1762,78 +1762,132 @@
       </x:c>
       <x:c r="G31" t="inlineStr" s="15">
         <x:is>
+          <x:t>Rickey McClam </x:t>
+        </x:is>
+      </x:c>
+      <x:c r="H31" t="inlineStr" s="17">
+        <x:is>
+          <x:t>Hold</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="I31" t="inlineStr" s="19">
+        <x:is>
+          <x:t>CS - HVAC - Service - 12</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="J31" t="inlineStr" s="21">
+        <x:is>
+          <x:t>Charles Funkey</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="K31" s="23">
+        <x:v>46086</x:v>
+      </x:c>
+      <x:c r="L31" s="25">
+        <x:v>46086</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="32">
+      <x:c r="A32" t="inlineStr" s="3">
+        <x:is>
+          <x:t>HC - Return to Repair</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B32" t="n" s="5">
+        <x:v>2125</x:v>
+      </x:c>
+      <x:c r="C32" t="inlineStr" s="7">
+        <x:is>
+          <x:t>Carrier enterprise, Parts Received , Potential Member</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D32" t="inlineStr" s="9">
+        <x:is>
+          <x:t>587416074</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E32" t="inlineStr" s="11">
+        <x:is>
+          <x:t>587416074</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F32" s="13">
+        <x:v>46108</x:v>
+      </x:c>
+      <x:c r="G32" t="inlineStr" s="15">
+        <x:is>
           <x:t>PP Michael Chenoy</x:t>
         </x:is>
       </x:c>
-      <x:c r="H31" t="inlineStr" s="17">
-        <x:is>
-          <x:t>Hold</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="I31" t="inlineStr" s="19">
+      <x:c r="H32" t="inlineStr" s="17">
+        <x:is>
+          <x:t>Hold</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="I32" t="inlineStr" s="19">
         <x:is>
           <x:t>PLM - HVAC - Service - 12</x:t>
         </x:is>
       </x:c>
-      <x:c r="J31" t="inlineStr" s="21">
+      <x:c r="J32" t="inlineStr" s="21">
         <x:is>
           <x:t>Jian Jia </x:t>
         </x:is>
       </x:c>
-      <x:c r="K31" s="23">
+      <x:c r="K32" s="23">
         <x:v>46106</x:v>
       </x:c>
-      <x:c r="L31" s="25">
+      <x:c r="L32" s="25">
         <x:v>46106</x:v>
       </x:c>
     </x:row>
-    <x:row r="32">
-      <x:c r="A32" t="n" s="4">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="B32" t="n" s="6">
-        <x:v>687.866</x:v>
-      </x:c>
-      <x:c r="C32" t="inlineStr" s="8">
+    <x:row r="33">
+      <x:c r="A33" t="n" s="4">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="B33" t="n" s="6">
+        <x:v>692.08419354838709677419354839</x:v>
+      </x:c>
+      <x:c r="C33" t="inlineStr" s="8">
         <x:is>
           <x:t/>
         </x:is>
       </x:c>
-      <x:c r="D32" t="n" s="10">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="E32" t="inlineStr" s="12">
+      <x:c r="D33" t="n" s="10">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="E33" t="inlineStr" s="12">
         <x:is>
           <x:t/>
         </x:is>
       </x:c>
-      <x:c r="F32" s="14">
+      <x:c r="F33" s="14">
         <x:v/>
       </x:c>
-      <x:c r="G32" t="inlineStr" s="16">
+      <x:c r="G33" t="inlineStr" s="16">
         <x:is>
           <x:t/>
         </x:is>
       </x:c>
-      <x:c r="H32" t="inlineStr" s="18">
+      <x:c r="H33" t="inlineStr" s="18">
         <x:is>
           <x:t/>
         </x:is>
       </x:c>
-      <x:c r="I32" t="inlineStr" s="20">
+      <x:c r="I33" t="inlineStr" s="20">
         <x:is>
           <x:t/>
         </x:is>
       </x:c>
-      <x:c r="J32" t="inlineStr" s="22">
+      <x:c r="J33" t="inlineStr" s="22">
         <x:is>
           <x:t/>
         </x:is>
       </x:c>
-      <x:c r="K32" s="24">
+      <x:c r="K33" s="24">
         <x:v/>
       </x:c>
-      <x:c r="L32" s="26">
+      <x:c r="L33" s="26">
         <x:v/>
       </x:c>
     </x:row>

--- a/data/parts_report_past.xlsx
+++ b/data/parts_report_past.xlsx
@@ -5,8 +5,8 @@
     <x:workbookView/>
   </x:bookViews>
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rca6e9244e0be4e06"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Filters" sheetId="2" r:id="R31f840ab955e4ea8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rb5ddda3f96104405"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Filters" sheetId="2" r:id="R3b0338e1df724b66"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -876,21 +876,21 @@
         </x:is>
       </x:c>
       <x:c r="B15" t="n" s="5">
-        <x:v>1662.36</x:v>
+        <x:v>225</x:v>
       </x:c>
       <x:c r="C15" t="inlineStr" s="7">
         <x:is>
-          <x:t>Club Member, Club Member (Additional System), MULTI- 2, Parts Received </x:t>
+          <x:t>12-Year Labor, 12-Year Labor, 12-Year Labor, 12-Year Labor, 12-Year Labor, Carrier enterprise, Club Member 2 sys , MULTI- 2, Parts Received , PLM</x:t>
         </x:is>
       </x:c>
       <x:c r="D15" t="inlineStr" s="9">
         <x:is>
-          <x:t>587268927</x:t>
+          <x:t>586903562</x:t>
         </x:is>
       </x:c>
       <x:c r="E15" t="inlineStr" s="11">
         <x:is>
-          <x:t>587268927</x:t>
+          <x:t>586903562</x:t>
         </x:is>
       </x:c>
       <x:c r="F15" s="13">
@@ -898,7 +898,7 @@
       </x:c>
       <x:c r="G15" t="inlineStr" s="15">
         <x:is>
-          <x:t>PP Demitri Semexant</x:t>
+          <x:t>PP Braxton Patterson </x:t>
         </x:is>
       </x:c>
       <x:c r="H15" t="inlineStr" s="17">
@@ -913,14 +913,14 @@
       </x:c>
       <x:c r="J15" t="inlineStr" s="21">
         <x:is>
-          <x:t>Susan  Paley</x:t>
+          <x:t>Ruth  Hochberg</x:t>
         </x:is>
       </x:c>
       <x:c r="K15" s="23">
-        <x:v>46105</x:v>
+        <x:v>46100</x:v>
       </x:c>
       <x:c r="L15" s="25">
-        <x:v>46105</x:v>
+        <x:v>46100</x:v>
       </x:c>
     </x:row>
     <x:row r="16">
@@ -930,21 +930,21 @@
         </x:is>
       </x:c>
       <x:c r="B16" t="n" s="5">
-        <x:v>225</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="C16" t="inlineStr" s="7">
         <x:is>
-          <x:t>12-Year Labor, 12-Year Labor, 12-Year Labor, 12-Year Labor, 12-Year Labor, Carrier enterprise, Club Member 2 sys , MULTI- 2, Parts Received , PLM</x:t>
+          <x:t>10-10-10, 10-10-10, Carrier enterprise, Club Member, Parts Received , PLM</x:t>
         </x:is>
       </x:c>
       <x:c r="D16" t="inlineStr" s="9">
         <x:is>
-          <x:t>586903562</x:t>
+          <x:t>586982846</x:t>
         </x:is>
       </x:c>
       <x:c r="E16" t="inlineStr" s="11">
         <x:is>
-          <x:t>586903562</x:t>
+          <x:t>586982846</x:t>
         </x:is>
       </x:c>
       <x:c r="F16" s="13">
@@ -952,7 +952,7 @@
       </x:c>
       <x:c r="G16" t="inlineStr" s="15">
         <x:is>
-          <x:t>PP Braxton Patterson </x:t>
+          <x:t>Rickey McClam </x:t>
         </x:is>
       </x:c>
       <x:c r="H16" t="inlineStr" s="17">
@@ -962,19 +962,19 @@
       </x:c>
       <x:c r="I16" t="inlineStr" s="19">
         <x:is>
-          <x:t>CS - HVAC - Service - 12</x:t>
+          <x:t>PLM - HVAC - Service - 12</x:t>
         </x:is>
       </x:c>
       <x:c r="J16" t="inlineStr" s="21">
         <x:is>
-          <x:t>Ruth  Hochberg</x:t>
+          <x:t>Gwyn Bonasoro</x:t>
         </x:is>
       </x:c>
       <x:c r="K16" s="23">
-        <x:v>46100</x:v>
+        <x:v>46101</x:v>
       </x:c>
       <x:c r="L16" s="25">
-        <x:v>46100</x:v>
+        <x:v>46101</x:v>
       </x:c>
     </x:row>
     <x:row r="17">
@@ -984,51 +984,51 @@
         </x:is>
       </x:c>
       <x:c r="B17" t="n" s="5">
-        <x:v>0</x:v>
+        <x:v>689.97</x:v>
       </x:c>
       <x:c r="C17" t="inlineStr" s="7">
         <x:is>
-          <x:t>10-10-10, 10-10-10, Carrier enterprise, Club Member, Parts Received , PLM</x:t>
+          <x:t>2-YR Labor Warranty, 2-YR Labor Warranty, 2-YR Labor Warranty, Club Member, Gemaire, Parts Received </x:t>
         </x:is>
       </x:c>
       <x:c r="D17" t="inlineStr" s="9">
         <x:is>
-          <x:t>586982846</x:t>
+          <x:t>587253199</x:t>
         </x:is>
       </x:c>
       <x:c r="E17" t="inlineStr" s="11">
         <x:is>
-          <x:t>586982846</x:t>
+          <x:t>587253199</x:t>
         </x:is>
       </x:c>
       <x:c r="F17" s="13">
+        <x:v>46106</x:v>
+      </x:c>
+      <x:c r="G17" t="inlineStr" s="15">
+        <x:is>
+          <x:t>PP Barrington Wilson</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="H17" t="inlineStr" s="17">
+        <x:is>
+          <x:t>Hold</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="I17" t="inlineStr" s="19">
+        <x:is>
+          <x:t>CS - HVAC - Service - 12</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="J17" t="inlineStr" s="21">
+        <x:is>
+          <x:t>Dane Lyons</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="K17" s="23">
         <x:v>46105</x:v>
       </x:c>
-      <x:c r="G17" t="inlineStr" s="15">
-        <x:is>
-          <x:t>Rickey McClam </x:t>
-        </x:is>
-      </x:c>
-      <x:c r="H17" t="inlineStr" s="17">
-        <x:is>
-          <x:t>Hold</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="I17" t="inlineStr" s="19">
-        <x:is>
-          <x:t>PLM - HVAC - Service - 12</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="J17" t="inlineStr" s="21">
-        <x:is>
-          <x:t>Gwyn Bonasoro</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="K17" s="23">
-        <x:v>46101</x:v>
-      </x:c>
       <x:c r="L17" s="25">
-        <x:v>46101</x:v>
+        <x:v>46105</x:v>
       </x:c>
     </x:row>
     <x:row r="18">
@@ -1038,21 +1038,21 @@
         </x:is>
       </x:c>
       <x:c r="B18" t="n" s="5">
-        <x:v>689.97</x:v>
+        <x:v>722.79</x:v>
       </x:c>
       <x:c r="C18" t="inlineStr" s="7">
         <x:is>
-          <x:t>2-YR Labor Warranty, 2-YR Labor Warranty, 2-YR Labor Warranty, Club Member, Gemaire, Parts Received </x:t>
+          <x:t>Baker Supply, Parts Ordered, PLM, Potential Member</x:t>
         </x:is>
       </x:c>
       <x:c r="D18" t="inlineStr" s="9">
         <x:is>
-          <x:t>587253199</x:t>
+          <x:t>459781920</x:t>
         </x:is>
       </x:c>
       <x:c r="E18" t="inlineStr" s="11">
         <x:is>
-          <x:t>587253199</x:t>
+          <x:t>459781920</x:t>
         </x:is>
       </x:c>
       <x:c r="F18" s="13">
@@ -1060,7 +1060,7 @@
       </x:c>
       <x:c r="G18" t="inlineStr" s="15">
         <x:is>
-          <x:t>PP Barrington Wilson</x:t>
+          <x:t>PLM-Quentin Stewart</x:t>
         </x:is>
       </x:c>
       <x:c r="H18" t="inlineStr" s="17">
@@ -1070,19 +1070,19 @@
       </x:c>
       <x:c r="I18" t="inlineStr" s="19">
         <x:is>
-          <x:t>CS - HVAC - Service - 12</x:t>
+          <x:t>PLM - HVAC - Service - 12</x:t>
         </x:is>
       </x:c>
       <x:c r="J18" t="inlineStr" s="21">
         <x:is>
-          <x:t>Dane Lyons</x:t>
+          <x:t>Gluck Carolyn</x:t>
         </x:is>
       </x:c>
       <x:c r="K18" s="23">
-        <x:v>46105</x:v>
+        <x:v>45726</x:v>
       </x:c>
       <x:c r="L18" s="25">
-        <x:v>46105</x:v>
+        <x:v>45726</x:v>
       </x:c>
     </x:row>
     <x:row r="19">
@@ -1092,29 +1092,29 @@
         </x:is>
       </x:c>
       <x:c r="B19" t="n" s="5">
-        <x:v>722.79</x:v>
+        <x:v>294.96</x:v>
       </x:c>
       <x:c r="C19" t="inlineStr" s="7">
         <x:is>
-          <x:t>Baker Supply, Parts Ordered, PLM, Potential Member</x:t>
+          <x:t>10-10-10, 10-10-10, Club Member, Club Member (Additional System), MULTI- 2, Parts Ordered, Trane Supply</x:t>
         </x:is>
       </x:c>
       <x:c r="D19" t="inlineStr" s="9">
         <x:is>
-          <x:t>459781920</x:t>
+          <x:t>554624809</x:t>
         </x:is>
       </x:c>
       <x:c r="E19" t="inlineStr" s="11">
         <x:is>
-          <x:t>459781920</x:t>
+          <x:t>554624809</x:t>
         </x:is>
       </x:c>
       <x:c r="F19" s="13">
-        <x:v>46106</x:v>
+        <x:v>46107</x:v>
       </x:c>
       <x:c r="G19" t="inlineStr" s="15">
         <x:is>
-          <x:t>PLM-Quentin Stewart</x:t>
+          <x:t>PP Carlos Machado</x:t>
         </x:is>
       </x:c>
       <x:c r="H19" t="inlineStr" s="17">
@@ -1124,19 +1124,19 @@
       </x:c>
       <x:c r="I19" t="inlineStr" s="19">
         <x:is>
-          <x:t>PLM - HVAC - Service - 12</x:t>
+          <x:t>CS - HVAC - Service - 12</x:t>
         </x:is>
       </x:c>
       <x:c r="J19" t="inlineStr" s="21">
         <x:is>
-          <x:t>Gluck Carolyn</x:t>
+          <x:t>Michael &amp; Delle Lenzen</x:t>
         </x:is>
       </x:c>
       <x:c r="K19" s="23">
-        <x:v>45726</x:v>
+        <x:v>45996</x:v>
       </x:c>
       <x:c r="L19" s="25">
-        <x:v>45726</x:v>
+        <x:v>45996</x:v>
       </x:c>
     </x:row>
     <x:row r="20">
@@ -1146,21 +1146,21 @@
         </x:is>
       </x:c>
       <x:c r="B20" t="n" s="5">
-        <x:v>294.96</x:v>
+        <x:v>3247.45</x:v>
       </x:c>
       <x:c r="C20" t="inlineStr" s="7">
         <x:is>
-          <x:t>10-10-10, 10-10-10, Club Member, Club Member (Additional System), MULTI- 2, Parts Ordered, Trane Supply</x:t>
+          <x:t>10-Year Labor, Club Member, Club Member 2 sys , Gemaire, Parts Received , PLM</x:t>
         </x:is>
       </x:c>
       <x:c r="D20" t="inlineStr" s="9">
         <x:is>
-          <x:t>554624809</x:t>
+          <x:t>587314216</x:t>
         </x:is>
       </x:c>
       <x:c r="E20" t="inlineStr" s="11">
         <x:is>
-          <x:t>554624809</x:t>
+          <x:t>587314216</x:t>
         </x:is>
       </x:c>
       <x:c r="F20" s="13">
@@ -1168,7 +1168,7 @@
       </x:c>
       <x:c r="G20" t="inlineStr" s="15">
         <x:is>
-          <x:t>PP Carlos Machado</x:t>
+          <x:t>Rolin Moimeme</x:t>
         </x:is>
       </x:c>
       <x:c r="H20" t="inlineStr" s="17">
@@ -1183,14 +1183,14 @@
       </x:c>
       <x:c r="J20" t="inlineStr" s="21">
         <x:is>
-          <x:t>Michael &amp; Delle Lenzen</x:t>
+          <x:t>FRIEDMAN, SAMANTHA</x:t>
         </x:is>
       </x:c>
       <x:c r="K20" s="23">
-        <x:v>45996</x:v>
+        <x:v>46105</x:v>
       </x:c>
       <x:c r="L20" s="25">
-        <x:v>45996</x:v>
+        <x:v>46105</x:v>
       </x:c>
     </x:row>
     <x:row r="21">
@@ -1200,29 +1200,29 @@
         </x:is>
       </x:c>
       <x:c r="B21" t="n" s="5">
-        <x:v>3247.45</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="C21" t="inlineStr" s="7">
         <x:is>
-          <x:t>10-Year Labor, Club Member, Club Member 2 sys , Gemaire, Parts Received , PLM</x:t>
+          <x:t>Club Member, Gemaire, Parts Received </x:t>
         </x:is>
       </x:c>
       <x:c r="D21" t="inlineStr" s="9">
         <x:is>
-          <x:t>587314216</x:t>
+          <x:t>587448096</x:t>
         </x:is>
       </x:c>
       <x:c r="E21" t="inlineStr" s="11">
         <x:is>
-          <x:t>587314216</x:t>
+          <x:t>587448096</x:t>
         </x:is>
       </x:c>
       <x:c r="F21" s="13">
-        <x:v>46107</x:v>
+        <x:v>46108</x:v>
       </x:c>
       <x:c r="G21" t="inlineStr" s="15">
         <x:is>
-          <x:t>Rolin Moimeme</x:t>
+          <x:t/>
         </x:is>
       </x:c>
       <x:c r="H21" t="inlineStr" s="17">
@@ -1232,19 +1232,19 @@
       </x:c>
       <x:c r="I21" t="inlineStr" s="19">
         <x:is>
-          <x:t>CS - HVAC - Service - 12</x:t>
+          <x:t>PLM - HVAC - Service - 12</x:t>
         </x:is>
       </x:c>
       <x:c r="J21" t="inlineStr" s="21">
         <x:is>
-          <x:t>FRIEDMAN, SAMANTHA</x:t>
+          <x:t>Cassandra Sexton</x:t>
         </x:is>
       </x:c>
       <x:c r="K21" s="23">
-        <x:v>46105</x:v>
+        <x:v>46106</x:v>
       </x:c>
       <x:c r="L21" s="25">
-        <x:v>46105</x:v>
+        <x:v>46106</x:v>
       </x:c>
     </x:row>
     <x:row r="22">
@@ -1254,21 +1254,21 @@
         </x:is>
       </x:c>
       <x:c r="B22" t="n" s="5">
-        <x:v>0</x:v>
+        <x:v>710.85</x:v>
       </x:c>
       <x:c r="C22" t="inlineStr" s="7">
         <x:is>
-          <x:t>Club Member, Gemaire, Parts Received </x:t>
+          <x:t>10-10-10, Club Member, Parts Ordered</x:t>
         </x:is>
       </x:c>
       <x:c r="D22" t="inlineStr" s="9">
         <x:is>
-          <x:t>587448096</x:t>
+          <x:t>587680855</x:t>
         </x:is>
       </x:c>
       <x:c r="E22" t="inlineStr" s="11">
         <x:is>
-          <x:t>587448096</x:t>
+          <x:t>587680855</x:t>
         </x:is>
       </x:c>
       <x:c r="F22" s="13">
@@ -1276,7 +1276,7 @@
       </x:c>
       <x:c r="G22" t="inlineStr" s="15">
         <x:is>
-          <x:t/>
+          <x:t>PP Martin Ebanks</x:t>
         </x:is>
       </x:c>
       <x:c r="H22" t="inlineStr" s="17">
@@ -1286,19 +1286,19 @@
       </x:c>
       <x:c r="I22" t="inlineStr" s="19">
         <x:is>
-          <x:t>PLM - HVAC - Service - 12</x:t>
+          <x:t>CS - HVAC - Service - 12</x:t>
         </x:is>
       </x:c>
       <x:c r="J22" t="inlineStr" s="21">
         <x:is>
-          <x:t>Cassandra Sexton</x:t>
+          <x:t>Lester  Mena</x:t>
         </x:is>
       </x:c>
       <x:c r="K22" s="23">
-        <x:v>46106</x:v>
+        <x:v>46108</x:v>
       </x:c>
       <x:c r="L22" s="25">
-        <x:v>46106</x:v>
+        <x:v>46108</x:v>
       </x:c>
     </x:row>
     <x:row r="23">
@@ -1308,21 +1308,21 @@
         </x:is>
       </x:c>
       <x:c r="B23" t="n" s="5">
-        <x:v>0</x:v>
+        <x:v>708.54</x:v>
       </x:c>
       <x:c r="C23" t="inlineStr" s="7">
         <x:is>
-          <x:t>Club Member, LW- 2 YEAR LABOR, Parts Ordered, Trane Supply</x:t>
+          <x:t>10-10-10, 10-10-10, 10-10-10, 10-10-10, Club Member, Need to order part (NTO)</x:t>
         </x:is>
       </x:c>
       <x:c r="D23" t="inlineStr" s="9">
         <x:is>
-          <x:t>587077196</x:t>
+          <x:t>587676974</x:t>
         </x:is>
       </x:c>
       <x:c r="E23" t="inlineStr" s="11">
         <x:is>
-          <x:t>587077196</x:t>
+          <x:t>587676974</x:t>
         </x:is>
       </x:c>
       <x:c r="F23" s="13">
@@ -1330,7 +1330,7 @@
       </x:c>
       <x:c r="G23" t="inlineStr" s="15">
         <x:is>
-          <x:t>Tyler Gallatin</x:t>
+          <x:t>Rolin Moimeme</x:t>
         </x:is>
       </x:c>
       <x:c r="H23" t="inlineStr" s="17">
@@ -1345,14 +1345,14 @@
       </x:c>
       <x:c r="J23" t="inlineStr" s="21">
         <x:is>
-          <x:t>Timberwalk Association Inc</x:t>
+          <x:t>Teresa &amp; Joe Perez</x:t>
         </x:is>
       </x:c>
       <x:c r="K23" s="23">
-        <x:v>46102</x:v>
+        <x:v>46108</x:v>
       </x:c>
       <x:c r="L23" s="25">
-        <x:v>46102</x:v>
+        <x:v>46108</x:v>
       </x:c>
     </x:row>
     <x:row r="24">
@@ -1788,52 +1788,646 @@
       </x:c>
     </x:row>
     <x:row r="32">
-      <x:c r="A32" t="n" s="4">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="B32" t="n" s="6">
-        <x:v>687.866</x:v>
-      </x:c>
-      <x:c r="C32" t="inlineStr" s="8">
+      <x:c r="A32" t="inlineStr" s="3">
+        <x:is>
+          <x:t>HC - Return to Repair</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B32" t="n" s="5">
+        <x:v>2418</x:v>
+      </x:c>
+      <x:c r="C32" t="inlineStr" s="7">
+        <x:is>
+          <x:t>Need to order part (NTO), Potential Member, Replacement Opportunity</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D32" t="inlineStr" s="9">
+        <x:is>
+          <x:t>587767849</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E32" t="inlineStr" s="11">
+        <x:is>
+          <x:t>587767849</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F32" s="13">
+        <x:v>46109</x:v>
+      </x:c>
+      <x:c r="G32" t="inlineStr" s="15">
+        <x:is>
+          <x:t>Michael Donnauro</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="H32" t="inlineStr" s="17">
+        <x:is>
+          <x:t>Hold</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="I32" t="inlineStr" s="19">
+        <x:is>
+          <x:t>CS - HVAC - Service - 12</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="J32" t="inlineStr" s="21">
+        <x:is>
+          <x:t>Diomicira Zecchino</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="K32" s="23">
+        <x:v>46109</x:v>
+      </x:c>
+      <x:c r="L32" s="25">
+        <x:v>46109</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="33">
+      <x:c r="A33" t="inlineStr" s="3">
+        <x:is>
+          <x:t>HC - Return to Repair</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B33" t="n" s="5">
+        <x:v>579.81</x:v>
+      </x:c>
+      <x:c r="C33" t="inlineStr" s="7">
+        <x:is>
+          <x:t>Club Member, Need to order part (NTO), Replacement Opportunity</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D33" t="inlineStr" s="9">
+        <x:is>
+          <x:t>587764352</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E33" t="inlineStr" s="11">
+        <x:is>
+          <x:t>587764352</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F33" s="13">
+        <x:v>46109</x:v>
+      </x:c>
+      <x:c r="G33" t="inlineStr" s="15">
+        <x:is>
+          <x:t>PP Barrington Wilson</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="H33" t="inlineStr" s="17">
+        <x:is>
+          <x:t>Hold</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="I33" t="inlineStr" s="19">
+        <x:is>
+          <x:t>CS - HVAC - Service - 12</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="J33" t="inlineStr" s="21">
+        <x:is>
+          <x:t>Edna Parkin</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="K33" s="23">
+        <x:v>46109</x:v>
+      </x:c>
+      <x:c r="L33" s="25">
+        <x:v>46109</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="34">
+      <x:c r="A34" t="inlineStr" s="3">
+        <x:is>
+          <x:t>HC - Return to Repair</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B34" t="n" s="5">
+        <x:v>810.22</x:v>
+      </x:c>
+      <x:c r="C34" t="inlineStr" s="7">
+        <x:is>
+          <x:t>Club Member, Need to order part (NTO)</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D34" t="inlineStr" s="9">
+        <x:is>
+          <x:t>587761129</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E34" t="inlineStr" s="11">
+        <x:is>
+          <x:t>587761129</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F34" s="13">
+        <x:v>46109</x:v>
+      </x:c>
+      <x:c r="G34" t="inlineStr" s="15">
+        <x:is>
+          <x:t>Rolin Moimeme</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="H34" t="inlineStr" s="17">
+        <x:is>
+          <x:t>Hold</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="I34" t="inlineStr" s="19">
+        <x:is>
+          <x:t>PLM - HVAC - Service - 12</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="J34" t="inlineStr" s="21">
+        <x:is>
+          <x:t>Nancy Brown</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="K34" s="23">
+        <x:v>46109</x:v>
+      </x:c>
+      <x:c r="L34" s="25">
+        <x:v>46109</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="35">
+      <x:c r="A35" t="inlineStr" s="3">
+        <x:is>
+          <x:t>HC - Return to Repair</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B35" t="n" s="5">
+        <x:v>2022</x:v>
+      </x:c>
+      <x:c r="C35" t="inlineStr" s="7">
+        <x:is>
+          <x:t>Need to order part (NTO), Potential Member</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D35" t="inlineStr" s="9">
+        <x:is>
+          <x:t>587751042</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E35" t="inlineStr" s="11">
+        <x:is>
+          <x:t>587751042</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F35" s="13">
+        <x:v>46109</x:v>
+      </x:c>
+      <x:c r="G35" t="inlineStr" s="15">
+        <x:is>
+          <x:t>Rickey McClam </x:t>
+        </x:is>
+      </x:c>
+      <x:c r="H35" t="inlineStr" s="17">
+        <x:is>
+          <x:t>Hold</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="I35" t="inlineStr" s="19">
+        <x:is>
+          <x:t>PLM - HVAC - Service - 12</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="J35" t="inlineStr" s="21">
+        <x:is>
+          <x:t>Andy Ong</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="K35" s="23">
+        <x:v>46109</x:v>
+      </x:c>
+      <x:c r="L35" s="25">
+        <x:v>46109</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="36">
+      <x:c r="A36" t="inlineStr" s="3">
+        <x:is>
+          <x:t>HC - Return to Repair</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B36" t="n" s="5">
+        <x:v>2295.35</x:v>
+      </x:c>
+      <x:c r="C36" t="inlineStr" s="7">
+        <x:is>
+          <x:t>Club Member 3 sys, Need to order part (NTO)</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D36" t="inlineStr" s="9">
+        <x:is>
+          <x:t>587732375</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E36" t="inlineStr" s="11">
+        <x:is>
+          <x:t>587732375</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F36" s="13">
+        <x:v>46109</x:v>
+      </x:c>
+      <x:c r="G36" t="inlineStr" s="15">
+        <x:is>
+          <x:t>PP Gurpreet Parihar</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="H36" t="inlineStr" s="17">
+        <x:is>
+          <x:t>Hold</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="I36" t="inlineStr" s="19">
+        <x:is>
+          <x:t>CS - HVAC - Service - 12</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="J36" t="inlineStr" s="21">
+        <x:is>
+          <x:t>Mandelbaum, Shelly 0201146</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="K36" s="23">
+        <x:v>46108</x:v>
+      </x:c>
+      <x:c r="L36" s="25">
+        <x:v>46108</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="37">
+      <x:c r="A37" t="inlineStr" s="3">
+        <x:is>
+          <x:t>HC - Return to Repair</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B37" t="n" s="5">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="C37" t="inlineStr" s="7">
+        <x:is>
+          <x:t>10-Year Labor, 10-Year Labor, 10-Year Labor, 10-Year Labor, 10-Year Labor, Costco Estimate, Need to order part (NTO), Potential Member</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D37" t="inlineStr" s="9">
+        <x:is>
+          <x:t>587732523</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E37" t="inlineStr" s="11">
+        <x:is>
+          <x:t>587732523</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F37" s="13">
+        <x:v>46109</x:v>
+      </x:c>
+      <x:c r="G37" t="inlineStr" s="15">
+        <x:is>
+          <x:t>Bruce Coe</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="H37" t="inlineStr" s="17">
+        <x:is>
+          <x:t>Hold</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="I37" t="inlineStr" s="19">
+        <x:is>
+          <x:t>CS - HVAC - Service - 12</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="J37" t="inlineStr" s="21">
+        <x:is>
+          <x:t>Chris Madzi</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="K37" s="23">
+        <x:v>46108</x:v>
+      </x:c>
+      <x:c r="L37" s="25">
+        <x:v>46108</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="38">
+      <x:c r="A38" t="inlineStr" s="3">
+        <x:is>
+          <x:t>HC - Return to Repair</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B38" t="n" s="5">
+        <x:v>486.28</x:v>
+      </x:c>
+      <x:c r="C38" t="inlineStr" s="7">
+        <x:is>
+          <x:t>10-10-10, 10-10-10, 10-10-10, 10-10-10, Need to order part (NTO), Potential Member</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D38" t="inlineStr" s="9">
+        <x:is>
+          <x:t>587789767</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E38" t="inlineStr" s="11">
+        <x:is>
+          <x:t>587789767</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F38" s="13">
+        <x:v>46110</x:v>
+      </x:c>
+      <x:c r="G38" t="inlineStr" s="15">
+        <x:is>
+          <x:t>Tyler Gallatin</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="H38" t="inlineStr" s="17">
+        <x:is>
+          <x:t>Hold</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="I38" t="inlineStr" s="19">
+        <x:is>
+          <x:t>CS - HVAC - Service - 12</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="J38" t="inlineStr" s="21">
+        <x:is>
+          <x:t>Angelina DeCerbo</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="K38" s="23">
+        <x:v>46110</x:v>
+      </x:c>
+      <x:c r="L38" s="25">
+        <x:v>46110</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="39">
+      <x:c r="A39" t="inlineStr" s="3">
+        <x:is>
+          <x:t>HC - Return to Repair</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B39" t="n" s="5">
+        <x:v>1883</x:v>
+      </x:c>
+      <x:c r="C39" t="inlineStr" s="7">
+        <x:is>
+          <x:t>Need to order part (NTO), NO AIR, PLM, Potential Member</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D39" t="inlineStr" s="9">
+        <x:is>
+          <x:t>587796621</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E39" t="inlineStr" s="11">
+        <x:is>
+          <x:t>587796621</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F39" s="13">
+        <x:v>46110</x:v>
+      </x:c>
+      <x:c r="G39" t="inlineStr" s="15">
+        <x:is>
+          <x:t>Jesse Dague</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="H39" t="inlineStr" s="17">
+        <x:is>
+          <x:t>Hold</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="I39" t="inlineStr" s="19">
+        <x:is>
+          <x:t>PLM - HVAC - Service - 12</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="J39" t="inlineStr" s="21">
+        <x:is>
+          <x:t>BONCZEK, TIM</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="K39" s="23">
+        <x:v>46110</x:v>
+      </x:c>
+      <x:c r="L39" s="25">
+        <x:v>46110</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="40">
+      <x:c r="A40" t="inlineStr" s="3">
+        <x:is>
+          <x:t>HC - Return to Repair</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B40" t="n" s="5">
+        <x:v>1340.1</x:v>
+      </x:c>
+      <x:c r="C40" t="inlineStr" s="7">
+        <x:is>
+          <x:t>Club Member, Club Member (Additional System), MULTI- 3, Need to order part (NTO), PLM</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D40" t="inlineStr" s="9">
+        <x:is>
+          <x:t>587789529</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E40" t="inlineStr" s="11">
+        <x:is>
+          <x:t>587789529</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F40" s="13">
+        <x:v>46110</x:v>
+      </x:c>
+      <x:c r="G40" t="inlineStr" s="15">
+        <x:is>
+          <x:t>PP Tyriq McCall</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="H40" t="inlineStr" s="17">
+        <x:is>
+          <x:t>Hold</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="I40" t="inlineStr" s="19">
+        <x:is>
+          <x:t>PLM - HVAC - Service - 12</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="J40" t="inlineStr" s="21">
+        <x:is>
+          <x:t>Robert Lake</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="K40" s="23">
+        <x:v>46110</x:v>
+      </x:c>
+      <x:c r="L40" s="25">
+        <x:v>46110</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="41">
+      <x:c r="A41" t="inlineStr" s="3">
+        <x:is>
+          <x:t>HC - Return to Repair</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B41" t="n" s="5">
+        <x:v>530</x:v>
+      </x:c>
+      <x:c r="C41" t="inlineStr" s="7">
+        <x:is>
+          <x:t>Club Member 3 sys, MULTI- 3, Need to order part (NTO), PLM, Replacement Opportunity</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D41" t="inlineStr" s="9">
+        <x:is>
+          <x:t>587789020</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E41" t="inlineStr" s="11">
+        <x:is>
+          <x:t>587789020</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F41" s="13">
+        <x:v>46110</x:v>
+      </x:c>
+      <x:c r="G41" t="inlineStr" s="15">
+        <x:is>
+          <x:t>PP Anthony Capalbo</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="H41" t="inlineStr" s="17">
+        <x:is>
+          <x:t>Hold</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="I41" t="inlineStr" s="19">
+        <x:is>
+          <x:t>PLM - HVAC - Service - 12</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="J41" t="inlineStr" s="21">
+        <x:is>
+          <x:t>HARRIS, MIKE</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="K41" s="23">
+        <x:v>46110</x:v>
+      </x:c>
+      <x:c r="L41" s="25">
+        <x:v>46110</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="42">
+      <x:c r="A42" t="inlineStr" s="3">
+        <x:is>
+          <x:t>HC - Return to Repair</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B42" t="n" s="5">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="C42" t="inlineStr" s="7">
+        <x:is>
+          <x:t>Club Member, Need to order part (NTO), PLM</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D42" t="inlineStr" s="9">
+        <x:is>
+          <x:t>587785435</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E42" t="inlineStr" s="11">
+        <x:is>
+          <x:t>587785435</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F42" s="13">
+        <x:v>46110</x:v>
+      </x:c>
+      <x:c r="G42" t="inlineStr" s="15">
+        <x:is>
+          <x:t>Tyler Gallatin</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="H42" t="inlineStr" s="17">
+        <x:is>
+          <x:t>Hold</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="I42" t="inlineStr" s="19">
+        <x:is>
+          <x:t>PLM - HVAC - Service - 12</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="J42" t="inlineStr" s="21">
+        <x:is>
+          <x:t>CHACON, LERA</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="K42" s="23">
+        <x:v>46110</x:v>
+      </x:c>
+      <x:c r="L42" s="25">
+        <x:v>46110</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="43">
+      <x:c r="A43" t="n" s="4">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="B43" t="n" s="6">
+        <x:v>798.97</x:v>
+      </x:c>
+      <x:c r="C43" t="inlineStr" s="8">
         <x:is>
           <x:t/>
         </x:is>
       </x:c>
-      <x:c r="D32" t="n" s="10">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="E32" t="inlineStr" s="12">
+      <x:c r="D43" t="n" s="10">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="E43" t="inlineStr" s="12">
         <x:is>
           <x:t/>
         </x:is>
       </x:c>
-      <x:c r="F32" s="14">
+      <x:c r="F43" s="14">
         <x:v/>
       </x:c>
-      <x:c r="G32" t="inlineStr" s="16">
+      <x:c r="G43" t="inlineStr" s="16">
         <x:is>
           <x:t/>
         </x:is>
       </x:c>
-      <x:c r="H32" t="inlineStr" s="18">
+      <x:c r="H43" t="inlineStr" s="18">
         <x:is>
           <x:t/>
         </x:is>
       </x:c>
-      <x:c r="I32" t="inlineStr" s="20">
+      <x:c r="I43" t="inlineStr" s="20">
         <x:is>
           <x:t/>
         </x:is>
       </x:c>
-      <x:c r="J32" t="inlineStr" s="22">
+      <x:c r="J43" t="inlineStr" s="22">
         <x:is>
           <x:t/>
         </x:is>
       </x:c>
-      <x:c r="K32" s="24">
+      <x:c r="K43" s="24">
         <x:v/>
       </x:c>
-      <x:c r="L32" s="26">
+      <x:c r="L43" s="26">
         <x:v/>
       </x:c>
     </x:row>
@@ -1864,7 +2458,7 @@
       </x:c>
       <x:c r="B2" t="inlineStr" s="28">
         <x:is>
-          <x:t>03/27/25 - 03/27/26</x:t>
+          <x:t>03/29/25 - 03/29/26</x:t>
         </x:is>
       </x:c>
     </x:row>
@@ -1930,7 +2524,7 @@
     <x:mergeCell ref="A8:B8"/>
   </x:mergeCells>
   <x:hyperlinks>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A8" r:id="hyperlinkId1" location="/new/reports/459565681?DateType=3&amp;BusinessUnitId=2415185%2C2415187%2C15775258%2C2415186%2C2415190%2C182981963%2C182981958%2C182981961%2C182981957&amp;IncludeAdjustmentInvoices=false&amp;IsScheduling=True&amp;From=2025-03-27&amp;To=2026-03-27" display="View Report"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A8" r:id="hyperlinkId1" location="/new/reports/459565681?DateType=3&amp;BusinessUnitId=2415185%2C2415187%2C15775258%2C2415186%2C2415190%2C182981963%2C182981958%2C182981961%2C182981957&amp;IncludeAdjustmentInvoices=false&amp;IsScheduling=True&amp;From=2025-03-29&amp;To=2026-03-29" display="View Report"/>
   </x:hyperlinks>
 </x:worksheet>
 </file>
--- a/data/parts_report_past.xlsx
+++ b/data/parts_report_past.xlsx
@@ -5,8 +5,8 @@
     <x:workbookView/>
   </x:bookViews>
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rb5ddda3f96104405"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Filters" sheetId="2" r:id="R3b0338e1df724b66"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Reb4265eb21734fb8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Filters" sheetId="2" r:id="Rcd49ef8499ef4458"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -1615,7 +1615,7 @@
       </x:c>
       <x:c r="J28" t="inlineStr" s="21">
         <x:is>
-          <x:t>CHACON, LERA</x:t>
+          <x:t>Lera Chacon</x:t>
         </x:is>
       </x:c>
       <x:c r="K28" s="23">
@@ -2118,21 +2118,21 @@
         </x:is>
       </x:c>
       <x:c r="B38" t="n" s="5">
-        <x:v>486.28</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="C38" t="inlineStr" s="7">
         <x:is>
-          <x:t>10-10-10, 10-10-10, 10-10-10, 10-10-10, Need to order part (NTO), Potential Member</x:t>
+          <x:t>10-10-10, Club Member, Need to order part (NTO), NO AIR</x:t>
         </x:is>
       </x:c>
       <x:c r="D38" t="inlineStr" s="9">
         <x:is>
-          <x:t>587789767</x:t>
+          <x:t>587794613</x:t>
         </x:is>
       </x:c>
       <x:c r="E38" t="inlineStr" s="11">
         <x:is>
-          <x:t>587789767</x:t>
+          <x:t>587794613</x:t>
         </x:is>
       </x:c>
       <x:c r="F38" s="13">
@@ -2140,7 +2140,7 @@
       </x:c>
       <x:c r="G38" t="inlineStr" s="15">
         <x:is>
-          <x:t>Tyler Gallatin</x:t>
+          <x:t>PP Cesar Levy</x:t>
         </x:is>
       </x:c>
       <x:c r="H38" t="inlineStr" s="17">
@@ -2155,7 +2155,7 @@
       </x:c>
       <x:c r="J38" t="inlineStr" s="21">
         <x:is>
-          <x:t>Angelina DeCerbo</x:t>
+          <x:t>Rene Ceusters</x:t>
         </x:is>
       </x:c>
       <x:c r="K38" s="23">
@@ -2172,21 +2172,21 @@
         </x:is>
       </x:c>
       <x:c r="B39" t="n" s="5">
-        <x:v>1883</x:v>
+        <x:v>436.28</x:v>
       </x:c>
       <x:c r="C39" t="inlineStr" s="7">
         <x:is>
-          <x:t>Need to order part (NTO), NO AIR, PLM, Potential Member</x:t>
+          <x:t>10-10-10, 10-10-10, 10-10-10, 10-10-10, Need to order part (NTO), Potential Member</x:t>
         </x:is>
       </x:c>
       <x:c r="D39" t="inlineStr" s="9">
         <x:is>
-          <x:t>587796621</x:t>
+          <x:t>587789767</x:t>
         </x:is>
       </x:c>
       <x:c r="E39" t="inlineStr" s="11">
         <x:is>
-          <x:t>587796621</x:t>
+          <x:t>587789767</x:t>
         </x:is>
       </x:c>
       <x:c r="F39" s="13">
@@ -2194,7 +2194,7 @@
       </x:c>
       <x:c r="G39" t="inlineStr" s="15">
         <x:is>
-          <x:t>Jesse Dague</x:t>
+          <x:t>Tyler Gallatin</x:t>
         </x:is>
       </x:c>
       <x:c r="H39" t="inlineStr" s="17">
@@ -2204,12 +2204,12 @@
       </x:c>
       <x:c r="I39" t="inlineStr" s="19">
         <x:is>
-          <x:t>PLM - HVAC - Service - 12</x:t>
+          <x:t>CS - HVAC - Service - 12</x:t>
         </x:is>
       </x:c>
       <x:c r="J39" t="inlineStr" s="21">
         <x:is>
-          <x:t>BONCZEK, TIM</x:t>
+          <x:t>Angelina DeCerbo</x:t>
         </x:is>
       </x:c>
       <x:c r="K39" s="23">
@@ -2226,21 +2226,21 @@
         </x:is>
       </x:c>
       <x:c r="B40" t="n" s="5">
-        <x:v>1340.1</x:v>
+        <x:v>1883</x:v>
       </x:c>
       <x:c r="C40" t="inlineStr" s="7">
         <x:is>
-          <x:t>Club Member, Club Member (Additional System), MULTI- 3, Need to order part (NTO), PLM</x:t>
+          <x:t>Need to order part (NTO), NO AIR, PLM, Potential Member</x:t>
         </x:is>
       </x:c>
       <x:c r="D40" t="inlineStr" s="9">
         <x:is>
-          <x:t>587789529</x:t>
+          <x:t>587796621</x:t>
         </x:is>
       </x:c>
       <x:c r="E40" t="inlineStr" s="11">
         <x:is>
-          <x:t>587789529</x:t>
+          <x:t>587796621</x:t>
         </x:is>
       </x:c>
       <x:c r="F40" s="13">
@@ -2248,7 +2248,7 @@
       </x:c>
       <x:c r="G40" t="inlineStr" s="15">
         <x:is>
-          <x:t>PP Tyriq McCall</x:t>
+          <x:t>Jesse Dague</x:t>
         </x:is>
       </x:c>
       <x:c r="H40" t="inlineStr" s="17">
@@ -2263,7 +2263,7 @@
       </x:c>
       <x:c r="J40" t="inlineStr" s="21">
         <x:is>
-          <x:t>Robert Lake</x:t>
+          <x:t>BONCZEK, TIM</x:t>
         </x:is>
       </x:c>
       <x:c r="K40" s="23">
@@ -2280,21 +2280,21 @@
         </x:is>
       </x:c>
       <x:c r="B41" t="n" s="5">
-        <x:v>530</x:v>
+        <x:v>1340.1</x:v>
       </x:c>
       <x:c r="C41" t="inlineStr" s="7">
         <x:is>
-          <x:t>Club Member 3 sys, MULTI- 3, Need to order part (NTO), PLM, Replacement Opportunity</x:t>
+          <x:t>Club Member, Club Member (Additional System), MULTI- 3, Need to order part (NTO), PLM</x:t>
         </x:is>
       </x:c>
       <x:c r="D41" t="inlineStr" s="9">
         <x:is>
-          <x:t>587789020</x:t>
+          <x:t>587789529</x:t>
         </x:is>
       </x:c>
       <x:c r="E41" t="inlineStr" s="11">
         <x:is>
-          <x:t>587789020</x:t>
+          <x:t>587789529</x:t>
         </x:is>
       </x:c>
       <x:c r="F41" s="13">
@@ -2302,7 +2302,7 @@
       </x:c>
       <x:c r="G41" t="inlineStr" s="15">
         <x:is>
-          <x:t>PP Anthony Capalbo</x:t>
+          <x:t>PP Tyriq McCall</x:t>
         </x:is>
       </x:c>
       <x:c r="H41" t="inlineStr" s="17">
@@ -2317,7 +2317,7 @@
       </x:c>
       <x:c r="J41" t="inlineStr" s="21">
         <x:is>
-          <x:t>HARRIS, MIKE</x:t>
+          <x:t>Robert Lake</x:t>
         </x:is>
       </x:c>
       <x:c r="K41" s="23">
@@ -2334,21 +2334,21 @@
         </x:is>
       </x:c>
       <x:c r="B42" t="n" s="5">
-        <x:v>0</x:v>
+        <x:v>530</x:v>
       </x:c>
       <x:c r="C42" t="inlineStr" s="7">
         <x:is>
-          <x:t>Club Member, Need to order part (NTO), PLM</x:t>
+          <x:t>Club Member 3 sys, MULTI- 3, Need to order part (NTO), PLM, Replacement Opportunity</x:t>
         </x:is>
       </x:c>
       <x:c r="D42" t="inlineStr" s="9">
         <x:is>
-          <x:t>587785435</x:t>
+          <x:t>587789020</x:t>
         </x:is>
       </x:c>
       <x:c r="E42" t="inlineStr" s="11">
         <x:is>
-          <x:t>587785435</x:t>
+          <x:t>587789020</x:t>
         </x:is>
       </x:c>
       <x:c r="F42" s="13">
@@ -2356,7 +2356,7 @@
       </x:c>
       <x:c r="G42" t="inlineStr" s="15">
         <x:is>
-          <x:t>Tyler Gallatin</x:t>
+          <x:t>PP Anthony Capalbo</x:t>
         </x:is>
       </x:c>
       <x:c r="H42" t="inlineStr" s="17">
@@ -2371,7 +2371,7 @@
       </x:c>
       <x:c r="J42" t="inlineStr" s="21">
         <x:is>
-          <x:t>CHACON, LERA</x:t>
+          <x:t>HARRIS, MIKE</x:t>
         </x:is>
       </x:c>
       <x:c r="K42" s="23">
@@ -2382,52 +2382,430 @@
       </x:c>
     </x:row>
     <x:row r="43">
-      <x:c r="A43" t="n" s="4">
-        <x:v>41</x:v>
-      </x:c>
-      <x:c r="B43" t="n" s="6">
-        <x:v>798.97</x:v>
-      </x:c>
-      <x:c r="C43" t="inlineStr" s="8">
+      <x:c r="A43" t="inlineStr" s="3">
+        <x:is>
+          <x:t>HC - Return to Repair</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B43" t="n" s="5">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="C43" t="inlineStr" s="7">
+        <x:is>
+          <x:t>Club Member, Need to order part (NTO), PLM</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D43" t="inlineStr" s="9">
+        <x:is>
+          <x:t>587785435</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E43" t="inlineStr" s="11">
+        <x:is>
+          <x:t>587785435</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F43" s="13">
+        <x:v>46110</x:v>
+      </x:c>
+      <x:c r="G43" t="inlineStr" s="15">
+        <x:is>
+          <x:t>Tyler Gallatin</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="H43" t="inlineStr" s="17">
+        <x:is>
+          <x:t>Hold</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="I43" t="inlineStr" s="19">
+        <x:is>
+          <x:t>PLM - HVAC - Service - 12</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="J43" t="inlineStr" s="21">
+        <x:is>
+          <x:t>Lera Chacon</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="K43" s="23">
+        <x:v>46110</x:v>
+      </x:c>
+      <x:c r="L43" s="25">
+        <x:v>46110</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="44">
+      <x:c r="A44" t="inlineStr" s="3">
+        <x:is>
+          <x:t>HC - Return to Repair</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B44" t="n" s="5">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="C44" t="inlineStr" s="7">
+        <x:is>
+          <x:t>5 YEAR WARRANTY, 5 YEAR WARRANTY, 5 YEAR WARRANTY, 5 YEAR WARRANTY, Club Member</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D44" t="inlineStr" s="9">
+        <x:is>
+          <x:t>587794082</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E44" t="inlineStr" s="11">
+        <x:is>
+          <x:t>587794082</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F44" s="13">
+        <x:v>46111</x:v>
+      </x:c>
+      <x:c r="G44" t="inlineStr" s="15">
+        <x:is>
+          <x:t>Tyler Gallatin</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="H44" t="inlineStr" s="17">
+        <x:is>
+          <x:t>Hold</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="I44" t="inlineStr" s="19">
+        <x:is>
+          <x:t>CS - HVAC - Service - 12</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="J44" t="inlineStr" s="21">
+        <x:is>
+          <x:t>Louise Claydon</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="K44" s="23">
+        <x:v>46110</x:v>
+      </x:c>
+      <x:c r="L44" s="25">
+        <x:v>46110</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="45">
+      <x:c r="A45" t="inlineStr" s="3">
+        <x:is>
+          <x:t>HC - Return to Repair</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B45" t="n" s="5">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="C45" t="inlineStr" s="7">
+        <x:is>
+          <x:t>5 YEAR WARRANTY, 5 YEAR WARRANTY, 5 YEAR WARRANTY, 5 YEAR WARRANTY, 5 YEAR WARRANTY, 5 YEAR WARRANTY, Club Member 3 sys, Gemaire, MULTI- 3, Parts Ordered</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D45" t="inlineStr" s="9">
+        <x:is>
+          <x:t>586595677</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E45" t="inlineStr" s="11">
+        <x:is>
+          <x:t>586595677</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F45" s="13">
+        <x:v>46111</x:v>
+      </x:c>
+      <x:c r="G45" t="inlineStr" s="15">
+        <x:is>
+          <x:t>PP Alejandro Espinosa</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="H45" t="inlineStr" s="17">
+        <x:is>
+          <x:t>Hold</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="I45" t="inlineStr" s="19">
+        <x:is>
+          <x:t>PLM - HVAC - Service - 12</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="J45" t="inlineStr" s="21">
+        <x:is>
+          <x:t>Bob Lauson</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="K45" s="23">
+        <x:v>46098</x:v>
+      </x:c>
+      <x:c r="L45" s="25">
+        <x:v>46098</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="46">
+      <x:c r="A46" t="inlineStr" s="3">
+        <x:is>
+          <x:t>HC - Return to Repair</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B46" t="n" s="5">
+        <x:v>462.83</x:v>
+      </x:c>
+      <x:c r="C46" t="inlineStr" s="7">
+        <x:is>
+          <x:t>Baker Supply, Club Member, Parts Ordered, PLM, Potential Membership Renewal, Residential Maintenance Agreement</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D46" t="inlineStr" s="9">
+        <x:is>
+          <x:t>555552166</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E46" t="inlineStr" s="11">
+        <x:is>
+          <x:t>555552166</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F46" s="13">
+        <x:v>46111</x:v>
+      </x:c>
+      <x:c r="G46" t="inlineStr" s="15">
+        <x:is>
+          <x:t>PP Cesar Levy</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="H46" t="inlineStr" s="17">
+        <x:is>
+          <x:t>Hold</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="I46" t="inlineStr" s="19">
+        <x:is>
+          <x:t>PLM - HVAC - Service - 12</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="J46" t="inlineStr" s="21">
+        <x:is>
+          <x:t>Wanda Betancourt</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="K46" s="23">
+        <x:v>46007</x:v>
+      </x:c>
+      <x:c r="L46" s="25">
+        <x:v>46007</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="47">
+      <x:c r="A47" t="inlineStr" s="3">
+        <x:is>
+          <x:t>HC - Return to Repair</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B47" t="n" s="5">
+        <x:v>945.4</x:v>
+      </x:c>
+      <x:c r="C47" t="inlineStr" s="7">
+        <x:is>
+          <x:t>Carrier enterprise, Club Member, Parts Received , PLM</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D47" t="inlineStr" s="9">
+        <x:is>
+          <x:t>587403893</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E47" t="inlineStr" s="11">
+        <x:is>
+          <x:t>587403893</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F47" s="13">
+        <x:v>46111</x:v>
+      </x:c>
+      <x:c r="G47" t="inlineStr" s="15">
+        <x:is>
+          <x:t>Rolin Moimeme</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="H47" t="inlineStr" s="17">
+        <x:is>
+          <x:t>Hold</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="I47" t="inlineStr" s="19">
+        <x:is>
+          <x:t>PLM - HVAC - Service - 12</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="J47" t="inlineStr" s="21">
+        <x:is>
+          <x:t>WALKER, CAMERON</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="K47" s="23">
+        <x:v>46106</x:v>
+      </x:c>
+      <x:c r="L47" s="25">
+        <x:v>46106</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="48">
+      <x:c r="A48" t="inlineStr" s="3">
+        <x:is>
+          <x:t>HC - Return to Repair</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B48" t="n" s="5">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="C48" t="inlineStr" s="7">
+        <x:is>
+          <x:t>Club Member, Gemaire, Parts Ordered</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D48" t="inlineStr" s="9">
+        <x:is>
+          <x:t>463016698</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E48" t="inlineStr" s="11">
+        <x:is>
+          <x:t>463016698</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F48" s="13">
+        <x:v>46111</x:v>
+      </x:c>
+      <x:c r="G48" t="inlineStr" s="15">
+        <x:is>
+          <x:t>PP Tyriq McCall</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="H48" t="inlineStr" s="17">
+        <x:is>
+          <x:t>Hold</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="I48" t="inlineStr" s="19">
+        <x:is>
+          <x:t>CS - HVAC - Service - 12</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="J48" t="inlineStr" s="21">
+        <x:is>
+          <x:t>Evan Frangos</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="K48" s="23">
+        <x:v>45762</x:v>
+      </x:c>
+      <x:c r="L48" s="25">
+        <x:v>45762</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="49">
+      <x:c r="A49" t="inlineStr" s="3">
+        <x:is>
+          <x:t>HC - Return to Repair</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B49" t="n" s="5">
+        <x:v>303.45</x:v>
+      </x:c>
+      <x:c r="C49" t="inlineStr" s="7">
+        <x:is>
+          <x:t>Carrier enterprise, Parts Ordered, Potential Member</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D49" t="inlineStr" s="9">
+        <x:is>
+          <x:t>581332764</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E49" t="inlineStr" s="11">
+        <x:is>
+          <x:t>581332764</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F49" s="13">
+        <x:v>46111</x:v>
+      </x:c>
+      <x:c r="G49" t="inlineStr" s="15">
+        <x:is>
+          <x:t>Justin Greene</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="H49" t="inlineStr" s="17">
+        <x:is>
+          <x:t>Hold</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="I49" t="inlineStr" s="19">
+        <x:is>
+          <x:t>CS - HVAC - Service - 12</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="J49" t="inlineStr" s="21">
+        <x:is>
+          <x:t>Chris Orsini</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="K49" s="23">
+        <x:v>46057</x:v>
+      </x:c>
+      <x:c r="L49" s="25">
+        <x:v>46057</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="50">
+      <x:c r="A50" t="n" s="4">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="B50" t="n" s="6">
+        <x:v>717.071875</x:v>
+      </x:c>
+      <x:c r="C50" t="inlineStr" s="8">
         <x:is>
           <x:t/>
         </x:is>
       </x:c>
-      <x:c r="D43" t="n" s="10">
-        <x:v>41</x:v>
-      </x:c>
-      <x:c r="E43" t="inlineStr" s="12">
+      <x:c r="D50" t="n" s="10">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="E50" t="inlineStr" s="12">
         <x:is>
           <x:t/>
         </x:is>
       </x:c>
-      <x:c r="F43" s="14">
+      <x:c r="F50" s="14">
         <x:v/>
       </x:c>
-      <x:c r="G43" t="inlineStr" s="16">
+      <x:c r="G50" t="inlineStr" s="16">
         <x:is>
           <x:t/>
         </x:is>
       </x:c>
-      <x:c r="H43" t="inlineStr" s="18">
+      <x:c r="H50" t="inlineStr" s="18">
         <x:is>
           <x:t/>
         </x:is>
       </x:c>
-      <x:c r="I43" t="inlineStr" s="20">
+      <x:c r="I50" t="inlineStr" s="20">
         <x:is>
           <x:t/>
         </x:is>
       </x:c>
-      <x:c r="J43" t="inlineStr" s="22">
+      <x:c r="J50" t="inlineStr" s="22">
         <x:is>
           <x:t/>
         </x:is>
       </x:c>
-      <x:c r="K43" s="24">
+      <x:c r="K50" s="24">
         <x:v/>
       </x:c>
-      <x:c r="L43" s="26">
+      <x:c r="L50" s="26">
         <x:v/>
       </x:c>
     </x:row>
@@ -2458,7 +2836,7 @@
       </x:c>
       <x:c r="B2" t="inlineStr" s="28">
         <x:is>
-          <x:t>03/29/25 - 03/29/26</x:t>
+          <x:t>03/30/25 - 03/30/26</x:t>
         </x:is>
       </x:c>
     </x:row>
@@ -2524,7 +2902,7 @@
     <x:mergeCell ref="A8:B8"/>
   </x:mergeCells>
   <x:hyperlinks>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A8" r:id="hyperlinkId1" location="/new/reports/459565681?DateType=3&amp;BusinessUnitId=2415185%2C2415187%2C15775258%2C2415186%2C2415190%2C182981963%2C182981958%2C182981961%2C182981957&amp;IncludeAdjustmentInvoices=false&amp;IsScheduling=True&amp;From=2025-03-29&amp;To=2026-03-29" display="View Report"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A8" r:id="hyperlinkId1" location="/new/reports/459565681?DateType=3&amp;BusinessUnitId=2415185%2C2415187%2C15775258%2C2415186%2C2415190%2C182981963%2C182981958%2C182981961%2C182981957&amp;IncludeAdjustmentInvoices=false&amp;IsScheduling=True&amp;From=2025-03-30&amp;To=2026-03-30" display="View Report"/>
   </x:hyperlinks>
 </x:worksheet>
 </file>
--- a/data/parts_report_past.xlsx
+++ b/data/parts_report_past.xlsx
@@ -5,8 +5,8 @@
     <x:workbookView/>
   </x:bookViews>
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Reb4265eb21734fb8"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Filters" sheetId="2" r:id="Rcd49ef8499ef4458"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R5260a6ba13cc4b82"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Filters" sheetId="2" r:id="Rea657e9dc8a7478a"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -498,29 +498,29 @@
         </x:is>
       </x:c>
       <x:c r="B8" t="n" s="5">
-        <x:v>0</x:v>
+        <x:v>1282.5</x:v>
       </x:c>
       <x:c r="C8" t="inlineStr" s="7">
         <x:is>
-          <x:t>10-Year Labor, 5 YEAR WARRANTY, 5 YEAR WARRANTY, 5 YEAR WARRANTY, Club Member, Goodman distribution , Parts Received </x:t>
+          <x:t>Club Member, Club Member (Additional System), Gemaire, Parts Received , PLM</x:t>
         </x:is>
       </x:c>
       <x:c r="D8" t="inlineStr" s="9">
         <x:is>
-          <x:t>584259475</x:t>
+          <x:t>586047631</x:t>
         </x:is>
       </x:c>
       <x:c r="E8" t="inlineStr" s="11">
         <x:is>
-          <x:t>584259475</x:t>
+          <x:t>586047631</x:t>
         </x:is>
       </x:c>
       <x:c r="F8" s="13">
-        <x:v>46094</x:v>
+        <x:v>46097</x:v>
       </x:c>
       <x:c r="G8" t="inlineStr" s="15">
         <x:is>
-          <x:t>Bruce Coe</x:t>
+          <x:t>PP Barrington Wilson</x:t>
         </x:is>
       </x:c>
       <x:c r="H8" t="inlineStr" s="17">
@@ -535,14 +535,14 @@
       </x:c>
       <x:c r="J8" t="inlineStr" s="21">
         <x:is>
-          <x:t>Barb Lois</x:t>
+          <x:t>MACLACHLAN, DAN</x:t>
         </x:is>
       </x:c>
       <x:c r="K8" s="23">
-        <x:v>46077</x:v>
+        <x:v>46092</x:v>
       </x:c>
       <x:c r="L8" s="25">
-        <x:v>46077</x:v>
+        <x:v>46092</x:v>
       </x:c>
     </x:row>
     <x:row r="9">
@@ -552,29 +552,29 @@
         </x:is>
       </x:c>
       <x:c r="B9" t="n" s="5">
-        <x:v>1282.5</x:v>
+        <x:v>292.95</x:v>
       </x:c>
       <x:c r="C9" t="inlineStr" s="7">
         <x:is>
-          <x:t>Club Member, Club Member (Additional System), Gemaire, Parts Received , PLM</x:t>
+          <x:t>Club Member, Gemaire, PSL Zone 4</x:t>
         </x:is>
       </x:c>
       <x:c r="D9" t="inlineStr" s="9">
         <x:is>
-          <x:t>586047631</x:t>
+          <x:t>586702574</x:t>
         </x:is>
       </x:c>
       <x:c r="E9" t="inlineStr" s="11">
         <x:is>
-          <x:t>586047631</x:t>
+          <x:t>586702574</x:t>
         </x:is>
       </x:c>
       <x:c r="F9" s="13">
-        <x:v>46097</x:v>
+        <x:v>46099</x:v>
       </x:c>
       <x:c r="G9" t="inlineStr" s="15">
         <x:is>
-          <x:t>PP Barrington Wilson</x:t>
+          <x:t>Jesse Dague</x:t>
         </x:is>
       </x:c>
       <x:c r="H9" t="inlineStr" s="17">
@@ -584,19 +584,19 @@
       </x:c>
       <x:c r="I9" t="inlineStr" s="19">
         <x:is>
-          <x:t>PLM - HVAC - Service - 12</x:t>
+          <x:t>CS - HVAC - Service - 12</x:t>
         </x:is>
       </x:c>
       <x:c r="J9" t="inlineStr" s="21">
         <x:is>
-          <x:t>MACLACHLAN, DAN</x:t>
+          <x:t>PAT WHELAN</x:t>
         </x:is>
       </x:c>
       <x:c r="K9" s="23">
-        <x:v>46092</x:v>
+        <x:v>46099</x:v>
       </x:c>
       <x:c r="L9" s="25">
-        <x:v>46092</x:v>
+        <x:v>46099</x:v>
       </x:c>
     </x:row>
     <x:row r="10">
@@ -606,29 +606,29 @@
         </x:is>
       </x:c>
       <x:c r="B10" t="n" s="5">
-        <x:v>292.95</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="C10" t="inlineStr" s="7">
         <x:is>
-          <x:t>Club Member, Gemaire, PSL Zone 4</x:t>
+          <x:t>5 YEAR WARRANTY, 5 YEAR WARRANTY, 5 YEAR WARRANTY, 5 YEAR WARRANTY, Club Member, Goodman distribution , Parts Received </x:t>
         </x:is>
       </x:c>
       <x:c r="D10" t="inlineStr" s="9">
         <x:is>
-          <x:t>586702574</x:t>
+          <x:t>586815067</x:t>
         </x:is>
       </x:c>
       <x:c r="E10" t="inlineStr" s="11">
         <x:is>
-          <x:t>586702574</x:t>
+          <x:t>586815067</x:t>
         </x:is>
       </x:c>
       <x:c r="F10" s="13">
-        <x:v>46099</x:v>
+        <x:v>46104</x:v>
       </x:c>
       <x:c r="G10" t="inlineStr" s="15">
         <x:is>
-          <x:t>Jesse Dague</x:t>
+          <x:t>Xavier Mateo</x:t>
         </x:is>
       </x:c>
       <x:c r="H10" t="inlineStr" s="17">
@@ -643,14 +643,14 @@
       </x:c>
       <x:c r="J10" t="inlineStr" s="21">
         <x:is>
-          <x:t>PAT WHELAN</x:t>
+          <x:t>Christine Semenza</x:t>
         </x:is>
       </x:c>
       <x:c r="K10" s="23">
-        <x:v>46099</x:v>
+        <x:v>46100</x:v>
       </x:c>
       <x:c r="L10" s="25">
-        <x:v>46099</x:v>
+        <x:v>46100</x:v>
       </x:c>
     </x:row>
     <x:row r="11">
@@ -660,21 +660,21 @@
         </x:is>
       </x:c>
       <x:c r="B11" t="n" s="5">
-        <x:v>0</x:v>
+        <x:v>1100</x:v>
       </x:c>
       <x:c r="C11" t="inlineStr" s="7">
         <x:is>
-          <x:t>5 YEAR WARRANTY, 5 YEAR WARRANTY, 5 YEAR WARRANTY, 5 YEAR WARRANTY, Club Member, Goodman distribution , Parts Received </x:t>
+          <x:t>Club Member, Parts Received , PLM</x:t>
         </x:is>
       </x:c>
       <x:c r="D11" t="inlineStr" s="9">
         <x:is>
-          <x:t>586815067</x:t>
+          <x:t>587202433</x:t>
         </x:is>
       </x:c>
       <x:c r="E11" t="inlineStr" s="11">
         <x:is>
-          <x:t>586815067</x:t>
+          <x:t>587202433</x:t>
         </x:is>
       </x:c>
       <x:c r="F11" s="13">
@@ -682,7 +682,7 @@
       </x:c>
       <x:c r="G11" t="inlineStr" s="15">
         <x:is>
-          <x:t>Xavier Mateo</x:t>
+          <x:t>PP Braxton Patterson </x:t>
         </x:is>
       </x:c>
       <x:c r="H11" t="inlineStr" s="17">
@@ -692,19 +692,19 @@
       </x:c>
       <x:c r="I11" t="inlineStr" s="19">
         <x:is>
-          <x:t>CS - HVAC - Service - 12</x:t>
+          <x:t>PLM - HVAC - Service - 12</x:t>
         </x:is>
       </x:c>
       <x:c r="J11" t="inlineStr" s="21">
         <x:is>
-          <x:t>Christine Semenza</x:t>
+          <x:t>CHRISTOPHER KENNEDY</x:t>
         </x:is>
       </x:c>
       <x:c r="K11" s="23">
-        <x:v>46100</x:v>
+        <x:v>46104</x:v>
       </x:c>
       <x:c r="L11" s="25">
-        <x:v>46100</x:v>
+        <x:v>46104</x:v>
       </x:c>
     </x:row>
     <x:row r="12">
@@ -714,29 +714,29 @@
         </x:is>
       </x:c>
       <x:c r="B12" t="n" s="5">
-        <x:v>0</x:v>
+        <x:v>691.98</x:v>
       </x:c>
       <x:c r="C12" t="inlineStr" s="7">
         <x:is>
-          <x:t>Carrier enterprise, Club Member, Parts Received </x:t>
+          <x:t>Club Member, Parts Received , Replacement Opportunity</x:t>
         </x:is>
       </x:c>
       <x:c r="D12" t="inlineStr" s="9">
         <x:is>
-          <x:t>586266511</x:t>
+          <x:t>587248489</x:t>
         </x:is>
       </x:c>
       <x:c r="E12" t="inlineStr" s="11">
         <x:is>
-          <x:t>586266511</x:t>
+          <x:t>587248489</x:t>
         </x:is>
       </x:c>
       <x:c r="F12" s="13">
-        <x:v>46104</x:v>
+        <x:v>46105</x:v>
       </x:c>
       <x:c r="G12" t="inlineStr" s="15">
         <x:is>
-          <x:t/>
+          <x:t>Justin Greene</x:t>
         </x:is>
       </x:c>
       <x:c r="H12" t="inlineStr" s="17">
@@ -751,14 +751,14 @@
       </x:c>
       <x:c r="J12" t="inlineStr" s="21">
         <x:is>
-          <x:t>Ruth Sapper</x:t>
+          <x:t>Baldwin Burey</x:t>
         </x:is>
       </x:c>
       <x:c r="K12" s="23">
-        <x:v>46094</x:v>
+        <x:v>46105</x:v>
       </x:c>
       <x:c r="L12" s="25">
-        <x:v>46094</x:v>
+        <x:v>46105</x:v>
       </x:c>
     </x:row>
     <x:row r="13">
@@ -768,25 +768,25 @@
         </x:is>
       </x:c>
       <x:c r="B13" t="n" s="5">
-        <x:v>1100</x:v>
+        <x:v>225</x:v>
       </x:c>
       <x:c r="C13" t="inlineStr" s="7">
         <x:is>
-          <x:t>Club Member, Parts Received , PLM</x:t>
+          <x:t>12-Year Labor, 12-Year Labor, 12-Year Labor, 12-Year Labor, 12-Year Labor, Carrier enterprise, Club Member 2 sys , MULTI- 2, Parts Received , PLM</x:t>
         </x:is>
       </x:c>
       <x:c r="D13" t="inlineStr" s="9">
         <x:is>
-          <x:t>587202433</x:t>
+          <x:t>586903562</x:t>
         </x:is>
       </x:c>
       <x:c r="E13" t="inlineStr" s="11">
         <x:is>
-          <x:t>587202433</x:t>
+          <x:t>586903562</x:t>
         </x:is>
       </x:c>
       <x:c r="F13" s="13">
-        <x:v>46104</x:v>
+        <x:v>46105</x:v>
       </x:c>
       <x:c r="G13" t="inlineStr" s="15">
         <x:is>
@@ -800,19 +800,19 @@
       </x:c>
       <x:c r="I13" t="inlineStr" s="19">
         <x:is>
-          <x:t>PLM - HVAC - Service - 12</x:t>
+          <x:t>CS - HVAC - Service - 12</x:t>
         </x:is>
       </x:c>
       <x:c r="J13" t="inlineStr" s="21">
         <x:is>
-          <x:t>CHRISTOPHER KENNEDY</x:t>
+          <x:t>Ruth  Hochberg</x:t>
         </x:is>
       </x:c>
       <x:c r="K13" s="23">
-        <x:v>46104</x:v>
+        <x:v>46100</x:v>
       </x:c>
       <x:c r="L13" s="25">
-        <x:v>46104</x:v>
+        <x:v>46100</x:v>
       </x:c>
     </x:row>
     <x:row r="14">
@@ -822,21 +822,21 @@
         </x:is>
       </x:c>
       <x:c r="B14" t="n" s="5">
-        <x:v>691.98</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="C14" t="inlineStr" s="7">
         <x:is>
-          <x:t>Club Member, Parts Received , Replacement Opportunity</x:t>
+          <x:t>10-10-10, 10-10-10, Carrier enterprise, Club Member, Parts Received , PLM</x:t>
         </x:is>
       </x:c>
       <x:c r="D14" t="inlineStr" s="9">
         <x:is>
-          <x:t>587248489</x:t>
+          <x:t>586982846</x:t>
         </x:is>
       </x:c>
       <x:c r="E14" t="inlineStr" s="11">
         <x:is>
-          <x:t>587248489</x:t>
+          <x:t>586982846</x:t>
         </x:is>
       </x:c>
       <x:c r="F14" s="13">
@@ -844,7 +844,7 @@
       </x:c>
       <x:c r="G14" t="inlineStr" s="15">
         <x:is>
-          <x:t>Justin Greene</x:t>
+          <x:t>Rickey McClam </x:t>
         </x:is>
       </x:c>
       <x:c r="H14" t="inlineStr" s="17">
@@ -854,19 +854,19 @@
       </x:c>
       <x:c r="I14" t="inlineStr" s="19">
         <x:is>
-          <x:t>CS - HVAC - Service - 12</x:t>
+          <x:t>PLM - HVAC - Service - 12</x:t>
         </x:is>
       </x:c>
       <x:c r="J14" t="inlineStr" s="21">
         <x:is>
-          <x:t>Baldwin Burey</x:t>
+          <x:t>Gwyn Bonasoro</x:t>
         </x:is>
       </x:c>
       <x:c r="K14" s="23">
-        <x:v>46105</x:v>
+        <x:v>46101</x:v>
       </x:c>
       <x:c r="L14" s="25">
-        <x:v>46105</x:v>
+        <x:v>46101</x:v>
       </x:c>
     </x:row>
     <x:row r="15">
@@ -876,51 +876,51 @@
         </x:is>
       </x:c>
       <x:c r="B15" t="n" s="5">
-        <x:v>225</x:v>
+        <x:v>689.97</x:v>
       </x:c>
       <x:c r="C15" t="inlineStr" s="7">
         <x:is>
-          <x:t>12-Year Labor, 12-Year Labor, 12-Year Labor, 12-Year Labor, 12-Year Labor, Carrier enterprise, Club Member 2 sys , MULTI- 2, Parts Received , PLM</x:t>
+          <x:t>2-YR Labor Warranty, 2-YR Labor Warranty, 2-YR Labor Warranty, Club Member, Gemaire, Parts Received </x:t>
         </x:is>
       </x:c>
       <x:c r="D15" t="inlineStr" s="9">
         <x:is>
-          <x:t>586903562</x:t>
+          <x:t>587253199</x:t>
         </x:is>
       </x:c>
       <x:c r="E15" t="inlineStr" s="11">
         <x:is>
-          <x:t>586903562</x:t>
+          <x:t>587253199</x:t>
         </x:is>
       </x:c>
       <x:c r="F15" s="13">
+        <x:v>46106</x:v>
+      </x:c>
+      <x:c r="G15" t="inlineStr" s="15">
+        <x:is>
+          <x:t>PP Barrington Wilson</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="H15" t="inlineStr" s="17">
+        <x:is>
+          <x:t>Hold</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="I15" t="inlineStr" s="19">
+        <x:is>
+          <x:t>CS - HVAC - Service - 12</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="J15" t="inlineStr" s="21">
+        <x:is>
+          <x:t>Dane Lyons</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="K15" s="23">
         <x:v>46105</x:v>
       </x:c>
-      <x:c r="G15" t="inlineStr" s="15">
-        <x:is>
-          <x:t>PP Braxton Patterson </x:t>
-        </x:is>
-      </x:c>
-      <x:c r="H15" t="inlineStr" s="17">
-        <x:is>
-          <x:t>Hold</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="I15" t="inlineStr" s="19">
-        <x:is>
-          <x:t>CS - HVAC - Service - 12</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="J15" t="inlineStr" s="21">
-        <x:is>
-          <x:t>Ruth  Hochberg</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="K15" s="23">
-        <x:v>46100</x:v>
-      </x:c>
       <x:c r="L15" s="25">
-        <x:v>46100</x:v>
+        <x:v>46105</x:v>
       </x:c>
     </x:row>
     <x:row r="16">
@@ -930,29 +930,29 @@
         </x:is>
       </x:c>
       <x:c r="B16" t="n" s="5">
-        <x:v>0</x:v>
+        <x:v>722.79</x:v>
       </x:c>
       <x:c r="C16" t="inlineStr" s="7">
         <x:is>
-          <x:t>10-10-10, 10-10-10, Carrier enterprise, Club Member, Parts Received , PLM</x:t>
+          <x:t>Baker Supply, Parts Ordered, PLM, Potential Member</x:t>
         </x:is>
       </x:c>
       <x:c r="D16" t="inlineStr" s="9">
         <x:is>
-          <x:t>586982846</x:t>
+          <x:t>459781920</x:t>
         </x:is>
       </x:c>
       <x:c r="E16" t="inlineStr" s="11">
         <x:is>
-          <x:t>586982846</x:t>
+          <x:t>459781920</x:t>
         </x:is>
       </x:c>
       <x:c r="F16" s="13">
-        <x:v>46105</x:v>
+        <x:v>46106</x:v>
       </x:c>
       <x:c r="G16" t="inlineStr" s="15">
         <x:is>
-          <x:t>Rickey McClam </x:t>
+          <x:t>PLM-Quentin Stewart</x:t>
         </x:is>
       </x:c>
       <x:c r="H16" t="inlineStr" s="17">
@@ -967,14 +967,14 @@
       </x:c>
       <x:c r="J16" t="inlineStr" s="21">
         <x:is>
-          <x:t>Gwyn Bonasoro</x:t>
+          <x:t>Gluck Carolyn</x:t>
         </x:is>
       </x:c>
       <x:c r="K16" s="23">
-        <x:v>46101</x:v>
+        <x:v>45726</x:v>
       </x:c>
       <x:c r="L16" s="25">
-        <x:v>46101</x:v>
+        <x:v>45726</x:v>
       </x:c>
     </x:row>
     <x:row r="17">
@@ -984,29 +984,29 @@
         </x:is>
       </x:c>
       <x:c r="B17" t="n" s="5">
-        <x:v>689.97</x:v>
+        <x:v>3247.45</x:v>
       </x:c>
       <x:c r="C17" t="inlineStr" s="7">
         <x:is>
-          <x:t>2-YR Labor Warranty, 2-YR Labor Warranty, 2-YR Labor Warranty, Club Member, Gemaire, Parts Received </x:t>
+          <x:t>10-Year Labor, Club Member, Club Member 2 sys , Gemaire, Parts Received , PLM</x:t>
         </x:is>
       </x:c>
       <x:c r="D17" t="inlineStr" s="9">
         <x:is>
-          <x:t>587253199</x:t>
+          <x:t>587314216</x:t>
         </x:is>
       </x:c>
       <x:c r="E17" t="inlineStr" s="11">
         <x:is>
-          <x:t>587253199</x:t>
+          <x:t>587314216</x:t>
         </x:is>
       </x:c>
       <x:c r="F17" s="13">
-        <x:v>46106</x:v>
+        <x:v>46107</x:v>
       </x:c>
       <x:c r="G17" t="inlineStr" s="15">
         <x:is>
-          <x:t>PP Barrington Wilson</x:t>
+          <x:t>Rolin Moimeme</x:t>
         </x:is>
       </x:c>
       <x:c r="H17" t="inlineStr" s="17">
@@ -1021,7 +1021,7 @@
       </x:c>
       <x:c r="J17" t="inlineStr" s="21">
         <x:is>
-          <x:t>Dane Lyons</x:t>
+          <x:t>FRIEDMAN, SAMANTHA</x:t>
         </x:is>
       </x:c>
       <x:c r="K17" s="23">
@@ -1038,51 +1038,51 @@
         </x:is>
       </x:c>
       <x:c r="B18" t="n" s="5">
-        <x:v>722.79</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="C18" t="inlineStr" s="7">
         <x:is>
-          <x:t>Baker Supply, Parts Ordered, PLM, Potential Member</x:t>
+          <x:t>Club Member, Gemaire, Parts Received </x:t>
         </x:is>
       </x:c>
       <x:c r="D18" t="inlineStr" s="9">
         <x:is>
-          <x:t>459781920</x:t>
+          <x:t>587448096</x:t>
         </x:is>
       </x:c>
       <x:c r="E18" t="inlineStr" s="11">
         <x:is>
-          <x:t>459781920</x:t>
+          <x:t>587448096</x:t>
         </x:is>
       </x:c>
       <x:c r="F18" s="13">
+        <x:v>46108</x:v>
+      </x:c>
+      <x:c r="G18" t="inlineStr" s="15">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+      <x:c r="H18" t="inlineStr" s="17">
+        <x:is>
+          <x:t>Hold</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="I18" t="inlineStr" s="19">
+        <x:is>
+          <x:t>PLM - HVAC - Service - 12</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="J18" t="inlineStr" s="21">
+        <x:is>
+          <x:t>Cassandra Sexton</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="K18" s="23">
         <x:v>46106</x:v>
       </x:c>
-      <x:c r="G18" t="inlineStr" s="15">
-        <x:is>
-          <x:t>PLM-Quentin Stewart</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="H18" t="inlineStr" s="17">
-        <x:is>
-          <x:t>Hold</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="I18" t="inlineStr" s="19">
-        <x:is>
-          <x:t>PLM - HVAC - Service - 12</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="J18" t="inlineStr" s="21">
-        <x:is>
-          <x:t>Gluck Carolyn</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="K18" s="23">
-        <x:v>45726</x:v>
-      </x:c>
       <x:c r="L18" s="25">
-        <x:v>45726</x:v>
+        <x:v>46106</x:v>
       </x:c>
     </x:row>
     <x:row r="19">
@@ -1092,29 +1092,29 @@
         </x:is>
       </x:c>
       <x:c r="B19" t="n" s="5">
-        <x:v>294.96</x:v>
+        <x:v>708.54</x:v>
       </x:c>
       <x:c r="C19" t="inlineStr" s="7">
         <x:is>
-          <x:t>10-10-10, 10-10-10, Club Member, Club Member (Additional System), MULTI- 2, Parts Ordered, Trane Supply</x:t>
+          <x:t>10-10-10, 10-10-10, 10-10-10, 10-10-10, Club Member, Need to order part (NTO)</x:t>
         </x:is>
       </x:c>
       <x:c r="D19" t="inlineStr" s="9">
         <x:is>
-          <x:t>554624809</x:t>
+          <x:t>587676974</x:t>
         </x:is>
       </x:c>
       <x:c r="E19" t="inlineStr" s="11">
         <x:is>
-          <x:t>554624809</x:t>
+          <x:t>587676974</x:t>
         </x:is>
       </x:c>
       <x:c r="F19" s="13">
-        <x:v>46107</x:v>
+        <x:v>46108</x:v>
       </x:c>
       <x:c r="G19" t="inlineStr" s="15">
         <x:is>
-          <x:t>PP Carlos Machado</x:t>
+          <x:t>Rolin Moimeme</x:t>
         </x:is>
       </x:c>
       <x:c r="H19" t="inlineStr" s="17">
@@ -1129,14 +1129,14 @@
       </x:c>
       <x:c r="J19" t="inlineStr" s="21">
         <x:is>
-          <x:t>Michael &amp; Delle Lenzen</x:t>
+          <x:t>Teresa &amp; Joe Perez</x:t>
         </x:is>
       </x:c>
       <x:c r="K19" s="23">
-        <x:v>45996</x:v>
+        <x:v>46108</x:v>
       </x:c>
       <x:c r="L19" s="25">
-        <x:v>45996</x:v>
+        <x:v>46108</x:v>
       </x:c>
     </x:row>
     <x:row r="20">
@@ -1146,29 +1146,29 @@
         </x:is>
       </x:c>
       <x:c r="B20" t="n" s="5">
-        <x:v>3247.45</x:v>
+        <x:v>292.95</x:v>
       </x:c>
       <x:c r="C20" t="inlineStr" s="7">
         <x:is>
-          <x:t>10-Year Labor, Club Member, Club Member 2 sys , Gemaire, Parts Received , PLM</x:t>
+          <x:t>Baker Supply, Club Member, Parts Received , PLM</x:t>
         </x:is>
       </x:c>
       <x:c r="D20" t="inlineStr" s="9">
         <x:is>
-          <x:t>587314216</x:t>
+          <x:t>587301961</x:t>
         </x:is>
       </x:c>
       <x:c r="E20" t="inlineStr" s="11">
         <x:is>
-          <x:t>587314216</x:t>
+          <x:t>587301961</x:t>
         </x:is>
       </x:c>
       <x:c r="F20" s="13">
-        <x:v>46107</x:v>
+        <x:v>46108</x:v>
       </x:c>
       <x:c r="G20" t="inlineStr" s="15">
         <x:is>
-          <x:t>Rolin Moimeme</x:t>
+          <x:t>Jesse Dague</x:t>
         </x:is>
       </x:c>
       <x:c r="H20" t="inlineStr" s="17">
@@ -1183,7 +1183,7 @@
       </x:c>
       <x:c r="J20" t="inlineStr" s="21">
         <x:is>
-          <x:t>FRIEDMAN, SAMANTHA</x:t>
+          <x:t>Lera Chacon</x:t>
         </x:is>
       </x:c>
       <x:c r="K20" s="23">
@@ -1204,17 +1204,17 @@
       </x:c>
       <x:c r="C21" t="inlineStr" s="7">
         <x:is>
-          <x:t>Club Member, Gemaire, Parts Received </x:t>
+          <x:t>10-Year Labor, 10-Year Labor, 10-Year Labor, 10-Year Labor, 10-Year Labor, Club Member, Goodman distribution , Parts Ordered</x:t>
         </x:is>
       </x:c>
       <x:c r="D21" t="inlineStr" s="9">
         <x:is>
-          <x:t>587448096</x:t>
+          <x:t>585388429</x:t>
         </x:is>
       </x:c>
       <x:c r="E21" t="inlineStr" s="11">
         <x:is>
-          <x:t>587448096</x:t>
+          <x:t>585388429</x:t>
         </x:is>
       </x:c>
       <x:c r="F21" s="13">
@@ -1222,7 +1222,7 @@
       </x:c>
       <x:c r="G21" t="inlineStr" s="15">
         <x:is>
-          <x:t/>
+          <x:t>Rickey McClam </x:t>
         </x:is>
       </x:c>
       <x:c r="H21" t="inlineStr" s="17">
@@ -1232,19 +1232,19 @@
       </x:c>
       <x:c r="I21" t="inlineStr" s="19">
         <x:is>
-          <x:t>PLM - HVAC - Service - 12</x:t>
+          <x:t>CS - HVAC - Service - 12</x:t>
         </x:is>
       </x:c>
       <x:c r="J21" t="inlineStr" s="21">
         <x:is>
-          <x:t>Cassandra Sexton</x:t>
+          <x:t>Charles Funkey</x:t>
         </x:is>
       </x:c>
       <x:c r="K21" s="23">
-        <x:v>46106</x:v>
+        <x:v>46086</x:v>
       </x:c>
       <x:c r="L21" s="25">
-        <x:v>46106</x:v>
+        <x:v>46086</x:v>
       </x:c>
     </x:row>
     <x:row r="22">
@@ -1254,21 +1254,21 @@
         </x:is>
       </x:c>
       <x:c r="B22" t="n" s="5">
-        <x:v>710.85</x:v>
+        <x:v>2125</x:v>
       </x:c>
       <x:c r="C22" t="inlineStr" s="7">
         <x:is>
-          <x:t>10-10-10, Club Member, Parts Ordered</x:t>
+          <x:t>Carrier enterprise, Parts Received , Potential Member</x:t>
         </x:is>
       </x:c>
       <x:c r="D22" t="inlineStr" s="9">
         <x:is>
-          <x:t>587680855</x:t>
+          <x:t>587416074</x:t>
         </x:is>
       </x:c>
       <x:c r="E22" t="inlineStr" s="11">
         <x:is>
-          <x:t>587680855</x:t>
+          <x:t>587416074</x:t>
         </x:is>
       </x:c>
       <x:c r="F22" s="13">
@@ -1276,7 +1276,7 @@
       </x:c>
       <x:c r="G22" t="inlineStr" s="15">
         <x:is>
-          <x:t>PP Martin Ebanks</x:t>
+          <x:t>PP Michael Chenoy</x:t>
         </x:is>
       </x:c>
       <x:c r="H22" t="inlineStr" s="17">
@@ -1286,19 +1286,19 @@
       </x:c>
       <x:c r="I22" t="inlineStr" s="19">
         <x:is>
-          <x:t>CS - HVAC - Service - 12</x:t>
+          <x:t>PLM - HVAC - Service - 12</x:t>
         </x:is>
       </x:c>
       <x:c r="J22" t="inlineStr" s="21">
         <x:is>
-          <x:t>Lester  Mena</x:t>
+          <x:t>Jian Jia </x:t>
         </x:is>
       </x:c>
       <x:c r="K22" s="23">
-        <x:v>46108</x:v>
+        <x:v>46106</x:v>
       </x:c>
       <x:c r="L22" s="25">
-        <x:v>46108</x:v>
+        <x:v>46106</x:v>
       </x:c>
     </x:row>
     <x:row r="23">
@@ -1308,29 +1308,29 @@
         </x:is>
       </x:c>
       <x:c r="B23" t="n" s="5">
-        <x:v>708.54</x:v>
+        <x:v>2295.35</x:v>
       </x:c>
       <x:c r="C23" t="inlineStr" s="7">
         <x:is>
-          <x:t>10-10-10, 10-10-10, 10-10-10, 10-10-10, Club Member, Need to order part (NTO)</x:t>
+          <x:t>Club Member 3 sys, Need to order part (NTO)</x:t>
         </x:is>
       </x:c>
       <x:c r="D23" t="inlineStr" s="9">
         <x:is>
-          <x:t>587676974</x:t>
+          <x:t>587732375</x:t>
         </x:is>
       </x:c>
       <x:c r="E23" t="inlineStr" s="11">
         <x:is>
-          <x:t>587676974</x:t>
+          <x:t>587732375</x:t>
         </x:is>
       </x:c>
       <x:c r="F23" s="13">
-        <x:v>46108</x:v>
+        <x:v>46109</x:v>
       </x:c>
       <x:c r="G23" t="inlineStr" s="15">
         <x:is>
-          <x:t>Rolin Moimeme</x:t>
+          <x:t>PP Gurpreet Parihar</x:t>
         </x:is>
       </x:c>
       <x:c r="H23" t="inlineStr" s="17">
@@ -1345,7 +1345,7 @@
       </x:c>
       <x:c r="J23" t="inlineStr" s="21">
         <x:is>
-          <x:t>Teresa &amp; Joe Perez</x:t>
+          <x:t>Mandelbaum, Shelly 0201146</x:t>
         </x:is>
       </x:c>
       <x:c r="K23" s="23">
@@ -1362,51 +1362,51 @@
         </x:is>
       </x:c>
       <x:c r="B24" t="n" s="5">
-        <x:v>1248.8</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="C24" t="inlineStr" s="7">
         <x:is>
-          <x:t>Club Member, Lennox Supply, Parts Received </x:t>
+          <x:t>10-Year Labor, 10-Year Labor, 10-Year Labor, 10-Year Labor, 10-Year Labor, Costco Estimate, Parts Received , Potential Member</x:t>
         </x:is>
       </x:c>
       <x:c r="D24" t="inlineStr" s="9">
         <x:is>
-          <x:t>587303898</x:t>
+          <x:t>587732523</x:t>
         </x:is>
       </x:c>
       <x:c r="E24" t="inlineStr" s="11">
         <x:is>
-          <x:t>587303898</x:t>
+          <x:t>587732523</x:t>
         </x:is>
       </x:c>
       <x:c r="F24" s="13">
+        <x:v>46109</x:v>
+      </x:c>
+      <x:c r="G24" t="inlineStr" s="15">
+        <x:is>
+          <x:t>Bruce Coe</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="H24" t="inlineStr" s="17">
+        <x:is>
+          <x:t>Hold</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="I24" t="inlineStr" s="19">
+        <x:is>
+          <x:t>CS - HVAC - Service - 12</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="J24" t="inlineStr" s="21">
+        <x:is>
+          <x:t>Chris Madzi</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="K24" s="23">
         <x:v>46108</x:v>
       </x:c>
-      <x:c r="G24" t="inlineStr" s="15">
-        <x:is>
-          <x:t>Xavier Mateo</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="H24" t="inlineStr" s="17">
-        <x:is>
-          <x:t>Hold</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="I24" t="inlineStr" s="19">
-        <x:is>
-          <x:t>CS - HVAC - Service - 12</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="J24" t="inlineStr" s="21">
-        <x:is>
-          <x:t>ROBERT MCCABE</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="K24" s="23">
-        <x:v>46105</x:v>
-      </x:c>
       <x:c r="L24" s="25">
-        <x:v>46105</x:v>
+        <x:v>46108</x:v>
       </x:c>
     </x:row>
     <x:row r="25">
@@ -1416,29 +1416,29 @@
         </x:is>
       </x:c>
       <x:c r="B25" t="n" s="5">
-        <x:v>1267.95</x:v>
+        <x:v>436.28</x:v>
       </x:c>
       <x:c r="C25" t="inlineStr" s="7">
         <x:is>
-          <x:t>Club Member 3 sys, Gemaire, Parts Received </x:t>
+          <x:t>10-10-10, 10-10-10, 10-10-10, 10-10-10, Need to order part (NTO), Potential Member</x:t>
         </x:is>
       </x:c>
       <x:c r="D25" t="inlineStr" s="9">
         <x:is>
-          <x:t>578585007</x:t>
+          <x:t>587789767</x:t>
         </x:is>
       </x:c>
       <x:c r="E25" t="inlineStr" s="11">
         <x:is>
-          <x:t>578585007</x:t>
+          <x:t>587789767</x:t>
         </x:is>
       </x:c>
       <x:c r="F25" s="13">
-        <x:v>46108</x:v>
+        <x:v>46110</x:v>
       </x:c>
       <x:c r="G25" t="inlineStr" s="15">
         <x:is>
-          <x:t>PP Cesar Levy</x:t>
+          <x:t>Tyler Gallatin</x:t>
         </x:is>
       </x:c>
       <x:c r="H25" t="inlineStr" s="17">
@@ -1453,14 +1453,14 @@
       </x:c>
       <x:c r="J25" t="inlineStr" s="21">
         <x:is>
-          <x:t>Serghei Arsentiev</x:t>
+          <x:t>Angelina DeCerbo</x:t>
         </x:is>
       </x:c>
       <x:c r="K25" s="23">
-        <x:v>46037</x:v>
+        <x:v>46110</x:v>
       </x:c>
       <x:c r="L25" s="25">
-        <x:v>46037</x:v>
+        <x:v>46110</x:v>
       </x:c>
     </x:row>
     <x:row r="26">
@@ -1470,29 +1470,29 @@
         </x:is>
       </x:c>
       <x:c r="B26" t="n" s="5">
-        <x:v>0</x:v>
+        <x:v>1340.1</x:v>
       </x:c>
       <x:c r="C26" t="inlineStr" s="7">
         <x:is>
-          <x:t>Carrier enterprise, Parts Ordered, PLM, Potential Member</x:t>
+          <x:t>Club Member, Club Member (Additional System), MULTI- 3, Parts Received , PLM</x:t>
         </x:is>
       </x:c>
       <x:c r="D26" t="inlineStr" s="9">
         <x:is>
-          <x:t>583259145</x:t>
+          <x:t>587789529</x:t>
         </x:is>
       </x:c>
       <x:c r="E26" t="inlineStr" s="11">
         <x:is>
-          <x:t>583259145</x:t>
+          <x:t>587789529</x:t>
         </x:is>
       </x:c>
       <x:c r="F26" s="13">
-        <x:v>46108</x:v>
+        <x:v>46110</x:v>
       </x:c>
       <x:c r="G26" t="inlineStr" s="15">
         <x:is>
-          <x:t/>
+          <x:t>PP Tyriq McCall</x:t>
         </x:is>
       </x:c>
       <x:c r="H26" t="inlineStr" s="17">
@@ -1502,19 +1502,19 @@
       </x:c>
       <x:c r="I26" t="inlineStr" s="19">
         <x:is>
-          <x:t>CS - HVAC - Service - 12</x:t>
+          <x:t>PLM - HVAC - Service - 12</x:t>
         </x:is>
       </x:c>
       <x:c r="J26" t="inlineStr" s="21">
         <x:is>
-          <x:t>John Moore</x:t>
+          <x:t>Robert Lake</x:t>
         </x:is>
       </x:c>
       <x:c r="K26" s="23">
-        <x:v>46070</x:v>
+        <x:v>46110</x:v>
       </x:c>
       <x:c r="L26" s="25">
-        <x:v>46070</x:v>
+        <x:v>46110</x:v>
       </x:c>
     </x:row>
     <x:row r="27">
@@ -1524,29 +1524,29 @@
         </x:is>
       </x:c>
       <x:c r="B27" t="n" s="5">
-        <x:v>1605.6</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="C27" t="inlineStr" s="7">
         <x:is>
-          <x:t>Club Member, Club Member (Additional System), Parts Ordered, PLM</x:t>
+          <x:t>5 YEAR WARRANTY, 5 YEAR WARRANTY, 5 YEAR WARRANTY, 5 YEAR WARRANTY, 5 YEAR WARRANTY, 5 YEAR WARRANTY, Club Member 3 sys, Gemaire, MULTI- 3, Parts Ordered</x:t>
         </x:is>
       </x:c>
       <x:c r="D27" t="inlineStr" s="9">
         <x:is>
-          <x:t>587681974</x:t>
+          <x:t>586595677</x:t>
         </x:is>
       </x:c>
       <x:c r="E27" t="inlineStr" s="11">
         <x:is>
-          <x:t>587681974</x:t>
+          <x:t>586595677</x:t>
         </x:is>
       </x:c>
       <x:c r="F27" s="13">
-        <x:v>46108</x:v>
+        <x:v>46111</x:v>
       </x:c>
       <x:c r="G27" t="inlineStr" s="15">
         <x:is>
-          <x:t>PP Barrington Wilson</x:t>
+          <x:t>PP Alejandro Espinosa</x:t>
         </x:is>
       </x:c>
       <x:c r="H27" t="inlineStr" s="17">
@@ -1556,19 +1556,19 @@
       </x:c>
       <x:c r="I27" t="inlineStr" s="19">
         <x:is>
-          <x:t>CS - HVAC - Service - 12</x:t>
+          <x:t>PLM - HVAC - Service - 12</x:t>
         </x:is>
       </x:c>
       <x:c r="J27" t="inlineStr" s="21">
         <x:is>
-          <x:t>MACLACHLAN, DAN</x:t>
+          <x:t>Bob Lauson</x:t>
         </x:is>
       </x:c>
       <x:c r="K27" s="23">
-        <x:v>46108</x:v>
+        <x:v>46098</x:v>
       </x:c>
       <x:c r="L27" s="25">
-        <x:v>46108</x:v>
+        <x:v>46098</x:v>
       </x:c>
     </x:row>
     <x:row r="28">
@@ -1578,29 +1578,29 @@
         </x:is>
       </x:c>
       <x:c r="B28" t="n" s="5">
-        <x:v>292.95</x:v>
+        <x:v>462.83</x:v>
       </x:c>
       <x:c r="C28" t="inlineStr" s="7">
         <x:is>
-          <x:t>Baker Supply, Club Member, Parts Received , PLM</x:t>
+          <x:t>Baker Supply, Club Member, Parts Ordered, PLM, Potential Membership Renewal, Residential Maintenance Agreement</x:t>
         </x:is>
       </x:c>
       <x:c r="D28" t="inlineStr" s="9">
         <x:is>
-          <x:t>587301961</x:t>
+          <x:t>555552166</x:t>
         </x:is>
       </x:c>
       <x:c r="E28" t="inlineStr" s="11">
         <x:is>
-          <x:t>587301961</x:t>
+          <x:t>555552166</x:t>
         </x:is>
       </x:c>
       <x:c r="F28" s="13">
-        <x:v>46108</x:v>
+        <x:v>46111</x:v>
       </x:c>
       <x:c r="G28" t="inlineStr" s="15">
         <x:is>
-          <x:t>Jesse Dague</x:t>
+          <x:t>PP Cesar Levy</x:t>
         </x:is>
       </x:c>
       <x:c r="H28" t="inlineStr" s="17">
@@ -1610,19 +1610,19 @@
       </x:c>
       <x:c r="I28" t="inlineStr" s="19">
         <x:is>
-          <x:t>CS - HVAC - Service - 12</x:t>
+          <x:t>PLM - HVAC - Service - 12</x:t>
         </x:is>
       </x:c>
       <x:c r="J28" t="inlineStr" s="21">
         <x:is>
-          <x:t>Lera Chacon</x:t>
+          <x:t>Wanda Betancourt</x:t>
         </x:is>
       </x:c>
       <x:c r="K28" s="23">
-        <x:v>46105</x:v>
+        <x:v>46007</x:v>
       </x:c>
       <x:c r="L28" s="25">
-        <x:v>46105</x:v>
+        <x:v>46007</x:v>
       </x:c>
     </x:row>
     <x:row r="29">
@@ -1632,29 +1632,29 @@
         </x:is>
       </x:c>
       <x:c r="B29" t="n" s="5">
-        <x:v>2405.92</x:v>
+        <x:v>945.4</x:v>
       </x:c>
       <x:c r="C29" t="inlineStr" s="7">
         <x:is>
-          <x:t>Baker Supply, Parts Ordered, Potential Member</x:t>
+          <x:t>Carrier enterprise, Club Member, Parts Received , PLM</x:t>
         </x:is>
       </x:c>
       <x:c r="D29" t="inlineStr" s="9">
         <x:is>
-          <x:t>578394047</x:t>
+          <x:t>587403893</x:t>
         </x:is>
       </x:c>
       <x:c r="E29" t="inlineStr" s="11">
         <x:is>
-          <x:t>578394047</x:t>
+          <x:t>587403893</x:t>
         </x:is>
       </x:c>
       <x:c r="F29" s="13">
-        <x:v>46108</x:v>
+        <x:v>46111</x:v>
       </x:c>
       <x:c r="G29" t="inlineStr" s="15">
         <x:is>
-          <x:t>PP Gurpreet Parihar</x:t>
+          <x:t>Rolin Moimeme</x:t>
         </x:is>
       </x:c>
       <x:c r="H29" t="inlineStr" s="17">
@@ -1669,14 +1669,14 @@
       </x:c>
       <x:c r="J29" t="inlineStr" s="21">
         <x:is>
-          <x:t>Edgar Irving</x:t>
+          <x:t>WALKER, CAMERON</x:t>
         </x:is>
       </x:c>
       <x:c r="K29" s="23">
-        <x:v>46036</x:v>
+        <x:v>46106</x:v>
       </x:c>
       <x:c r="L29" s="25">
-        <x:v>46036</x:v>
+        <x:v>46106</x:v>
       </x:c>
     </x:row>
     <x:row r="30">
@@ -1686,51 +1686,51 @@
         </x:is>
       </x:c>
       <x:c r="B30" t="n" s="5">
-        <x:v>0</x:v>
+        <x:v>1605.6</x:v>
       </x:c>
       <x:c r="C30" t="inlineStr" s="7">
         <x:is>
-          <x:t>10-Year Labor, 10-Year Labor, 10-Year Labor, 10-Year Labor, 10-Year Labor, Club Member, Goodman distribution , Parts Ordered</x:t>
+          <x:t>Club Member, Club Member (Additional System), Parts Ordered, PLM</x:t>
         </x:is>
       </x:c>
       <x:c r="D30" t="inlineStr" s="9">
         <x:is>
-          <x:t>585388429</x:t>
+          <x:t>587681974</x:t>
         </x:is>
       </x:c>
       <x:c r="E30" t="inlineStr" s="11">
         <x:is>
-          <x:t>585388429</x:t>
+          <x:t>587681974</x:t>
         </x:is>
       </x:c>
       <x:c r="F30" s="13">
+        <x:v>46111</x:v>
+      </x:c>
+      <x:c r="G30" t="inlineStr" s="15">
+        <x:is>
+          <x:t>PP Barrington Wilson</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="H30" t="inlineStr" s="17">
+        <x:is>
+          <x:t>Hold</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="I30" t="inlineStr" s="19">
+        <x:is>
+          <x:t>CS - HVAC - Service - 12</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="J30" t="inlineStr" s="21">
+        <x:is>
+          <x:t>MACLACHLAN, DAN</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="K30" s="23">
         <x:v>46108</x:v>
       </x:c>
-      <x:c r="G30" t="inlineStr" s="15">
-        <x:is>
-          <x:t>Rickey McClam </x:t>
-        </x:is>
-      </x:c>
-      <x:c r="H30" t="inlineStr" s="17">
-        <x:is>
-          <x:t>Hold</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="I30" t="inlineStr" s="19">
-        <x:is>
-          <x:t>CS - HVAC - Service - 12</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="J30" t="inlineStr" s="21">
-        <x:is>
-          <x:t>Charles Funkey</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="K30" s="23">
-        <x:v>46086</x:v>
-      </x:c>
       <x:c r="L30" s="25">
-        <x:v>46086</x:v>
+        <x:v>46108</x:v>
       </x:c>
     </x:row>
     <x:row r="31">
@@ -1740,29 +1740,29 @@
         </x:is>
       </x:c>
       <x:c r="B31" t="n" s="5">
-        <x:v>2125</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="C31" t="inlineStr" s="7">
         <x:is>
-          <x:t>Carrier enterprise, Parts Received , Potential Member</x:t>
+          <x:t>Club Member, Gemaire, Parts Ordered</x:t>
         </x:is>
       </x:c>
       <x:c r="D31" t="inlineStr" s="9">
         <x:is>
-          <x:t>587416074</x:t>
+          <x:t>463016698</x:t>
         </x:is>
       </x:c>
       <x:c r="E31" t="inlineStr" s="11">
         <x:is>
-          <x:t>587416074</x:t>
+          <x:t>463016698</x:t>
         </x:is>
       </x:c>
       <x:c r="F31" s="13">
-        <x:v>46108</x:v>
+        <x:v>46111</x:v>
       </x:c>
       <x:c r="G31" t="inlineStr" s="15">
         <x:is>
-          <x:t>PP Michael Chenoy</x:t>
+          <x:t>PP Tyriq McCall</x:t>
         </x:is>
       </x:c>
       <x:c r="H31" t="inlineStr" s="17">
@@ -1772,19 +1772,19 @@
       </x:c>
       <x:c r="I31" t="inlineStr" s="19">
         <x:is>
-          <x:t>PLM - HVAC - Service - 12</x:t>
+          <x:t>CS - HVAC - Service - 12</x:t>
         </x:is>
       </x:c>
       <x:c r="J31" t="inlineStr" s="21">
         <x:is>
-          <x:t>Jian Jia </x:t>
+          <x:t>Evan Frangos</x:t>
         </x:is>
       </x:c>
       <x:c r="K31" s="23">
-        <x:v>46106</x:v>
+        <x:v>45762</x:v>
       </x:c>
       <x:c r="L31" s="25">
-        <x:v>46106</x:v>
+        <x:v>45762</x:v>
       </x:c>
     </x:row>
     <x:row r="32">
@@ -1794,29 +1794,29 @@
         </x:is>
       </x:c>
       <x:c r="B32" t="n" s="5">
-        <x:v>2418</x:v>
+        <x:v>303.45</x:v>
       </x:c>
       <x:c r="C32" t="inlineStr" s="7">
         <x:is>
-          <x:t>Need to order part (NTO), Potential Member, Replacement Opportunity</x:t>
+          <x:t>Carrier enterprise, Parts Ordered, Potential Member</x:t>
         </x:is>
       </x:c>
       <x:c r="D32" t="inlineStr" s="9">
         <x:is>
-          <x:t>587767849</x:t>
+          <x:t>581332764</x:t>
         </x:is>
       </x:c>
       <x:c r="E32" t="inlineStr" s="11">
         <x:is>
-          <x:t>587767849</x:t>
+          <x:t>581332764</x:t>
         </x:is>
       </x:c>
       <x:c r="F32" s="13">
-        <x:v>46109</x:v>
+        <x:v>46111</x:v>
       </x:c>
       <x:c r="G32" t="inlineStr" s="15">
         <x:is>
-          <x:t>Michael Donnauro</x:t>
+          <x:t>Justin Greene</x:t>
         </x:is>
       </x:c>
       <x:c r="H32" t="inlineStr" s="17">
@@ -1831,14 +1831,14 @@
       </x:c>
       <x:c r="J32" t="inlineStr" s="21">
         <x:is>
-          <x:t>Diomicira Zecchino</x:t>
+          <x:t>Chris Orsini</x:t>
         </x:is>
       </x:c>
       <x:c r="K32" s="23">
-        <x:v>46109</x:v>
+        <x:v>46057</x:v>
       </x:c>
       <x:c r="L32" s="25">
-        <x:v>46109</x:v>
+        <x:v>46057</x:v>
       </x:c>
     </x:row>
     <x:row r="33">
@@ -1848,29 +1848,29 @@
         </x:is>
       </x:c>
       <x:c r="B33" t="n" s="5">
-        <x:v>579.81</x:v>
+        <x:v>828.5</x:v>
       </x:c>
       <x:c r="C33" t="inlineStr" s="7">
         <x:is>
-          <x:t>Club Member, Need to order part (NTO), Replacement Opportunity</x:t>
+          <x:t>Dan$, Need to order part (NTO), Potential Member</x:t>
         </x:is>
       </x:c>
       <x:c r="D33" t="inlineStr" s="9">
         <x:is>
-          <x:t>587764352</x:t>
+          <x:t>587820789</x:t>
         </x:is>
       </x:c>
       <x:c r="E33" t="inlineStr" s="11">
         <x:is>
-          <x:t>587764352</x:t>
+          <x:t>587820789</x:t>
         </x:is>
       </x:c>
       <x:c r="F33" s="13">
-        <x:v>46109</x:v>
+        <x:v>46111</x:v>
       </x:c>
       <x:c r="G33" t="inlineStr" s="15">
         <x:is>
-          <x:t>PP Barrington Wilson</x:t>
+          <x:t>Chris Johnson</x:t>
         </x:is>
       </x:c>
       <x:c r="H33" t="inlineStr" s="17">
@@ -1880,932 +1880,68 @@
       </x:c>
       <x:c r="I33" t="inlineStr" s="19">
         <x:is>
-          <x:t>CS - HVAC - Service - 12</x:t>
+          <x:t>PLM - HVAC - Service - 12</x:t>
         </x:is>
       </x:c>
       <x:c r="J33" t="inlineStr" s="21">
         <x:is>
-          <x:t>Edna Parkin</x:t>
+          <x:t>Joe Buck</x:t>
         </x:is>
       </x:c>
       <x:c r="K33" s="23">
-        <x:v>46109</x:v>
+        <x:v>46111</x:v>
       </x:c>
       <x:c r="L33" s="25">
-        <x:v>46109</x:v>
+        <x:v>46111</x:v>
       </x:c>
     </x:row>
     <x:row r="34">
-      <x:c r="A34" t="inlineStr" s="3">
-        <x:is>
-          <x:t>HC - Return to Repair</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B34" t="n" s="5">
-        <x:v>810.22</x:v>
-      </x:c>
-      <x:c r="C34" t="inlineStr" s="7">
-        <x:is>
-          <x:t>Club Member, Need to order part (NTO)</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D34" t="inlineStr" s="9">
-        <x:is>
-          <x:t>587761129</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="E34" t="inlineStr" s="11">
-        <x:is>
-          <x:t>587761129</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="F34" s="13">
-        <x:v>46109</x:v>
-      </x:c>
-      <x:c r="G34" t="inlineStr" s="15">
-        <x:is>
-          <x:t>Rolin Moimeme</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="H34" t="inlineStr" s="17">
-        <x:is>
-          <x:t>Hold</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="I34" t="inlineStr" s="19">
-        <x:is>
-          <x:t>PLM - HVAC - Service - 12</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="J34" t="inlineStr" s="21">
-        <x:is>
-          <x:t>Nancy Brown</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="K34" s="23">
-        <x:v>46109</x:v>
-      </x:c>
-      <x:c r="L34" s="25">
-        <x:v>46109</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="35">
-      <x:c r="A35" t="inlineStr" s="3">
-        <x:is>
-          <x:t>HC - Return to Repair</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B35" t="n" s="5">
-        <x:v>2022</x:v>
-      </x:c>
-      <x:c r="C35" t="inlineStr" s="7">
-        <x:is>
-          <x:t>Need to order part (NTO), Potential Member</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D35" t="inlineStr" s="9">
-        <x:is>
-          <x:t>587751042</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="E35" t="inlineStr" s="11">
-        <x:is>
-          <x:t>587751042</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="F35" s="13">
-        <x:v>46109</x:v>
-      </x:c>
-      <x:c r="G35" t="inlineStr" s="15">
-        <x:is>
-          <x:t>Rickey McClam </x:t>
-        </x:is>
-      </x:c>
-      <x:c r="H35" t="inlineStr" s="17">
-        <x:is>
-          <x:t>Hold</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="I35" t="inlineStr" s="19">
-        <x:is>
-          <x:t>PLM - HVAC - Service - 12</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="J35" t="inlineStr" s="21">
-        <x:is>
-          <x:t>Andy Ong</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="K35" s="23">
-        <x:v>46109</x:v>
-      </x:c>
-      <x:c r="L35" s="25">
-        <x:v>46109</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="36">
-      <x:c r="A36" t="inlineStr" s="3">
-        <x:is>
-          <x:t>HC - Return to Repair</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B36" t="n" s="5">
-        <x:v>2295.35</x:v>
-      </x:c>
-      <x:c r="C36" t="inlineStr" s="7">
-        <x:is>
-          <x:t>Club Member 3 sys, Need to order part (NTO)</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D36" t="inlineStr" s="9">
-        <x:is>
-          <x:t>587732375</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="E36" t="inlineStr" s="11">
-        <x:is>
-          <x:t>587732375</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="F36" s="13">
-        <x:v>46109</x:v>
-      </x:c>
-      <x:c r="G36" t="inlineStr" s="15">
-        <x:is>
-          <x:t>PP Gurpreet Parihar</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="H36" t="inlineStr" s="17">
-        <x:is>
-          <x:t>Hold</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="I36" t="inlineStr" s="19">
-        <x:is>
-          <x:t>CS - HVAC - Service - 12</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="J36" t="inlineStr" s="21">
-        <x:is>
-          <x:t>Mandelbaum, Shelly 0201146</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="K36" s="23">
-        <x:v>46108</x:v>
-      </x:c>
-      <x:c r="L36" s="25">
-        <x:v>46108</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="37">
-      <x:c r="A37" t="inlineStr" s="3">
-        <x:is>
-          <x:t>HC - Return to Repair</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B37" t="n" s="5">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="C37" t="inlineStr" s="7">
-        <x:is>
-          <x:t>10-Year Labor, 10-Year Labor, 10-Year Labor, 10-Year Labor, 10-Year Labor, Costco Estimate, Need to order part (NTO), Potential Member</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D37" t="inlineStr" s="9">
-        <x:is>
-          <x:t>587732523</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="E37" t="inlineStr" s="11">
-        <x:is>
-          <x:t>587732523</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="F37" s="13">
-        <x:v>46109</x:v>
-      </x:c>
-      <x:c r="G37" t="inlineStr" s="15">
-        <x:is>
-          <x:t>Bruce Coe</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="H37" t="inlineStr" s="17">
-        <x:is>
-          <x:t>Hold</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="I37" t="inlineStr" s="19">
-        <x:is>
-          <x:t>CS - HVAC - Service - 12</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="J37" t="inlineStr" s="21">
-        <x:is>
-          <x:t>Chris Madzi</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="K37" s="23">
-        <x:v>46108</x:v>
-      </x:c>
-      <x:c r="L37" s="25">
-        <x:v>46108</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="38">
-      <x:c r="A38" t="inlineStr" s="3">
-        <x:is>
-          <x:t>HC - Return to Repair</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B38" t="n" s="5">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="C38" t="inlineStr" s="7">
-        <x:is>
-          <x:t>10-10-10, Club Member, Need to order part (NTO), NO AIR</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D38" t="inlineStr" s="9">
-        <x:is>
-          <x:t>587794613</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="E38" t="inlineStr" s="11">
-        <x:is>
-          <x:t>587794613</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="F38" s="13">
-        <x:v>46110</x:v>
-      </x:c>
-      <x:c r="G38" t="inlineStr" s="15">
-        <x:is>
-          <x:t>PP Cesar Levy</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="H38" t="inlineStr" s="17">
-        <x:is>
-          <x:t>Hold</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="I38" t="inlineStr" s="19">
-        <x:is>
-          <x:t>CS - HVAC - Service - 12</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="J38" t="inlineStr" s="21">
-        <x:is>
-          <x:t>Rene Ceusters</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="K38" s="23">
-        <x:v>46110</x:v>
-      </x:c>
-      <x:c r="L38" s="25">
-        <x:v>46110</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="39">
-      <x:c r="A39" t="inlineStr" s="3">
-        <x:is>
-          <x:t>HC - Return to Repair</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B39" t="n" s="5">
-        <x:v>436.28</x:v>
-      </x:c>
-      <x:c r="C39" t="inlineStr" s="7">
-        <x:is>
-          <x:t>10-10-10, 10-10-10, 10-10-10, 10-10-10, Need to order part (NTO), Potential Member</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D39" t="inlineStr" s="9">
-        <x:is>
-          <x:t>587789767</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="E39" t="inlineStr" s="11">
-        <x:is>
-          <x:t>587789767</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="F39" s="13">
-        <x:v>46110</x:v>
-      </x:c>
-      <x:c r="G39" t="inlineStr" s="15">
-        <x:is>
-          <x:t>Tyler Gallatin</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="H39" t="inlineStr" s="17">
-        <x:is>
-          <x:t>Hold</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="I39" t="inlineStr" s="19">
-        <x:is>
-          <x:t>CS - HVAC - Service - 12</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="J39" t="inlineStr" s="21">
-        <x:is>
-          <x:t>Angelina DeCerbo</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="K39" s="23">
-        <x:v>46110</x:v>
-      </x:c>
-      <x:c r="L39" s="25">
-        <x:v>46110</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="40">
-      <x:c r="A40" t="inlineStr" s="3">
-        <x:is>
-          <x:t>HC - Return to Repair</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B40" t="n" s="5">
-        <x:v>1883</x:v>
-      </x:c>
-      <x:c r="C40" t="inlineStr" s="7">
-        <x:is>
-          <x:t>Need to order part (NTO), NO AIR, PLM, Potential Member</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D40" t="inlineStr" s="9">
-        <x:is>
-          <x:t>587796621</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="E40" t="inlineStr" s="11">
-        <x:is>
-          <x:t>587796621</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="F40" s="13">
-        <x:v>46110</x:v>
-      </x:c>
-      <x:c r="G40" t="inlineStr" s="15">
-        <x:is>
-          <x:t>Jesse Dague</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="H40" t="inlineStr" s="17">
-        <x:is>
-          <x:t>Hold</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="I40" t="inlineStr" s="19">
-        <x:is>
-          <x:t>PLM - HVAC - Service - 12</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="J40" t="inlineStr" s="21">
-        <x:is>
-          <x:t>BONCZEK, TIM</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="K40" s="23">
-        <x:v>46110</x:v>
-      </x:c>
-      <x:c r="L40" s="25">
-        <x:v>46110</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="41">
-      <x:c r="A41" t="inlineStr" s="3">
-        <x:is>
-          <x:t>HC - Return to Repair</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B41" t="n" s="5">
-        <x:v>1340.1</x:v>
-      </x:c>
-      <x:c r="C41" t="inlineStr" s="7">
-        <x:is>
-          <x:t>Club Member, Club Member (Additional System), MULTI- 3, Need to order part (NTO), PLM</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D41" t="inlineStr" s="9">
-        <x:is>
-          <x:t>587789529</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="E41" t="inlineStr" s="11">
-        <x:is>
-          <x:t>587789529</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="F41" s="13">
-        <x:v>46110</x:v>
-      </x:c>
-      <x:c r="G41" t="inlineStr" s="15">
-        <x:is>
-          <x:t>PP Tyriq McCall</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="H41" t="inlineStr" s="17">
-        <x:is>
-          <x:t>Hold</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="I41" t="inlineStr" s="19">
-        <x:is>
-          <x:t>PLM - HVAC - Service - 12</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="J41" t="inlineStr" s="21">
-        <x:is>
-          <x:t>Robert Lake</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="K41" s="23">
-        <x:v>46110</x:v>
-      </x:c>
-      <x:c r="L41" s="25">
-        <x:v>46110</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="42">
-      <x:c r="A42" t="inlineStr" s="3">
-        <x:is>
-          <x:t>HC - Return to Repair</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B42" t="n" s="5">
-        <x:v>530</x:v>
-      </x:c>
-      <x:c r="C42" t="inlineStr" s="7">
-        <x:is>
-          <x:t>Club Member 3 sys, MULTI- 3, Need to order part (NTO), PLM, Replacement Opportunity</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D42" t="inlineStr" s="9">
-        <x:is>
-          <x:t>587789020</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="E42" t="inlineStr" s="11">
-        <x:is>
-          <x:t>587789020</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="F42" s="13">
-        <x:v>46110</x:v>
-      </x:c>
-      <x:c r="G42" t="inlineStr" s="15">
-        <x:is>
-          <x:t>PP Anthony Capalbo</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="H42" t="inlineStr" s="17">
-        <x:is>
-          <x:t>Hold</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="I42" t="inlineStr" s="19">
-        <x:is>
-          <x:t>PLM - HVAC - Service - 12</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="J42" t="inlineStr" s="21">
-        <x:is>
-          <x:t>HARRIS, MIKE</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="K42" s="23">
-        <x:v>46110</x:v>
-      </x:c>
-      <x:c r="L42" s="25">
-        <x:v>46110</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="43">
-      <x:c r="A43" t="inlineStr" s="3">
-        <x:is>
-          <x:t>HC - Return to Repair</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B43" t="n" s="5">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="C43" t="inlineStr" s="7">
-        <x:is>
-          <x:t>Club Member, Need to order part (NTO), PLM</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D43" t="inlineStr" s="9">
-        <x:is>
-          <x:t>587785435</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="E43" t="inlineStr" s="11">
-        <x:is>
-          <x:t>587785435</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="F43" s="13">
-        <x:v>46110</x:v>
-      </x:c>
-      <x:c r="G43" t="inlineStr" s="15">
-        <x:is>
-          <x:t>Tyler Gallatin</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="H43" t="inlineStr" s="17">
-        <x:is>
-          <x:t>Hold</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="I43" t="inlineStr" s="19">
-        <x:is>
-          <x:t>PLM - HVAC - Service - 12</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="J43" t="inlineStr" s="21">
-        <x:is>
-          <x:t>Lera Chacon</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="K43" s="23">
-        <x:v>46110</x:v>
-      </x:c>
-      <x:c r="L43" s="25">
-        <x:v>46110</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="44">
-      <x:c r="A44" t="inlineStr" s="3">
-        <x:is>
-          <x:t>HC - Return to Repair</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B44" t="n" s="5">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="C44" t="inlineStr" s="7">
-        <x:is>
-          <x:t>5 YEAR WARRANTY, 5 YEAR WARRANTY, 5 YEAR WARRANTY, 5 YEAR WARRANTY, Club Member</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D44" t="inlineStr" s="9">
-        <x:is>
-          <x:t>587794082</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="E44" t="inlineStr" s="11">
-        <x:is>
-          <x:t>587794082</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="F44" s="13">
-        <x:v>46111</x:v>
-      </x:c>
-      <x:c r="G44" t="inlineStr" s="15">
-        <x:is>
-          <x:t>Tyler Gallatin</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="H44" t="inlineStr" s="17">
-        <x:is>
-          <x:t>Hold</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="I44" t="inlineStr" s="19">
-        <x:is>
-          <x:t>CS - HVAC - Service - 12</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="J44" t="inlineStr" s="21">
-        <x:is>
-          <x:t>Louise Claydon</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="K44" s="23">
-        <x:v>46110</x:v>
-      </x:c>
-      <x:c r="L44" s="25">
-        <x:v>46110</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="45">
-      <x:c r="A45" t="inlineStr" s="3">
-        <x:is>
-          <x:t>HC - Return to Repair</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B45" t="n" s="5">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="C45" t="inlineStr" s="7">
-        <x:is>
-          <x:t>5 YEAR WARRANTY, 5 YEAR WARRANTY, 5 YEAR WARRANTY, 5 YEAR WARRANTY, 5 YEAR WARRANTY, 5 YEAR WARRANTY, Club Member 3 sys, Gemaire, MULTI- 3, Parts Ordered</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D45" t="inlineStr" s="9">
-        <x:is>
-          <x:t>586595677</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="E45" t="inlineStr" s="11">
-        <x:is>
-          <x:t>586595677</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="F45" s="13">
-        <x:v>46111</x:v>
-      </x:c>
-      <x:c r="G45" t="inlineStr" s="15">
-        <x:is>
-          <x:t>PP Alejandro Espinosa</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="H45" t="inlineStr" s="17">
-        <x:is>
-          <x:t>Hold</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="I45" t="inlineStr" s="19">
-        <x:is>
-          <x:t>PLM - HVAC - Service - 12</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="J45" t="inlineStr" s="21">
-        <x:is>
-          <x:t>Bob Lauson</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="K45" s="23">
-        <x:v>46098</x:v>
-      </x:c>
-      <x:c r="L45" s="25">
-        <x:v>46098</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="46">
-      <x:c r="A46" t="inlineStr" s="3">
-        <x:is>
-          <x:t>HC - Return to Repair</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B46" t="n" s="5">
-        <x:v>462.83</x:v>
-      </x:c>
-      <x:c r="C46" t="inlineStr" s="7">
-        <x:is>
-          <x:t>Baker Supply, Club Member, Parts Ordered, PLM, Potential Membership Renewal, Residential Maintenance Agreement</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D46" t="inlineStr" s="9">
-        <x:is>
-          <x:t>555552166</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="E46" t="inlineStr" s="11">
-        <x:is>
-          <x:t>555552166</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="F46" s="13">
-        <x:v>46111</x:v>
-      </x:c>
-      <x:c r="G46" t="inlineStr" s="15">
-        <x:is>
-          <x:t>PP Cesar Levy</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="H46" t="inlineStr" s="17">
-        <x:is>
-          <x:t>Hold</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="I46" t="inlineStr" s="19">
-        <x:is>
-          <x:t>PLM - HVAC - Service - 12</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="J46" t="inlineStr" s="21">
-        <x:is>
-          <x:t>Wanda Betancourt</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="K46" s="23">
-        <x:v>46007</x:v>
-      </x:c>
-      <x:c r="L46" s="25">
-        <x:v>46007</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="47">
-      <x:c r="A47" t="inlineStr" s="3">
-        <x:is>
-          <x:t>HC - Return to Repair</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B47" t="n" s="5">
-        <x:v>945.4</x:v>
-      </x:c>
-      <x:c r="C47" t="inlineStr" s="7">
-        <x:is>
-          <x:t>Carrier enterprise, Club Member, Parts Received , PLM</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D47" t="inlineStr" s="9">
-        <x:is>
-          <x:t>587403893</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="E47" t="inlineStr" s="11">
-        <x:is>
-          <x:t>587403893</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="F47" s="13">
-        <x:v>46111</x:v>
-      </x:c>
-      <x:c r="G47" t="inlineStr" s="15">
-        <x:is>
-          <x:t>Rolin Moimeme</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="H47" t="inlineStr" s="17">
-        <x:is>
-          <x:t>Hold</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="I47" t="inlineStr" s="19">
-        <x:is>
-          <x:t>PLM - HVAC - Service - 12</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="J47" t="inlineStr" s="21">
-        <x:is>
-          <x:t>WALKER, CAMERON</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="K47" s="23">
-        <x:v>46106</x:v>
-      </x:c>
-      <x:c r="L47" s="25">
-        <x:v>46106</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="48">
-      <x:c r="A48" t="inlineStr" s="3">
-        <x:is>
-          <x:t>HC - Return to Repair</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B48" t="n" s="5">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="C48" t="inlineStr" s="7">
-        <x:is>
-          <x:t>Club Member, Gemaire, Parts Ordered</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D48" t="inlineStr" s="9">
-        <x:is>
-          <x:t>463016698</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="E48" t="inlineStr" s="11">
-        <x:is>
-          <x:t>463016698</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="F48" s="13">
-        <x:v>46111</x:v>
-      </x:c>
-      <x:c r="G48" t="inlineStr" s="15">
-        <x:is>
-          <x:t>PP Tyriq McCall</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="H48" t="inlineStr" s="17">
-        <x:is>
-          <x:t>Hold</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="I48" t="inlineStr" s="19">
-        <x:is>
-          <x:t>CS - HVAC - Service - 12</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="J48" t="inlineStr" s="21">
-        <x:is>
-          <x:t>Evan Frangos</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="K48" s="23">
-        <x:v>45762</x:v>
-      </x:c>
-      <x:c r="L48" s="25">
-        <x:v>45762</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="49">
-      <x:c r="A49" t="inlineStr" s="3">
-        <x:is>
-          <x:t>HC - Return to Repair</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B49" t="n" s="5">
-        <x:v>303.45</x:v>
-      </x:c>
-      <x:c r="C49" t="inlineStr" s="7">
-        <x:is>
-          <x:t>Carrier enterprise, Parts Ordered, Potential Member</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D49" t="inlineStr" s="9">
-        <x:is>
-          <x:t>581332764</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="E49" t="inlineStr" s="11">
-        <x:is>
-          <x:t>581332764</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="F49" s="13">
-        <x:v>46111</x:v>
-      </x:c>
-      <x:c r="G49" t="inlineStr" s="15">
-        <x:is>
-          <x:t>Justin Greene</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="H49" t="inlineStr" s="17">
-        <x:is>
-          <x:t>Hold</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="I49" t="inlineStr" s="19">
-        <x:is>
-          <x:t>CS - HVAC - Service - 12</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="J49" t="inlineStr" s="21">
-        <x:is>
-          <x:t>Chris Orsini</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="K49" s="23">
-        <x:v>46057</x:v>
-      </x:c>
-      <x:c r="L49" s="25">
-        <x:v>46057</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="50">
-      <x:c r="A50" t="n" s="4">
-        <x:v>48</x:v>
-      </x:c>
-      <x:c r="B50" t="n" s="6">
-        <x:v>717.071875</x:v>
-      </x:c>
-      <x:c r="C50" t="inlineStr" s="8">
+      <x:c r="A34" t="n" s="4">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="B34" t="n" s="6">
+        <x:v>658.63875</x:v>
+      </x:c>
+      <x:c r="C34" t="inlineStr" s="8">
         <x:is>
           <x:t/>
         </x:is>
       </x:c>
-      <x:c r="D50" t="n" s="10">
-        <x:v>48</x:v>
-      </x:c>
-      <x:c r="E50" t="inlineStr" s="12">
+      <x:c r="D34" t="n" s="10">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="E34" t="inlineStr" s="12">
         <x:is>
           <x:t/>
         </x:is>
       </x:c>
-      <x:c r="F50" s="14">
+      <x:c r="F34" s="14">
         <x:v/>
       </x:c>
-      <x:c r="G50" t="inlineStr" s="16">
+      <x:c r="G34" t="inlineStr" s="16">
         <x:is>
           <x:t/>
         </x:is>
       </x:c>
-      <x:c r="H50" t="inlineStr" s="18">
+      <x:c r="H34" t="inlineStr" s="18">
         <x:is>
           <x:t/>
         </x:is>
       </x:c>
-      <x:c r="I50" t="inlineStr" s="20">
+      <x:c r="I34" t="inlineStr" s="20">
         <x:is>
           <x:t/>
         </x:is>
       </x:c>
-      <x:c r="J50" t="inlineStr" s="22">
+      <x:c r="J34" t="inlineStr" s="22">
         <x:is>
           <x:t/>
         </x:is>
       </x:c>
-      <x:c r="K50" s="24">
+      <x:c r="K34" s="24">
         <x:v/>
       </x:c>
-      <x:c r="L50" s="26">
+      <x:c r="L34" s="26">
         <x:v/>
       </x:c>
     </x:row>
